--- a/research/traditional_assets/database/data/portugal/portugal_power.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_power.xlsx
@@ -650,10 +650,10 @@
         <v>0.1001995909210874</v>
       </c>
       <c r="X2">
-        <v>0.1134284912858791</v>
+        <v>0.1134055959833604</v>
       </c>
       <c r="Y2">
-        <v>-0.01322890036479177</v>
+        <v>-0.01320600506227304</v>
       </c>
       <c r="Z2">
         <v>0.5363306810150247</v>
@@ -662,10 +662,10 @@
         <v>0.05390288250147486</v>
       </c>
       <c r="AB2">
-        <v>0.07468003654948915</v>
+        <v>0.07467233577845106</v>
       </c>
       <c r="AC2">
-        <v>-0.02077715404801429</v>
+        <v>-0.0207694532769762</v>
       </c>
       <c r="AD2">
         <v>26291.8</v>
@@ -787,10 +787,10 @@
         <v>0.1001995909210874</v>
       </c>
       <c r="X3">
-        <v>0.1134284912858791</v>
+        <v>0.1134055959833604</v>
       </c>
       <c r="Y3">
-        <v>-0.01322890036479177</v>
+        <v>-0.01320600506227304</v>
       </c>
       <c r="Z3">
         <v>0.5363306810150247</v>
@@ -799,10 +799,10 @@
         <v>0.05390288250147486</v>
       </c>
       <c r="AB3">
-        <v>0.07468003654948915</v>
+        <v>0.07467233577845106</v>
       </c>
       <c r="AC3">
-        <v>-0.02077715404801429</v>
+        <v>-0.0207694532769762</v>
       </c>
       <c r="AD3">
         <v>26291.8</v>
@@ -1139,7 +1139,7 @@
         <v>2.23059716008559</v>
       </c>
       <c r="F2">
-        <v>8.98738199813681</v>
+        <v>9.18975742763403</v>
       </c>
       <c r="G2">
         <v>5.96564712288982</v>
@@ -1157,13 +1157,13 @@
         <v>13325</v>
       </c>
       <c r="L2">
-        <v>37415.9791082699</v>
+        <v>37681.0082101668</v>
       </c>
       <c r="M2">
         <v>37518.3</v>
       </c>
       <c r="N2">
-        <v>41259.9991082699</v>
+        <v>41525.0282101668</v>
       </c>
       <c r="O2">
         <v>26291.8</v>
@@ -1172,16 +1172,16 @@
         <v>5942.52</v>
       </c>
       <c r="Q2">
-        <v>0.0746800365494892</v>
+        <v>0.0746723357784511</v>
       </c>
       <c r="R2">
-        <v>0.0720610251743201</v>
+        <v>0.07188645923018171</v>
       </c>
       <c r="S2">
         <v>0.0550418543268039</v>
       </c>
       <c r="T2">
-        <v>0.0502228543268039</v>
+        <v>0.0491168543268039</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.113428491285879</v>
+        <v>0.11340559598336</v>
       </c>
       <c r="X2">
-        <v>0.0759148200297641</v>
+        <v>0.07590462480136601</v>
       </c>
       <c r="Y2">
         <v>1.13992747193953</v>
@@ -1236,7 +1236,7 @@
         <v>13325</v>
       </c>
       <c r="AK2">
-        <v>0.05932701242019611</v>
+        <v>0.05930692754367341</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07223014664460452</v>
+        <v>0.07222119884477138</v>
       </c>
       <c r="C2">
-        <v>43094.4842389256</v>
+        <v>43097.43278124389</v>
       </c>
       <c r="D2">
-        <v>40995.9842389256</v>
+        <v>40998.93278124389</v>
       </c>
       <c r="E2">
         <v>-26291.8</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07223014664460452</v>
+        <v>0.07222119884477138</v>
       </c>
       <c r="T2">
         <v>0.4454993697880388</v>
       </c>
       <c r="U2">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V2">
         <v>0.21</v>
       </c>
       <c r="W2">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07221887187991888</v>
+        <v>0.0721988828704654</v>
       </c>
       <c r="C3">
-        <v>42715.81206832555</v>
+        <v>42735.92273002939</v>
       </c>
       <c r="D3">
-        <v>41013.48006832555</v>
+        <v>41033.59073002938</v>
       </c>
       <c r="E3">
         <v>-25895.632</v>
@@ -1539,37 +1539,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M3">
-        <v>25.18568069992562</v>
+        <v>24.63104549992562</v>
       </c>
       <c r="N3">
-        <v>3370.114319300073</v>
+        <v>3370.668954500074</v>
       </c>
       <c r="O3">
-        <v>707.7240070530154</v>
+        <v>707.8404804450154</v>
       </c>
       <c r="P3">
-        <v>2662.390312247058</v>
+        <v>2662.828474055058</v>
       </c>
       <c r="Q3">
-        <v>4776.090312247058</v>
+        <v>4776.528474055058</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07244105387540489</v>
+        <v>0.07243203467393673</v>
       </c>
       <c r="T3">
         <v>0.4490543647590746</v>
       </c>
       <c r="U3">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V3">
         <v>0.21</v>
       </c>
       <c r="W3">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.8107299720522</v>
+        <v>137.8463614145105</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07220759711523327</v>
+        <v>0.07217656689615942</v>
       </c>
       <c r="C4">
-        <v>42337.15483746862</v>
+        <v>42374.47132373994</v>
       </c>
       <c r="D4">
-        <v>41030.99083746862</v>
+        <v>41068.30732373994</v>
       </c>
       <c r="E4">
         <v>-25499.464</v>
@@ -1621,37 +1621,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M4">
-        <v>50.37136139985125</v>
+        <v>49.26209099985125</v>
       </c>
       <c r="N4">
-        <v>3344.928638600148</v>
+        <v>3346.037909000148</v>
       </c>
       <c r="O4">
-        <v>702.4350141060311</v>
+        <v>702.6679608900311</v>
       </c>
       <c r="P4">
-        <v>2642.493624494117</v>
+        <v>2643.369948110117</v>
       </c>
       <c r="Q4">
-        <v>4756.193624494117</v>
+        <v>4757.069948110116</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07265626533540528</v>
+        <v>0.07264717327512586</v>
       </c>
       <c r="T4">
         <v>0.4526819106478868</v>
       </c>
       <c r="U4">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V4">
         <v>0.21</v>
       </c>
       <c r="W4">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.40536498602609</v>
+        <v>68.92318070725524</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07219632235054763</v>
+        <v>0.07215425092185344</v>
       </c>
       <c r="C5">
-        <v>41958.51256549874</v>
+        <v>42013.07871135177</v>
       </c>
       <c r="D5">
-        <v>41048.51656549874</v>
+        <v>41103.08271135177</v>
       </c>
       <c r="E5">
         <v>-25103.296</v>
@@ -1703,37 +1703,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M5">
-        <v>75.55704209977687</v>
+        <v>73.89313649977687</v>
       </c>
       <c r="N5">
-        <v>3319.742957900222</v>
+        <v>3321.406863500222</v>
       </c>
       <c r="O5">
-        <v>697.1460211590467</v>
+        <v>697.4954413350466</v>
       </c>
       <c r="P5">
-        <v>2622.596936741176</v>
+        <v>2623.911422165176</v>
       </c>
       <c r="Q5">
-        <v>4736.296936741175</v>
+        <v>4737.611422165175</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07287591414509641</v>
+        <v>0.0728667477237622</v>
       </c>
       <c r="T5">
         <v>0.4563842512972929</v>
       </c>
       <c r="U5">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V5">
         <v>0.21</v>
       </c>
       <c r="W5">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.93690999068406</v>
+        <v>45.94878713817015</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07218504758586199</v>
+        <v>0.07213193494754747</v>
       </c>
       <c r="C6">
-        <v>41579.88527159239</v>
+        <v>41651.74504234605</v>
       </c>
       <c r="D6">
-        <v>41066.05727159239</v>
+        <v>41137.91704234605</v>
       </c>
       <c r="E6">
         <v>-24707.128</v>
@@ -1785,37 +1785,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M6">
-        <v>100.7427227997025</v>
+        <v>98.52418199970249</v>
       </c>
       <c r="N6">
-        <v>3294.557277200297</v>
+        <v>3296.775818000297</v>
       </c>
       <c r="O6">
-        <v>691.8570282120623</v>
+        <v>692.3229217800623</v>
       </c>
       <c r="P6">
-        <v>2602.700248988235</v>
+        <v>2604.452896220234</v>
       </c>
       <c r="Q6">
-        <v>4716.400248988235</v>
+        <v>4718.152896220234</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07310013897165608</v>
+        <v>0.07309089664007845</v>
       </c>
       <c r="T6">
         <v>0.4601637240435618</v>
       </c>
       <c r="U6">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V6">
         <v>0.21</v>
       </c>
       <c r="W6">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.70268249301305</v>
+        <v>34.46159035362761</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07217377282117636</v>
+        <v>0.07210961897324147</v>
       </c>
       <c r="C7">
-        <v>41201.27297495888</v>
+        <v>41290.47046671121</v>
       </c>
       <c r="D7">
-        <v>41083.61297495888</v>
+        <v>41172.81046671121</v>
       </c>
       <c r="E7">
         <v>-24310.96</v>
@@ -1867,37 +1867,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M7">
-        <v>125.9284034996281</v>
+        <v>123.1552274996281</v>
       </c>
       <c r="N7">
-        <v>3269.371596500371</v>
+        <v>3272.144772500371</v>
       </c>
       <c r="O7">
-        <v>686.5680352650779</v>
+        <v>687.150402225078</v>
       </c>
       <c r="P7">
-        <v>2582.803561235293</v>
+        <v>2584.994370275293</v>
       </c>
       <c r="Q7">
-        <v>4696.503561235293</v>
+        <v>4698.694370275293</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07332908432088019</v>
+        <v>0.07331976448094872</v>
       </c>
       <c r="T7">
         <v>0.4640227646371204</v>
       </c>
       <c r="U7">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V7">
         <v>0.21</v>
       </c>
       <c r="W7">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.96214599441044</v>
+        <v>27.5692722829021</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07216249805649073</v>
+        <v>0.07208730299893551</v>
       </c>
       <c r="C8">
-        <v>40822.67569484041</v>
+        <v>40929.25513494487</v>
       </c>
       <c r="D8">
-        <v>41101.18369484041</v>
+        <v>41207.76313494487</v>
       </c>
       <c r="E8">
         <v>-23914.792</v>
@@ -1949,37 +1949,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M8">
-        <v>151.1140841995537</v>
+        <v>147.7862729995537</v>
       </c>
       <c r="N8">
-        <v>3244.185915800445</v>
+        <v>3247.513727000446</v>
       </c>
       <c r="O8">
-        <v>681.2790423180935</v>
+        <v>681.9778826700935</v>
       </c>
       <c r="P8">
-        <v>2562.906873482352</v>
+        <v>2565.535844330352</v>
       </c>
       <c r="Q8">
-        <v>4676.606873482351</v>
+        <v>4679.235844330352</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07356290084774735</v>
+        <v>0.07355350185034816</v>
       </c>
       <c r="T8">
         <v>0.4679639124773505</v>
       </c>
       <c r="U8">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V8">
         <v>0.21</v>
       </c>
       <c r="W8">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.46845499534203</v>
+        <v>22.97439356908508</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07215122329180509</v>
+        <v>0.07206498702462952</v>
       </c>
       <c r="C9">
-        <v>40444.09345051213</v>
+        <v>40568.09919805628</v>
       </c>
       <c r="D9">
-        <v>41118.76945051213</v>
+        <v>41242.77519805628</v>
       </c>
       <c r="E9">
         <v>-23518.624</v>
@@ -2031,37 +2031,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M9">
-        <v>176.2997648994794</v>
+        <v>172.4173184994794</v>
       </c>
       <c r="N9">
-        <v>3219.00023510052</v>
+        <v>3222.88268150052</v>
       </c>
       <c r="O9">
-        <v>675.9900493711092</v>
+        <v>676.8053631151091</v>
       </c>
       <c r="P9">
-        <v>2543.010185729411</v>
+        <v>2546.077318385411</v>
       </c>
       <c r="Q9">
-        <v>4656.710185729411</v>
+        <v>4659.777318385411</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07380174568702025</v>
+        <v>0.0737922658298422</v>
       </c>
       <c r="T9">
         <v>0.4719898161851125</v>
       </c>
       <c r="U9">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V9">
         <v>0.21</v>
       </c>
       <c r="W9">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.25867571029317</v>
+        <v>19.69233734493007</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07213994852711947</v>
+        <v>0.07204267105032354</v>
       </c>
       <c r="C10">
-        <v>40065.52626128212</v>
+        <v>40207.00280756822</v>
       </c>
       <c r="D10">
-        <v>41136.37026128211</v>
+        <v>41277.84680756822</v>
       </c>
       <c r="E10">
         <v>-23122.456</v>
@@ -2113,37 +2113,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M10">
-        <v>201.485445599405</v>
+        <v>197.048363999405</v>
       </c>
       <c r="N10">
-        <v>3193.814554400594</v>
+        <v>3198.251636000594</v>
       </c>
       <c r="O10">
-        <v>670.7010564241248</v>
+        <v>671.6328435601248</v>
       </c>
       <c r="P10">
-        <v>2523.113497976469</v>
+        <v>2526.618792440469</v>
       </c>
       <c r="Q10">
-        <v>4636.813497976469</v>
+        <v>4640.318792440469</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07404578280540779</v>
+        <v>0.07403622033062959</v>
       </c>
       <c r="T10">
         <v>0.4761032395386954</v>
       </c>
       <c r="U10">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V10">
         <v>0.21</v>
       </c>
       <c r="W10">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.85134124650652</v>
+        <v>17.23079517681381</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07212867376243384</v>
+        <v>0.07202035507601756</v>
       </c>
       <c r="C11">
-        <v>39686.97414649159</v>
+        <v>39845.96611551935</v>
       </c>
       <c r="D11">
-        <v>41153.98614649159</v>
+        <v>41312.97811551936</v>
       </c>
       <c r="E11">
         <v>-22726.288</v>
@@ -2195,37 +2195,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M11">
-        <v>226.6711262993306</v>
+        <v>221.6794094993306</v>
       </c>
       <c r="N11">
-        <v>3168.628873700669</v>
+        <v>3173.620590500669</v>
       </c>
       <c r="O11">
-        <v>665.4120634771405</v>
+        <v>666.4603240051404</v>
       </c>
       <c r="P11">
-        <v>2503.216810223528</v>
+        <v>2507.160266495528</v>
       </c>
       <c r="Q11">
-        <v>4616.916810223528</v>
+        <v>4620.860266495528</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0742951833769467</v>
+        <v>0.07428553646879693</v>
       </c>
       <c r="T11">
         <v>0.4803070678011482</v>
       </c>
       <c r="U11">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V11">
         <v>0.21</v>
       </c>
       <c r="W11">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.97896999689469</v>
+        <v>15.31626237939006</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07211739899774822</v>
+        <v>0.07199803910171157</v>
       </c>
       <c r="C12">
-        <v>39308.43712551489</v>
+        <v>39484.98927446642</v>
       </c>
       <c r="D12">
-        <v>41171.61712551489</v>
+        <v>41348.16927446643</v>
       </c>
       <c r="E12">
         <v>-22330.12</v>
@@ -2277,37 +2277,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M12">
-        <v>251.8568069992562</v>
+        <v>246.3104549992562</v>
       </c>
       <c r="N12">
-        <v>3143.443193000743</v>
+        <v>3148.989545000743</v>
       </c>
       <c r="O12">
-        <v>660.123070530156</v>
+        <v>661.287804450156</v>
       </c>
       <c r="P12">
-        <v>2483.320122470587</v>
+        <v>2487.701740550587</v>
       </c>
       <c r="Q12">
-        <v>4597.020122470587</v>
+        <v>4601.401740550587</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07455012618340869</v>
+        <v>0.0745403929655902</v>
       </c>
       <c r="T12">
         <v>0.4846043144694333</v>
       </c>
       <c r="U12">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V12">
         <v>0.21</v>
       </c>
       <c r="W12">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.48107299720522</v>
+        <v>13.78463614145105</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07210612423306258</v>
+        <v>0.07197572312740559</v>
       </c>
       <c r="C13">
-        <v>38929.9152177596</v>
+        <v>39124.07243748635</v>
       </c>
       <c r="D13">
-        <v>41189.2632177596</v>
+        <v>41383.42043748635</v>
       </c>
       <c r="E13">
         <v>-21933.952</v>
@@ -2359,37 +2359,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M13">
-        <v>277.0424876991818</v>
+        <v>270.9415004991818</v>
       </c>
       <c r="N13">
-        <v>3118.257512300817</v>
+        <v>3124.358499500817</v>
       </c>
       <c r="O13">
-        <v>654.8340775831716</v>
+        <v>656.1152848951716</v>
       </c>
       <c r="P13">
-        <v>2463.423434717646</v>
+        <v>2468.243214605646</v>
       </c>
       <c r="Q13">
-        <v>4577.123434717645</v>
+        <v>4581.943214605646</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07481079804170129</v>
+        <v>0.07480097657467097</v>
       </c>
       <c r="T13">
         <v>0.4889981284785787</v>
       </c>
       <c r="U13">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V13">
         <v>0.21</v>
       </c>
       <c r="W13">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.2555209065502</v>
+        <v>12.53148740131913</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07209484946837694</v>
+        <v>0.0719534071530996</v>
       </c>
       <c r="C14">
-        <v>38551.40844266654</v>
+        <v>38763.21575817855</v>
       </c>
       <c r="D14">
-        <v>41206.92444266655</v>
+        <v>41418.73175817855</v>
       </c>
       <c r="E14">
         <v>-21537.784</v>
@@ -2441,37 +2441,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M14">
-        <v>302.2281683991075</v>
+        <v>295.5725459991075</v>
       </c>
       <c r="N14">
-        <v>3093.071831600892</v>
+        <v>3099.727454000892</v>
       </c>
       <c r="O14">
-        <v>649.5450846361873</v>
+        <v>650.9427653401872</v>
       </c>
       <c r="P14">
-        <v>2443.526746964705</v>
+        <v>2448.784688660704</v>
       </c>
       <c r="Q14">
-        <v>4557.226746964705</v>
+        <v>4562.484688660705</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07507739426040963</v>
+        <v>0.07506748253850357</v>
       </c>
       <c r="T14">
         <v>0.4934918018970229</v>
       </c>
       <c r="U14">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V14">
         <v>0.21</v>
       </c>
       <c r="W14">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.23422749767102</v>
+        <v>11.48719678454254</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07208357470369131</v>
+        <v>0.07193109117879364</v>
       </c>
       <c r="C15">
-        <v>38172.91681970988</v>
+        <v>38402.41939066711</v>
       </c>
       <c r="D15">
-        <v>41224.60081970989</v>
+        <v>41454.10339066711</v>
       </c>
       <c r="E15">
         <v>-21141.616</v>
@@ -2523,37 +2523,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M15">
-        <v>327.4138490990331</v>
+        <v>320.2035914990331</v>
       </c>
       <c r="N15">
-        <v>3067.886150900966</v>
+        <v>3075.096408500966</v>
       </c>
       <c r="O15">
-        <v>644.2560916892029</v>
+        <v>645.770245785203</v>
       </c>
       <c r="P15">
-        <v>2423.630059211763</v>
+        <v>2429.326162715764</v>
       </c>
       <c r="Q15">
-        <v>4537.330059211763</v>
+        <v>4543.026162715763</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07535011912782393</v>
+        <v>0.07534011507621739</v>
       </c>
       <c r="T15">
         <v>0.4980887781526728</v>
       </c>
       <c r="U15">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V15">
         <v>0.21</v>
       </c>
       <c r="W15">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.37005615169632</v>
+        <v>10.60356626265465</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07207229993900569</v>
+        <v>0.07190877520448766</v>
       </c>
       <c r="C16">
-        <v>37794.4403683973</v>
+        <v>38041.68348960312</v>
       </c>
       <c r="D16">
-        <v>41242.2923683973</v>
+        <v>41489.53548960312</v>
       </c>
       <c r="E16">
         <v>-20745.448</v>
@@ -2605,37 +2605,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M16">
-        <v>352.5995297989587</v>
+        <v>344.8346369989587</v>
       </c>
       <c r="N16">
-        <v>3042.70047020104</v>
+        <v>3050.465363001041</v>
       </c>
       <c r="O16">
-        <v>638.9670987422185</v>
+        <v>640.5977262302185</v>
       </c>
       <c r="P16">
-        <v>2403.733371458822</v>
+        <v>2409.867636770822</v>
       </c>
       <c r="Q16">
-        <v>4517.433371458822</v>
+        <v>4523.567636770822</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07562918643401528</v>
+        <v>0.07561908790550595</v>
       </c>
       <c r="T16">
         <v>0.5027926608328727</v>
       </c>
       <c r="U16">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V16">
         <v>0.21</v>
       </c>
       <c r="W16">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.629337855146584</v>
+        <v>9.846168672465033</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07206102517432006</v>
+        <v>0.07188645923018167</v>
       </c>
       <c r="C17">
-        <v>37415.97910826989</v>
+        <v>37681.00821016682</v>
       </c>
       <c r="D17">
-        <v>41259.9991082699</v>
+        <v>41525.02821016683</v>
       </c>
       <c r="E17">
         <v>-20349.28</v>
@@ -2687,37 +2687,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M17">
-        <v>377.7852104988843</v>
+        <v>369.4656824988843</v>
       </c>
       <c r="N17">
-        <v>3017.514789501115</v>
+        <v>3025.834317501115</v>
       </c>
       <c r="O17">
-        <v>633.6781057952342</v>
+        <v>635.4252066752341</v>
       </c>
       <c r="P17">
-        <v>2383.836683705881</v>
+        <v>2390.409110825881</v>
       </c>
       <c r="Q17">
-        <v>4497.536683705881</v>
+        <v>4504.109110825881</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07591482002976409</v>
+        <v>0.07590462480136598</v>
       </c>
       <c r="T17">
         <v>0.5076072231055477</v>
       </c>
       <c r="U17">
-        <v>0.0635732333250682</v>
+        <v>0.0621732333250682</v>
       </c>
       <c r="V17">
         <v>0.21</v>
       </c>
       <c r="W17">
-        <v>0.05022285432680388</v>
+        <v>0.04911685432680388</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.987381998136811</v>
+        <v>9.189757427634031</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07218879040963444</v>
+        <v>0.07205374325587569</v>
       </c>
       <c r="C18">
-        <v>36820.04471453573</v>
+        <v>37020.2503641265</v>
       </c>
       <c r="D18">
-        <v>41060.23271453573</v>
+        <v>41260.4383641265</v>
       </c>
       <c r="E18">
         <v>-19953.112</v>
@@ -2769,37 +2769,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M18">
-        <v>409.9434479988099</v>
+        <v>403.6047599988099</v>
       </c>
       <c r="N18">
-        <v>2985.356552001189</v>
+        <v>2991.695240001189</v>
       </c>
       <c r="O18">
-        <v>626.9248759202497</v>
+        <v>628.2560004002497</v>
       </c>
       <c r="P18">
-        <v>2358.43167608094</v>
+        <v>2363.439239600939</v>
       </c>
       <c r="Q18">
-        <v>4472.13167608094</v>
+        <v>4477.13923960094</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07620725442541168</v>
+        <v>0.0761969601947465</v>
       </c>
       <c r="T18">
         <v>0.5125364178132865</v>
       </c>
       <c r="U18">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V18">
         <v>0.21</v>
       </c>
       <c r="W18">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.282361912538375</v>
+        <v>8.412437950459282</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07218620564494879</v>
+        <v>0.0720432772815697</v>
       </c>
       <c r="C19">
-        <v>36427.89893133088</v>
+        <v>36640.53727115428</v>
       </c>
       <c r="D19">
-        <v>41064.25493133088</v>
+        <v>41276.89327115428</v>
       </c>
       <c r="E19">
         <v>-19556.944</v>
@@ -2851,37 +2851,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M19">
-        <v>435.5649134987355</v>
+        <v>428.8300574987355</v>
       </c>
       <c r="N19">
-        <v>2959.735086501264</v>
+        <v>2966.469942501264</v>
       </c>
       <c r="O19">
-        <v>621.5443681652654</v>
+        <v>622.9586879252654</v>
       </c>
       <c r="P19">
-        <v>2338.190718335998</v>
+        <v>2343.511254575998</v>
       </c>
       <c r="Q19">
-        <v>4451.890718335998</v>
+        <v>4457.211254575998</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07650673543300257</v>
+        <v>0.07649633981447354</v>
       </c>
       <c r="T19">
         <v>0.5175843882971154</v>
       </c>
       <c r="U19">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.795164152977295</v>
+        <v>7.917588659255797</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07218362088026316</v>
+        <v>0.07203281130726372</v>
       </c>
       <c r="C20">
-        <v>36035.75393622736</v>
+        <v>36260.83730804697</v>
       </c>
       <c r="D20">
-        <v>41068.27793622736</v>
+        <v>41293.36130804697</v>
       </c>
       <c r="E20">
         <v>-19160.776</v>
@@ -2933,37 +2933,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M20">
-        <v>461.1863789986611</v>
+        <v>454.0553549986611</v>
       </c>
       <c r="N20">
-        <v>2934.113621001338</v>
+        <v>2941.244645001338</v>
       </c>
       <c r="O20">
-        <v>616.163860410281</v>
+        <v>617.661375450281</v>
       </c>
       <c r="P20">
-        <v>2317.949760591057</v>
+        <v>2323.583269551057</v>
       </c>
       <c r="Q20">
-        <v>4431.649760591057</v>
+        <v>4437.283269551057</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07681352085541276</v>
+        <v>0.07680302137614514</v>
       </c>
       <c r="T20">
         <v>0.5227554800122571</v>
       </c>
       <c r="U20">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V20">
         <v>0.21</v>
       </c>
       <c r="W20">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.36209947781189</v>
+        <v>7.477722622630475</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07218103611557754</v>
+        <v>0.07202234533295775</v>
       </c>
       <c r="C21">
-        <v>35643.60972945685</v>
+        <v>35881.15049052586</v>
       </c>
       <c r="D21">
-        <v>41072.30172945686</v>
+        <v>41309.84249052587</v>
       </c>
       <c r="E21">
         <v>-18764.608</v>
@@ -3015,37 +3015,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M21">
-        <v>486.8078444985867</v>
+        <v>479.2806524985867</v>
       </c>
       <c r="N21">
-        <v>2908.492155501413</v>
+        <v>2916.019347501413</v>
       </c>
       <c r="O21">
-        <v>610.7833526552967</v>
+        <v>612.3640629752966</v>
       </c>
       <c r="P21">
-        <v>2297.708802846116</v>
+        <v>2303.655284526116</v>
       </c>
       <c r="Q21">
-        <v>4411.408802846116</v>
+        <v>4417.355284526116</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07712788122652445</v>
+        <v>0.07711727532205556</v>
       </c>
       <c r="T21">
         <v>0.5280542530043161</v>
       </c>
       <c r="U21">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V21">
         <v>0.21</v>
       </c>
       <c r="W21">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.974620557927053</v>
+        <v>7.084158274070976</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07252605135089191</v>
+        <v>0.07201187935865176</v>
       </c>
       <c r="C22">
-        <v>34717.22611099369</v>
+        <v>35501.47683433748</v>
       </c>
       <c r="D22">
-        <v>40542.08611099369</v>
+        <v>41326.33683433748</v>
       </c>
       <c r="E22">
         <v>-18368.44</v>
@@ -3097,45 +3097,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M22">
-        <v>529.8607019985124</v>
+        <v>504.5059499985123</v>
       </c>
       <c r="N22">
-        <v>2865.439298001487</v>
+        <v>2890.794050001487</v>
       </c>
       <c r="O22">
-        <v>601.7422525803122</v>
+        <v>607.0667505003122</v>
       </c>
       <c r="P22">
-        <v>2263.697045421175</v>
+        <v>2283.727299501175</v>
       </c>
       <c r="Q22">
-        <v>4377.397045421174</v>
+        <v>4397.427299501174</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.0774501006069139</v>
+        <v>0.07743938561661373</v>
       </c>
       <c r="T22">
         <v>0.5334854953211764</v>
       </c>
       <c r="U22">
-        <v>0.0668732333250682</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.05282985432680388</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.407910583279173</v>
+        <v>6.729950360367427</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07254084658620627</v>
+        <v>0.07228344338434578</v>
       </c>
       <c r="C23">
-        <v>34298.62689505542</v>
+        <v>34681.54421147301</v>
       </c>
       <c r="D23">
-        <v>40519.65489505542</v>
+        <v>40902.57221147301</v>
       </c>
       <c r="E23">
         <v>-17972.272</v>
@@ -3179,37 +3179,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M23">
-        <v>556.353737098438</v>
+        <v>543.8744450984379</v>
       </c>
       <c r="N23">
-        <v>2838.946262901561</v>
+        <v>2851.425554901562</v>
       </c>
       <c r="O23">
-        <v>596.1787152093278</v>
+        <v>598.7993665293279</v>
       </c>
       <c r="P23">
-        <v>2242.767547692233</v>
+        <v>2252.626188372234</v>
       </c>
       <c r="Q23">
-        <v>4356.467547692233</v>
+        <v>4366.326188372233</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07778047743997146</v>
+        <v>0.07776965060217338</v>
       </c>
       <c r="T23">
         <v>0.5390542374435269</v>
       </c>
       <c r="U23">
-        <v>0.0668732333250682</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V23">
         <v>0.21</v>
       </c>
       <c r="W23">
-        <v>0.05282985432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.102771984075401</v>
+        <v>6.242801129193468</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07255564182152063</v>
+        <v>0.07228640741003979</v>
       </c>
       <c r="C24">
-        <v>33880.05248697789</v>
+        <v>34280.79890987415</v>
       </c>
       <c r="D24">
-        <v>40497.24848697789</v>
+        <v>40897.99490987416</v>
       </c>
       <c r="E24">
         <v>-17576.104</v>
@@ -3261,37 +3261,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M24">
-        <v>582.8467721983636</v>
+        <v>569.7732281983635</v>
       </c>
       <c r="N24">
-        <v>2812.453227801636</v>
+        <v>2825.526771801636</v>
       </c>
       <c r="O24">
-        <v>590.6151778383435</v>
+        <v>593.3606220783435</v>
       </c>
       <c r="P24">
-        <v>2221.838049963292</v>
+        <v>2232.166149723292</v>
       </c>
       <c r="Q24">
-        <v>4335.538049963292</v>
+        <v>4345.866149723292</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07811932547387665</v>
+        <v>0.07810838392069608</v>
       </c>
       <c r="T24">
         <v>0.5447657678254249</v>
       </c>
       <c r="U24">
-        <v>0.0668732333250682</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V24">
         <v>0.21</v>
       </c>
       <c r="W24">
-        <v>0.05282985432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.825373257526521</v>
+        <v>5.959037441502856</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07284298705683501</v>
+        <v>0.07228937143573382</v>
       </c>
       <c r="C25">
-        <v>33053.58100860774</v>
+        <v>33880.05463262873</v>
       </c>
       <c r="D25">
-        <v>40066.94500860774</v>
+        <v>40893.41863262873</v>
       </c>
       <c r="E25">
         <v>-17179.936</v>
@@ -3343,45 +3343,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M25">
-        <v>623.0076032982893</v>
+        <v>595.6720112982892</v>
       </c>
       <c r="N25">
-        <v>2772.29239670171</v>
+        <v>2799.62798870171</v>
       </c>
       <c r="O25">
-        <v>582.1814033073591</v>
+        <v>587.9218776273591</v>
       </c>
       <c r="P25">
-        <v>2190.110993394351</v>
+        <v>2211.706111074351</v>
       </c>
       <c r="Q25">
-        <v>4303.810993394351</v>
+        <v>4325.406111074351</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07846697475541574</v>
+        <v>0.07845591550723237</v>
       </c>
       <c r="T25">
         <v>0.5506256496458136</v>
       </c>
       <c r="U25">
-        <v>0.0683732333250682</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V25">
         <v>0.21</v>
       </c>
       <c r="W25">
-        <v>0.05401485432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.449853231364765</v>
+        <v>5.699948857089687</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07286963229214938</v>
+        <v>0.07244401546142784</v>
       </c>
       <c r="C26">
-        <v>32617.97423210127</v>
+        <v>33246.53791576975</v>
       </c>
       <c r="D26">
-        <v>40027.50623210127</v>
+        <v>40656.06991576975</v>
       </c>
       <c r="E26">
         <v>-16783.768</v>
@@ -3425,37 +3425,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M26">
-        <v>650.0948903982149</v>
+        <v>629.1772199982148</v>
       </c>
       <c r="N26">
-        <v>2745.205109601784</v>
+        <v>2766.122780001785</v>
       </c>
       <c r="O26">
-        <v>576.4930730163748</v>
+        <v>580.8857838003747</v>
       </c>
       <c r="P26">
-        <v>2168.71203658541</v>
+        <v>2185.23699620141</v>
       </c>
       <c r="Q26">
-        <v>4282.41203658541</v>
+        <v>4298.93699620141</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07882377270225849</v>
+        <v>0.07881259266183541</v>
       </c>
       <c r="T26">
         <v>0.5566397388825285</v>
       </c>
       <c r="U26">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V26">
         <v>0.21</v>
       </c>
       <c r="W26">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.222776013391233</v>
+        <v>5.396412794489974</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07289627752746375</v>
+        <v>0.07245329948712186</v>
       </c>
       <c r="C27">
-        <v>32182.44502015912</v>
+        <v>32836.20836710677</v>
       </c>
       <c r="D27">
-        <v>39988.14502015912</v>
+        <v>40641.90836710677</v>
       </c>
       <c r="E27">
         <v>-16387.6</v>
@@ -3507,37 +3507,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M27">
-        <v>677.1821774981405</v>
+        <v>655.3929374981404</v>
       </c>
       <c r="N27">
-        <v>2718.117822501859</v>
+        <v>2739.907062501859</v>
       </c>
       <c r="O27">
-        <v>570.8047427253904</v>
+        <v>575.3804831253904</v>
       </c>
       <c r="P27">
-        <v>2147.313079776468</v>
+        <v>2164.526579376468</v>
       </c>
       <c r="Q27">
-        <v>4261.013079776469</v>
+        <v>4278.226579376468</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07919008526101703</v>
+        <v>0.07917878120722785</v>
       </c>
       <c r="T27">
         <v>0.5628142038322222</v>
       </c>
       <c r="U27">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V27">
         <v>0.21</v>
       </c>
       <c r="W27">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.013864972855584</v>
+        <v>5.180556282710374</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07292292276277811</v>
+        <v>0.07246258351281587</v>
       </c>
       <c r="C28">
-        <v>31746.99314418581</v>
+        <v>32425.88868066751</v>
       </c>
       <c r="D28">
-        <v>39948.86114418581</v>
+        <v>40627.75668066752</v>
       </c>
       <c r="E28">
         <v>-15991.432</v>
@@ -3589,37 +3589,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M28">
-        <v>704.2694645980661</v>
+        <v>681.6086549980661</v>
       </c>
       <c r="N28">
-        <v>2691.030535401933</v>
+        <v>2713.691345001933</v>
       </c>
       <c r="O28">
-        <v>565.116412434406</v>
+        <v>569.875182450406</v>
       </c>
       <c r="P28">
-        <v>2125.914122967527</v>
+        <v>2143.816162551527</v>
       </c>
       <c r="Q28">
-        <v>4239.614122967527</v>
+        <v>4257.516162551527</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07956629815920149</v>
+        <v>0.0795548667403336</v>
       </c>
       <c r="T28">
         <v>0.569155546212989</v>
       </c>
       <c r="U28">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V28">
         <v>0.21</v>
       </c>
       <c r="W28">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.821024012361139</v>
+        <v>4.981304117990745</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07294956799809248</v>
+        <v>0.0724718675385099</v>
       </c>
       <c r="C29">
-        <v>31311.61837648317</v>
+        <v>32015.57884615332</v>
       </c>
       <c r="D29">
-        <v>39909.65437648317</v>
+        <v>40613.61484615332</v>
       </c>
       <c r="E29">
         <v>-15595.264</v>
@@ -3671,37 +3671,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M29">
-        <v>731.3567516979919</v>
+        <v>707.8243724979917</v>
       </c>
       <c r="N29">
-        <v>2663.943248302007</v>
+        <v>2687.475627502008</v>
       </c>
       <c r="O29">
-        <v>559.4280821434215</v>
+        <v>564.3698817754216</v>
       </c>
       <c r="P29">
-        <v>2104.515166158586</v>
+        <v>2123.105745726586</v>
       </c>
       <c r="Q29">
-        <v>4218.215166158586</v>
+        <v>4236.805745726586</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07995281826007594</v>
+        <v>0.07994125598667515</v>
       </c>
       <c r="T29">
         <v>0.575670624001448</v>
       </c>
       <c r="U29">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V29">
         <v>0.21</v>
       </c>
       <c r="W29">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.642467567458873</v>
+        <v>4.796811372879977</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07297621323340686</v>
+        <v>0.07248115156420391</v>
       </c>
       <c r="C30">
-        <v>30876.32049024612</v>
+        <v>31605.27885327996</v>
       </c>
       <c r="D30">
-        <v>39870.52449024612</v>
+        <v>40599.48285327996</v>
       </c>
       <c r="E30">
         <v>-15199.096</v>
@@ -3753,37 +3753,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M30">
-        <v>758.4440387979174</v>
+        <v>734.0400899979173</v>
       </c>
       <c r="N30">
-        <v>2636.855961202082</v>
+        <v>2661.259910002082</v>
       </c>
       <c r="O30">
-        <v>553.7397518524372</v>
+        <v>558.8645811004372</v>
       </c>
       <c r="P30">
-        <v>2083.116209349645</v>
+        <v>2102.395328901645</v>
       </c>
       <c r="Q30">
-        <v>4196.816209349645</v>
+        <v>4216.095328901645</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08035007503041913</v>
+        <v>0.08033837826763726</v>
       </c>
       <c r="T30">
         <v>0.5823666761729196</v>
       </c>
       <c r="U30">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V30">
         <v>0.21</v>
       </c>
       <c r="W30">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.476665154335342</v>
+        <v>4.625496680991406</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07300285846872122</v>
+        <v>0.07249043558989793</v>
       </c>
       <c r="C31">
-        <v>30441.09925955822</v>
+        <v>31194.98869177742</v>
       </c>
       <c r="D31">
-        <v>39831.47125955822</v>
+        <v>40585.36069177742</v>
       </c>
       <c r="E31">
         <v>-14802.928</v>
@@ -3835,37 +3835,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M31">
-        <v>785.5313258978429</v>
+        <v>760.2558074978429</v>
       </c>
       <c r="N31">
-        <v>2609.768674102156</v>
+        <v>2635.044192502156</v>
       </c>
       <c r="O31">
-        <v>548.0514215614528</v>
+        <v>553.3592804254529</v>
       </c>
       <c r="P31">
-        <v>2061.717252540703</v>
+        <v>2081.684912076704</v>
       </c>
       <c r="Q31">
-        <v>4175.417252540703</v>
+        <v>4195.384912076704</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08075852213232126</v>
+        <v>0.08074668709172508</v>
       </c>
       <c r="T31">
         <v>0.5892513495323201</v>
       </c>
       <c r="U31">
-        <v>0.0683732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V31">
         <v>0.21</v>
       </c>
       <c r="W31">
-        <v>0.05401485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.322297390392745</v>
+        <v>4.465996795439978</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0733613037040356</v>
+        <v>0.07249971961559196</v>
       </c>
       <c r="C32">
-        <v>29526.9078292493</v>
+        <v>30784.70835139</v>
       </c>
       <c r="D32">
-        <v>39313.4478292493</v>
+        <v>40571.24835139</v>
       </c>
       <c r="E32">
         <v>-14406.76</v>
@@ -3917,45 +3917,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M32">
-        <v>829.2576689977686</v>
+        <v>786.4715249977685</v>
       </c>
       <c r="N32">
-        <v>2566.042331002231</v>
+        <v>2608.828475002231</v>
       </c>
       <c r="O32">
-        <v>538.8688895104684</v>
+        <v>547.8539797504684</v>
       </c>
       <c r="P32">
-        <v>2027.173441491762</v>
+        <v>2060.974495251762</v>
       </c>
       <c r="Q32">
-        <v>4140.873441491762</v>
+        <v>4174.674495251762</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08117863915142062</v>
+        <v>0.08116666188221541</v>
       </c>
       <c r="T32">
         <v>0.5963327278448461</v>
       </c>
       <c r="U32">
-        <v>0.0697732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.05512085432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.09438480575467</v>
+        <v>4.317130235591979</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07339900893934996</v>
+        <v>0.07275390364128596</v>
       </c>
       <c r="C33">
-        <v>29077.03055277933</v>
+        <v>30005.94036251152</v>
       </c>
       <c r="D33">
-        <v>39259.73855277933</v>
+        <v>40188.64836251152</v>
       </c>
       <c r="E33">
         <v>-14010.592</v>
@@ -3999,37 +3999,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M33">
-        <v>856.8995912976942</v>
+        <v>824.9684504976941</v>
       </c>
       <c r="N33">
-        <v>2538.400408702305</v>
+        <v>2570.331549502305</v>
       </c>
       <c r="O33">
-        <v>533.0640858274841</v>
+        <v>539.7696253954841</v>
       </c>
       <c r="P33">
-        <v>2005.336322874821</v>
+        <v>2030.561924106821</v>
       </c>
       <c r="Q33">
-        <v>4119.036322874821</v>
+        <v>4144.261924106821</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08161093347542139</v>
+        <v>0.0815988098550388</v>
       </c>
       <c r="T33">
         <v>0.6036193634997645</v>
       </c>
       <c r="U33">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V33">
         <v>0.21</v>
       </c>
       <c r="W33">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.962307876536777</v>
+        <v>4.115672542327713</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07343671417466432</v>
+        <v>0.07277108766697998</v>
       </c>
       <c r="C34">
-        <v>28627.29982925302</v>
+        <v>29584.16706343732</v>
       </c>
       <c r="D34">
-        <v>39206.17582925303</v>
+        <v>40163.04306343733</v>
       </c>
       <c r="E34">
         <v>-13614.424</v>
@@ -4081,37 +4081,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M34">
-        <v>884.5415135976199</v>
+        <v>851.5803359976198</v>
       </c>
       <c r="N34">
-        <v>2510.758486402379</v>
+        <v>2543.719664002379</v>
       </c>
       <c r="O34">
-        <v>527.2592821444996</v>
+        <v>534.1811294404997</v>
       </c>
       <c r="P34">
-        <v>1983.49920425788</v>
+        <v>2009.53853456188</v>
       </c>
       <c r="Q34">
-        <v>4097.19920425788</v>
+        <v>4123.23853456188</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08205594233836337</v>
+        <v>0.08204366806235698</v>
       </c>
       <c r="T34">
         <v>0.6111203119680626</v>
       </c>
       <c r="U34">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V34">
         <v>0.21</v>
       </c>
       <c r="W34">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.838485755395003</v>
+        <v>3.987057775379972</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0734744194099787</v>
+        <v>0.072788271692674</v>
       </c>
       <c r="C35">
-        <v>28177.71505965367</v>
+        <v>29162.42637127641</v>
       </c>
       <c r="D35">
-        <v>39152.75905965367</v>
+        <v>40137.47037127641</v>
       </c>
       <c r="E35">
         <v>-13218.256</v>
@@ -4163,37 +4163,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M35">
-        <v>912.1834358975456</v>
+        <v>878.1922214975455</v>
       </c>
       <c r="N35">
-        <v>2483.116564102454</v>
+        <v>2517.107778502454</v>
       </c>
       <c r="O35">
-        <v>521.4544784615152</v>
+        <v>528.5926334855152</v>
       </c>
       <c r="P35">
-        <v>1961.662085640938</v>
+        <v>1988.515145016938</v>
       </c>
       <c r="Q35">
-        <v>4075.362085640938</v>
+        <v>4102.215145016939</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08251423504796034</v>
+        <v>0.08250180561914736</v>
       </c>
       <c r="T35">
         <v>0.6188451693458622</v>
       </c>
       <c r="U35">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V35">
         <v>0.21</v>
       </c>
       <c r="W35">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.722168005231518</v>
+        <v>3.8662378427927</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07351212464529308</v>
+        <v>0.07280545571836802</v>
       </c>
       <c r="C36">
-        <v>27728.27564822466</v>
+        <v>28740.71822378377</v>
       </c>
       <c r="D36">
-        <v>39099.48764822466</v>
+        <v>40111.93022378377</v>
       </c>
       <c r="E36">
         <v>-12822.088</v>
@@ -4245,37 +4245,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M36">
-        <v>939.8253581974711</v>
+        <v>904.8041069974711</v>
       </c>
       <c r="N36">
-        <v>2455.474641802528</v>
+        <v>2490.495893002528</v>
       </c>
       <c r="O36">
-        <v>515.6496747785309</v>
+        <v>523.0041375305309</v>
       </c>
       <c r="P36">
-        <v>1939.824967023997</v>
+        <v>1967.491755471997</v>
       </c>
       <c r="Q36">
-        <v>4053.524967023997</v>
+        <v>4081.191755471997</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08298641541542388</v>
+        <v>0.08297382613220411</v>
       </c>
       <c r="T36">
         <v>0.626804113310868</v>
       </c>
       <c r="U36">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.612692475665885</v>
+        <v>3.752524965063503</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07354982988060745</v>
+        <v>0.07282263974406204</v>
       </c>
       <c r="C37">
-        <v>27278.98100244736</v>
+        <v>28319.04255887276</v>
       </c>
       <c r="D37">
-        <v>39046.36100244736</v>
+        <v>40086.42255887276</v>
       </c>
       <c r="E37">
         <v>-12425.92</v>
@@ -4327,37 +4327,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M37">
-        <v>967.4672804973968</v>
+        <v>931.4159924973967</v>
       </c>
       <c r="N37">
-        <v>2427.832719502602</v>
+        <v>2463.884007502603</v>
       </c>
       <c r="O37">
-        <v>509.8448710955465</v>
+        <v>517.4156415755466</v>
       </c>
       <c r="P37">
-        <v>1917.987848407056</v>
+        <v>1946.468365927056</v>
       </c>
       <c r="Q37">
-        <v>4031.687848407056</v>
+        <v>4060.168365927056</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0834731244095786</v>
+        <v>0.08346037035335491</v>
       </c>
       <c r="T37">
         <v>0.6350079478594123</v>
       </c>
       <c r="U37">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V37">
         <v>0.21</v>
       </c>
       <c r="W37">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.509472690646859</v>
+        <v>3.645309966061689</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07358753511592181</v>
+        <v>0.07283982376975606</v>
       </c>
       <c r="C38">
-        <v>26829.83053301906</v>
+        <v>27897.39931461457</v>
       </c>
       <c r="D38">
-        <v>38993.37853301907</v>
+        <v>40060.94731461458</v>
       </c>
       <c r="E38">
         <v>-12029.752</v>
@@ -4409,37 +4409,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M38">
-        <v>995.1092027973223</v>
+        <v>958.0278779973222</v>
       </c>
       <c r="N38">
-        <v>2400.190797202677</v>
+        <v>2437.272122002677</v>
       </c>
       <c r="O38">
-        <v>504.0400674125622</v>
+        <v>511.8271456205621</v>
       </c>
       <c r="P38">
-        <v>1896.150729790115</v>
+        <v>1925.444976382115</v>
       </c>
       <c r="Q38">
-        <v>4009.850729790115</v>
+        <v>4039.144976382115</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08397504305980065</v>
+        <v>0.08396211908141667</v>
       </c>
       <c r="T38">
         <v>0.6434681522375985</v>
       </c>
       <c r="U38">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V38">
         <v>0.21</v>
       </c>
       <c r="W38">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.411987338128892</v>
+        <v>3.544051355893309</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07362524035123619</v>
+        <v>0.0728570077954501</v>
       </c>
       <c r="C39">
-        <v>26380.82365383128</v>
+        <v>27475.78842923767</v>
       </c>
       <c r="D39">
-        <v>38940.53965383128</v>
+        <v>40035.50442923767</v>
       </c>
       <c r="E39">
         <v>-11633.584</v>
@@ -4491,37 +4491,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M39">
-        <v>1022.751125097248</v>
+        <v>984.6397634972478</v>
       </c>
       <c r="N39">
-        <v>2372.548874902751</v>
+        <v>2410.660236502752</v>
       </c>
       <c r="O39">
-        <v>498.2352637295778</v>
+        <v>506.2386496655778</v>
       </c>
       <c r="P39">
-        <v>1874.313611173174</v>
+        <v>1904.421586837174</v>
       </c>
       <c r="Q39">
-        <v>3988.013611173174</v>
+        <v>4018.121586837174</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08449289563542658</v>
+        <v>0.08447979634052802</v>
       </c>
       <c r="T39">
         <v>0.6521969345325527</v>
       </c>
       <c r="U39">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V39">
         <v>0.21</v>
       </c>
       <c r="W39">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.319771464125409</v>
+        <v>3.448266184112409</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07366294558655055</v>
+        <v>0.0728741918211441</v>
       </c>
       <c r="C40">
-        <v>25931.95978194813</v>
+        <v>27054.20984112744</v>
       </c>
       <c r="D40">
-        <v>38887.84378194813</v>
+        <v>40010.09384112744</v>
       </c>
       <c r="E40">
         <v>-11237.416</v>
@@ -4573,37 +4573,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M40">
-        <v>1050.393047397174</v>
+        <v>1011.251648997174</v>
       </c>
       <c r="N40">
-        <v>2344.906952602826</v>
+        <v>2384.048351002826</v>
       </c>
       <c r="O40">
-        <v>492.4304600465933</v>
+        <v>500.6501537105934</v>
       </c>
       <c r="P40">
-        <v>1852.476492556232</v>
+        <v>1883.398197292232</v>
       </c>
       <c r="Q40">
-        <v>3966.176492556232</v>
+        <v>3997.098197292232</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.0850274531328469</v>
+        <v>0.0850141728660623</v>
       </c>
       <c r="T40">
         <v>0.6612072904499248</v>
       </c>
       <c r="U40">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V40">
         <v>0.21</v>
       </c>
       <c r="W40">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.232409057174739</v>
+        <v>3.357522337162082</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07370065082186492</v>
+        <v>0.07289137584683812</v>
       </c>
       <c r="C41">
-        <v>25483.23833758483</v>
+        <v>26632.66348882546</v>
       </c>
       <c r="D41">
-        <v>38835.29033758483</v>
+        <v>39984.71548882547</v>
       </c>
       <c r="E41">
         <v>-10841.248</v>
@@ -4655,37 +4655,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M41">
-        <v>1078.034969697099</v>
+        <v>1037.863534497099</v>
       </c>
       <c r="N41">
-        <v>2317.2650303029</v>
+        <v>2357.4364655029</v>
       </c>
       <c r="O41">
-        <v>486.625656363609</v>
+        <v>495.0616577556091</v>
       </c>
       <c r="P41">
-        <v>1830.639373939291</v>
+        <v>1862.374807747291</v>
       </c>
       <c r="Q41">
-        <v>3944.339373939291</v>
+        <v>3976.074807747291</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08557953710559248</v>
+        <v>0.08556606993341739</v>
       </c>
       <c r="T41">
         <v>0.6705130678727843</v>
       </c>
       <c r="U41">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V41">
         <v>0.21</v>
       </c>
       <c r="W41">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.149526773657438</v>
+        <v>3.271432020824593</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07373835605717929</v>
+        <v>0.07290855987253214</v>
       </c>
       <c r="C42">
-        <v>25034.6587440865</v>
+        <v>26211.14931102927</v>
       </c>
       <c r="D42">
-        <v>38782.8787440865</v>
+        <v>39959.36931102927</v>
       </c>
       <c r="E42">
         <v>-10445.08</v>
@@ -4737,37 +4737,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M42">
-        <v>1105.676891997025</v>
+        <v>1064.475419997025</v>
       </c>
       <c r="N42">
-        <v>2289.623108002975</v>
+        <v>2330.824580002974</v>
       </c>
       <c r="O42">
-        <v>480.8208526806247</v>
+        <v>489.4731618006246</v>
       </c>
       <c r="P42">
-        <v>1808.80225532235</v>
+        <v>1841.35141820235</v>
       </c>
       <c r="Q42">
-        <v>3922.50225532235</v>
+        <v>3955.05141820235</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08615002387742957</v>
+        <v>0.08613636356968432</v>
       </c>
       <c r="T42">
         <v>0.680129037876406</v>
       </c>
       <c r="U42">
-        <v>0.0697732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V42">
         <v>0.21</v>
       </c>
       <c r="W42">
-        <v>0.05512085432680388</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.070788604316003</v>
+        <v>3.189646220303977</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07461820129249366</v>
+        <v>0.07292574389822616</v>
       </c>
       <c r="C43">
-        <v>23454.41507161739</v>
+        <v>25789.66724659167</v>
       </c>
       <c r="D43">
-        <v>37598.8030716174</v>
+        <v>39934.05524659168</v>
       </c>
       <c r="E43">
         <v>-10048.912</v>
@@ -4819,45 +4819,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M43">
-        <v>1175.550323096951</v>
+        <v>1091.08730549695</v>
       </c>
       <c r="N43">
-        <v>2219.749676903049</v>
+        <v>2304.212694503049</v>
       </c>
       <c r="O43">
-        <v>466.1474321496402</v>
+        <v>483.8846658456402</v>
       </c>
       <c r="P43">
-        <v>1753.602244753408</v>
+        <v>1820.328028657408</v>
       </c>
       <c r="Q43">
-        <v>3867.302244753408</v>
+        <v>3934.028028657408</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.0867398491839052</v>
+        <v>0.0867259891936213</v>
       </c>
       <c r="T43">
         <v>0.6900709729648959</v>
       </c>
       <c r="U43">
-        <v>0.0723732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V43">
         <v>0.21</v>
       </c>
       <c r="W43">
-        <v>0.05717485432680389</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.888264273583105</v>
+        <v>3.111849971028271</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07467644652780804</v>
+        <v>0.07294292792392018</v>
       </c>
       <c r="C44">
-        <v>22982.40840738506</v>
+        <v>25368.21723452034</v>
       </c>
       <c r="D44">
-        <v>37522.96440738506</v>
+        <v>39908.77323452034</v>
       </c>
       <c r="E44">
         <v>-9652.743999999999</v>
@@ -4901,45 +4901,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M44">
-        <v>1204.222282196876</v>
+        <v>1117.699190996876</v>
       </c>
       <c r="N44">
-        <v>2191.077717803123</v>
+        <v>2277.600809003124</v>
       </c>
       <c r="O44">
-        <v>460.1263207386558</v>
+        <v>478.296169890656</v>
       </c>
       <c r="P44">
-        <v>1730.951397064467</v>
+        <v>1799.304639112468</v>
       </c>
       <c r="Q44">
-        <v>3844.651397064467</v>
+        <v>3913.004639112467</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08735001329405241</v>
+        <v>0.08733594673562509</v>
       </c>
       <c r="T44">
         <v>0.7003557334012651</v>
       </c>
       <c r="U44">
-        <v>0.0723732333250682</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V44">
         <v>0.21</v>
       </c>
       <c r="W44">
-        <v>0.05717485432680389</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.819496076593032</v>
+        <v>3.037758305051408</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0747346917631224</v>
+        <v>0.0738093619496142</v>
       </c>
       <c r="C45">
-        <v>22510.7070680465</v>
+        <v>23737.52203906699</v>
       </c>
       <c r="D45">
-        <v>37447.4310680465</v>
+        <v>38674.24603906699</v>
       </c>
       <c r="E45">
         <v>-9256.575999999997</v>
@@ -4983,37 +4983,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M45">
-        <v>1232.894241296802</v>
+        <v>1186.899136496802</v>
       </c>
       <c r="N45">
-        <v>2162.405758703198</v>
+        <v>2208.400863503198</v>
       </c>
       <c r="O45">
-        <v>454.1052093276714</v>
+        <v>463.7641813356715</v>
       </c>
       <c r="P45">
-        <v>1708.300549375526</v>
+        <v>1744.636682167526</v>
       </c>
       <c r="Q45">
-        <v>3822.000549375526</v>
+        <v>3858.336682167526</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08798158667122233</v>
+        <v>0.08796730629664654</v>
       </c>
       <c r="T45">
         <v>0.7110013626248751</v>
       </c>
       <c r="U45">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V45">
         <v>0.21</v>
       </c>
       <c r="W45">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.753926400393194</v>
+        <v>2.860647459919311</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07479293699843678</v>
+        <v>0.07384629597530823</v>
       </c>
       <c r="C46">
-        <v>22039.3092134583</v>
+        <v>23290.42411954529</v>
       </c>
       <c r="D46">
-        <v>37372.2012134583</v>
+        <v>38623.31611954529</v>
       </c>
       <c r="E46">
         <v>-8860.407999999999</v>
@@ -5065,37 +5065,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M46">
-        <v>1261.566200396727</v>
+        <v>1214.501441996727</v>
       </c>
       <c r="N46">
-        <v>2133.733799603272</v>
+        <v>2180.798558003272</v>
       </c>
       <c r="O46">
-        <v>448.0840979166871</v>
+        <v>457.9676971806871</v>
       </c>
       <c r="P46">
-        <v>1685.649701686585</v>
+        <v>1722.830860822585</v>
       </c>
       <c r="Q46">
-        <v>3799.349701686585</v>
+        <v>3836.530860822585</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08863571624043404</v>
+        <v>0.08862121441341878</v>
       </c>
       <c r="T46">
         <v>0.7220271928921858</v>
       </c>
       <c r="U46">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V46">
         <v>0.21</v>
       </c>
       <c r="W46">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.691337164020622</v>
+        <v>2.795632744921145</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07485118223375115</v>
+        <v>0.07388323000100225</v>
       </c>
       <c r="C47">
-        <v>21568.21301823446</v>
+        <v>22843.46016231756</v>
       </c>
       <c r="D47">
-        <v>37297.27301823446</v>
+        <v>38572.52016231756</v>
       </c>
       <c r="E47">
         <v>-8464.239999999998</v>
@@ -5147,37 +5147,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M47">
-        <v>1290.238159496653</v>
+        <v>1242.103747496653</v>
       </c>
       <c r="N47">
-        <v>2105.061840503347</v>
+        <v>2153.196252503346</v>
       </c>
       <c r="O47">
-        <v>442.0629865057027</v>
+        <v>452.1712130257027</v>
       </c>
       <c r="P47">
-        <v>1662.998853997644</v>
+        <v>1701.025039477644</v>
       </c>
       <c r="Q47">
-        <v>3776.698853997644</v>
+        <v>3814.725039477643</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08931363233943526</v>
+        <v>0.08929890100716453</v>
       </c>
       <c r="T47">
         <v>0.7334539624419439</v>
       </c>
       <c r="U47">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V47">
         <v>0.21</v>
       </c>
       <c r="W47">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.63152967148683</v>
+        <v>2.733507572811786</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07490942746906551</v>
+        <v>0.07392016402669625</v>
       </c>
       <c r="C48">
-        <v>21097.41667159866</v>
+        <v>22396.62963953124</v>
       </c>
       <c r="D48">
-        <v>37222.64467159866</v>
+        <v>38521.85763953124</v>
       </c>
       <c r="E48">
         <v>-8068.071999999996</v>
@@ -5229,37 +5229,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M48">
-        <v>1318.910118596579</v>
+        <v>1269.706052996579</v>
       </c>
       <c r="N48">
-        <v>2076.389881403421</v>
+        <v>2125.593947003421</v>
       </c>
       <c r="O48">
-        <v>436.0418750947183</v>
+        <v>446.3747288707184</v>
       </c>
       <c r="P48">
-        <v>1640.348006308702</v>
+        <v>1679.219218132703</v>
       </c>
       <c r="Q48">
-        <v>3754.048006308702</v>
+        <v>3792.919218132703</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09001665644210319</v>
+        <v>0.09000168710438235</v>
       </c>
       <c r="T48">
         <v>0.74530394567873</v>
       </c>
       <c r="U48">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V48">
         <v>0.21</v>
       </c>
       <c r="W48">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.574322504715377</v>
+        <v>2.674083495141965</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07496767270437987</v>
+        <v>0.07395709805239027</v>
       </c>
       <c r="C49">
-        <v>20626.9183772384</v>
+        <v>21949.9320261033</v>
       </c>
       <c r="D49">
-        <v>37148.31437723841</v>
+        <v>38471.3280261033</v>
       </c>
       <c r="E49">
         <v>-7671.903999999995</v>
@@ -5311,37 +5311,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M49">
-        <v>1347.582077696504</v>
+        <v>1297.308358496504</v>
       </c>
       <c r="N49">
-        <v>2047.717922303495</v>
+        <v>2097.991641503495</v>
       </c>
       <c r="O49">
-        <v>430.0207636837339</v>
+        <v>440.5782447157339</v>
       </c>
       <c r="P49">
-        <v>1617.697158619761</v>
+        <v>1657.413396787761</v>
       </c>
       <c r="Q49">
-        <v>3731.397158619761</v>
+        <v>3771.113396787761</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09074620975619255</v>
+        <v>0.09073099343168387</v>
       </c>
       <c r="T49">
         <v>0.757601098094263</v>
       </c>
       <c r="U49">
-        <v>0.0723732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V49">
         <v>0.21</v>
       </c>
       <c r="W49">
-        <v>0.05717485432680389</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.519549685466113</v>
+        <v>2.617188101628305</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07604975793969425</v>
+        <v>0.07399403207808429</v>
       </c>
       <c r="C50">
-        <v>18901.89205762592</v>
+        <v>21503.36679970219</v>
       </c>
       <c r="D50">
-        <v>35819.45605762592</v>
+        <v>38420.9307997022</v>
       </c>
       <c r="E50">
         <v>-7275.735999999997</v>
@@ -5393,45 +5393,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M50">
-        <v>1427.59740959643</v>
+        <v>1324.91066399643</v>
       </c>
       <c r="N50">
-        <v>1967.70259040357</v>
+        <v>2070.389336003569</v>
       </c>
       <c r="O50">
-        <v>413.2175439847496</v>
+        <v>434.7817605607496</v>
       </c>
       <c r="P50">
-        <v>1554.48504641882</v>
+        <v>1635.60757544282</v>
       </c>
       <c r="Q50">
-        <v>3668.18504641882</v>
+        <v>3749.30757544282</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09150382281313151</v>
+        <v>0.09148835000234314</v>
       </c>
       <c r="T50">
         <v>0.7703712179103932</v>
       </c>
       <c r="U50">
-        <v>0.0750732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V50">
         <v>0.21</v>
       </c>
       <c r="W50">
-        <v>0.05930785432680388</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.378331578060108</v>
+        <v>2.562663349511049</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07612933317500861</v>
+        <v>0.07403096610377831</v>
       </c>
       <c r="C51">
-        <v>18411.74435724244</v>
+        <v>21056.93344072979</v>
       </c>
       <c r="D51">
-        <v>35725.47635724244</v>
+        <v>38370.66544072979</v>
       </c>
       <c r="E51">
         <v>-6879.567999999999</v>
@@ -5475,45 +5475,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M51">
-        <v>1457.339022296355</v>
+        <v>1352.512969496355</v>
       </c>
       <c r="N51">
-        <v>1937.960977703644</v>
+        <v>2042.787030503644</v>
       </c>
       <c r="O51">
-        <v>406.9718053177652</v>
+        <v>428.9852764057652</v>
       </c>
       <c r="P51">
-        <v>1530.989172385879</v>
+        <v>1613.801754097879</v>
       </c>
       <c r="Q51">
-        <v>3644.689172385878</v>
+        <v>3727.501754097879</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09229114618602885</v>
+        <v>0.09227540683067531</v>
       </c>
       <c r="T51">
         <v>0.7836421267389208</v>
       </c>
       <c r="U51">
-        <v>0.0750732333250682</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V51">
         <v>0.21</v>
       </c>
       <c r="W51">
-        <v>0.05930785432680388</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.329794198916024</v>
+        <v>2.510364097480212</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07620890841032298</v>
+        <v>0.07545040012947232</v>
       </c>
       <c r="C52">
-        <v>17922.08851645957</v>
+        <v>18823.87191223552</v>
       </c>
       <c r="D52">
-        <v>35631.98851645957</v>
+        <v>36533.77191223552</v>
       </c>
       <c r="E52">
         <v>-6483.399999999998</v>
@@ -5557,37 +5557,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M52">
-        <v>1487.080634996281</v>
+        <v>1449.444674996281</v>
       </c>
       <c r="N52">
-        <v>1908.219365003718</v>
+        <v>1945.855325003718</v>
       </c>
       <c r="O52">
-        <v>400.7260666507808</v>
+        <v>408.6296182507808</v>
       </c>
       <c r="P52">
-        <v>1507.493298352937</v>
+        <v>1537.225706752937</v>
       </c>
       <c r="Q52">
-        <v>3621.193298352937</v>
+        <v>3650.925706752937</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09310996249384208</v>
+        <v>0.09309394593214078</v>
       </c>
       <c r="T52">
         <v>0.7974438719205894</v>
       </c>
       <c r="U52">
-        <v>0.0750732333250682</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V52">
         <v>0.21</v>
       </c>
       <c r="W52">
-        <v>0.05930785432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.283198314937704</v>
+        <v>2.342483337633229</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07818211364563736</v>
+        <v>0.07551498415516635</v>
       </c>
       <c r="C53">
-        <v>15354.68404144916</v>
+        <v>18348.29959380955</v>
       </c>
       <c r="D53">
-        <v>33460.75204144916</v>
+        <v>36454.36759380955</v>
       </c>
       <c r="E53">
         <v>-6087.231999999996</v>
@@ -5639,45 +5639,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M53">
-        <v>1611.783717296207</v>
+        <v>1478.433568496207</v>
       </c>
       <c r="N53">
-        <v>1783.516282703793</v>
+        <v>1916.866431503792</v>
       </c>
       <c r="O53">
-        <v>374.5384193677964</v>
+        <v>402.5419506157964</v>
       </c>
       <c r="P53">
-        <v>1408.977863335996</v>
+        <v>1514.324480887996</v>
       </c>
       <c r="Q53">
-        <v>3522.677863335996</v>
+        <v>3628.024480887996</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09396219987544363</v>
+        <v>0.09394589479284973</v>
       </c>
       <c r="T53">
         <v>0.8118089536402855</v>
       </c>
       <c r="U53">
-        <v>0.07977323332506819</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V53">
         <v>0.21</v>
       </c>
       <c r="W53">
-        <v>0.06302085432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.106548145116933</v>
+        <v>2.296552291797283</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07829881888095172</v>
+        <v>0.07557956818086037</v>
       </c>
       <c r="C54">
-        <v>14838.35644564669</v>
+        <v>17873.07168941339</v>
       </c>
       <c r="D54">
-        <v>33340.59244564669</v>
+        <v>36375.30768941339</v>
       </c>
       <c r="E54">
         <v>-5691.063999999998</v>
@@ -5721,45 +5721,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M54">
-        <v>1643.387319596132</v>
+        <v>1507.422461996132</v>
       </c>
       <c r="N54">
-        <v>1751.912680403867</v>
+        <v>1887.877538003867</v>
       </c>
       <c r="O54">
-        <v>367.9016628848121</v>
+        <v>396.4542829808121</v>
       </c>
       <c r="P54">
-        <v>1384.011017519055</v>
+        <v>1491.423255023055</v>
       </c>
       <c r="Q54">
-        <v>3497.711017519055</v>
+        <v>3605.123255023055</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09484994714794523</v>
+        <v>0.0948333415227549</v>
       </c>
       <c r="T54">
         <v>0.8267725804316354</v>
       </c>
       <c r="U54">
-        <v>0.07977323332506819</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V54">
         <v>0.21</v>
       </c>
       <c r="W54">
-        <v>0.06302085432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.066037603864685</v>
+        <v>2.252387824647336</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07841552411626609</v>
+        <v>0.07681651220655439</v>
       </c>
       <c r="C55">
-        <v>14322.88876267918</v>
+        <v>16026.24994635025</v>
       </c>
       <c r="D55">
-        <v>33221.29276267918</v>
+        <v>34924.65394635025</v>
       </c>
       <c r="E55">
         <v>-5294.895999999997</v>
@@ -5803,37 +5803,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M55">
-        <v>1674.990921896058</v>
+        <v>1595.202686696058</v>
       </c>
       <c r="N55">
-        <v>1720.309078103941</v>
+        <v>1800.097313303941</v>
       </c>
       <c r="O55">
-        <v>361.2649064018277</v>
+        <v>378.0204357938276</v>
       </c>
       <c r="P55">
-        <v>1359.044171702114</v>
+        <v>1422.076877510114</v>
       </c>
       <c r="Q55">
-        <v>3472.744171702114</v>
+        <v>3535.776877510114</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09577547090012774</v>
+        <v>0.09575855194329433</v>
       </c>
       <c r="T55">
         <v>0.8423729572992129</v>
       </c>
       <c r="U55">
-        <v>0.07977323332506819</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V55">
         <v>0.21</v>
       </c>
       <c r="W55">
-        <v>0.06302085432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.027055762282332</v>
+        <v>2.128444258724423</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08249960935158046</v>
+        <v>0.0769032162322484</v>
       </c>
       <c r="C56">
-        <v>10229.71707061478</v>
+        <v>15532.72519486488</v>
       </c>
       <c r="D56">
-        <v>29524.28907061478</v>
+        <v>34827.29719486488</v>
       </c>
       <c r="E56">
         <v>-4898.727999999996</v>
@@ -5885,45 +5885,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M56">
-        <v>1905.550093795984</v>
+        <v>1625.300850595984</v>
       </c>
       <c r="N56">
-        <v>1489.749906204016</v>
+        <v>1769.999149404016</v>
       </c>
       <c r="O56">
-        <v>312.8474803028433</v>
+        <v>371.6998213748433</v>
       </c>
       <c r="P56">
-        <v>1176.902425901172</v>
+        <v>1398.299328029173</v>
       </c>
       <c r="Q56">
-        <v>3290.602425901172</v>
+        <v>3511.999328029172</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09674123481544862</v>
+        <v>0.09672398890385719</v>
       </c>
       <c r="T56">
         <v>0.8586516114219026</v>
       </c>
       <c r="U56">
-        <v>0.0890732333250682</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V56">
         <v>0.21</v>
       </c>
       <c r="W56">
-        <v>0.07036785432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.781795194497529</v>
+        <v>2.089028624303601</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08473193458689485</v>
+        <v>0.07698992025794243</v>
       </c>
       <c r="C57">
-        <v>8140.650522253512</v>
+        <v>15039.74172224217</v>
       </c>
       <c r="D57">
-        <v>27831.39052225351</v>
+        <v>34730.48172224217</v>
       </c>
       <c r="E57">
         <v>-4502.559999999998</v>
@@ -5967,45 +5967,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M57">
-        <v>2043.247486495909</v>
+        <v>1655.399014495909</v>
       </c>
       <c r="N57">
-        <v>1352.05251350409</v>
+        <v>1739.90098550409</v>
       </c>
       <c r="O57">
-        <v>283.9310278358589</v>
+        <v>365.3792069558589</v>
       </c>
       <c r="P57">
-        <v>1068.121485668231</v>
+        <v>1374.521778548231</v>
       </c>
       <c r="Q57">
-        <v>3181.821485668231</v>
+        <v>3488.221778548231</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09774992157145045</v>
+        <v>0.09773233417377844</v>
       </c>
       <c r="T57">
         <v>0.8756537612833786</v>
       </c>
       <c r="U57">
-        <v>0.09377323332506821</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V57">
         <v>0.21</v>
       </c>
       <c r="W57">
-        <v>0.07408085432680389</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.661717448542079</v>
+        <v>2.051046285679899</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08495923982220921</v>
+        <v>0.07707662428363644</v>
       </c>
       <c r="C58">
-        <v>7582.931358326194</v>
+        <v>14547.29502693597</v>
       </c>
       <c r="D58">
-        <v>27669.8393583262</v>
+        <v>34634.20302693597</v>
       </c>
       <c r="E58">
         <v>-4106.391999999996</v>
@@ -6049,45 +6049,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M58">
-        <v>2080.397440795835</v>
+        <v>1685.497178395835</v>
       </c>
       <c r="N58">
-        <v>1314.902559204164</v>
+        <v>1709.802821604165</v>
       </c>
       <c r="O58">
-        <v>276.1295374328745</v>
+        <v>359.0585925368745</v>
       </c>
       <c r="P58">
-        <v>1038.77302177129</v>
+        <v>1350.74422906729</v>
       </c>
       <c r="Q58">
-        <v>3152.473021771289</v>
+        <v>3464.44422906729</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09880445772545235</v>
+        <v>0.09878651331960517</v>
       </c>
       <c r="T58">
         <v>0.8934287361385579</v>
       </c>
       <c r="U58">
-        <v>0.09377323332506821</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V58">
         <v>0.21</v>
       </c>
       <c r="W58">
-        <v>0.07408085432680389</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.632043922675257</v>
+        <v>2.014420459149901</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08518654505752357</v>
+        <v>0.08067566830933047</v>
       </c>
       <c r="C59">
-        <v>7027.076862918453</v>
+        <v>10577.00135332359</v>
       </c>
       <c r="D59">
-        <v>27510.15286291846</v>
+        <v>31060.07735332359</v>
       </c>
       <c r="E59">
         <v>-3710.223999999995</v>
@@ -6131,45 +6131,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M59">
-        <v>2117.547395095761</v>
+        <v>1891.731635095761</v>
       </c>
       <c r="N59">
-        <v>1277.752604904239</v>
+        <v>1503.568364904239</v>
       </c>
       <c r="O59">
-        <v>268.3280470298901</v>
+        <v>315.7493566298901</v>
       </c>
       <c r="P59">
-        <v>1009.424557874348</v>
+        <v>1187.819008274349</v>
       </c>
       <c r="Q59">
-        <v>3123.124557874348</v>
+        <v>3301.519008274348</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09990804207266363</v>
+        <v>0.09988972405360991</v>
       </c>
       <c r="T59">
         <v>0.9120304540102573</v>
       </c>
       <c r="U59">
-        <v>0.09377323332506821</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V59">
         <v>0.21</v>
       </c>
       <c r="W59">
-        <v>0.07408085432680389</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.603411573154638</v>
+        <v>1.794810604744223</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08541385029283793</v>
+        <v>0.08082399233502446</v>
       </c>
       <c r="C60">
-        <v>6473.054937490506</v>
+        <v>10049.29621537131</v>
       </c>
       <c r="D60">
-        <v>27352.2989374905</v>
+        <v>30928.5402153713</v>
       </c>
       <c r="E60">
         <v>-3314.056</v>
@@ -6213,45 +6213,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M60">
-        <v>2154.697349395686</v>
+        <v>1924.919909395686</v>
       </c>
       <c r="N60">
-        <v>1240.602650604314</v>
+        <v>1470.380090604314</v>
       </c>
       <c r="O60">
-        <v>260.5265566269059</v>
+        <v>308.7798190269058</v>
       </c>
       <c r="P60">
-        <v>980.0760939774077</v>
+        <v>1161.600271577408</v>
       </c>
       <c r="Q60">
-        <v>3093.776093977408</v>
+        <v>3275.300271577407</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1010641780554564</v>
+        <v>0.101045468632091</v>
       </c>
       <c r="T60">
         <v>0.9315179679710849</v>
       </c>
       <c r="U60">
-        <v>0.09377323332506821</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V60">
         <v>0.21</v>
       </c>
       <c r="W60">
-        <v>0.07408085432680389</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.575766546031283</v>
+        <v>1.763865594317599</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08564115552815232</v>
+        <v>0.0827901063607185</v>
       </c>
       <c r="C61">
-        <v>5920.834216028084</v>
+        <v>8009.201157722735</v>
       </c>
       <c r="D61">
-        <v>27196.24621602808</v>
+        <v>29284.61315772274</v>
       </c>
       <c r="E61">
         <v>-2917.887999999999</v>
@@ -6295,37 +6295,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M61">
-        <v>2191.847303695612</v>
+        <v>2049.266440495611</v>
       </c>
       <c r="N61">
-        <v>1203.452696304388</v>
+        <v>1346.033559504388</v>
       </c>
       <c r="O61">
-        <v>252.7250662239214</v>
+        <v>282.6670474959215</v>
       </c>
       <c r="P61">
-        <v>950.7276300804663</v>
+        <v>1063.366512008467</v>
       </c>
       <c r="Q61">
-        <v>3064.427630080466</v>
+        <v>3177.066512008466</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1022767109154586</v>
+        <v>0.1022575909948883</v>
       </c>
       <c r="T61">
         <v>0.9519560923690262</v>
       </c>
       <c r="U61">
-        <v>0.09377323332506821</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V61">
         <v>0.21</v>
       </c>
       <c r="W61">
-        <v>0.07408085432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.54905863847143</v>
+        <v>1.656836774811406</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08586846076346669</v>
+        <v>0.08296924038641251</v>
       </c>
       <c r="C62">
-        <v>5370.384044264745</v>
+        <v>7471.898429347912</v>
       </c>
       <c r="D62">
-        <v>27041.96404426475</v>
+        <v>29143.47842934791</v>
       </c>
       <c r="E62">
         <v>-2521.719999999998</v>
@@ -6377,37 +6377,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M62">
-        <v>2228.997257995537</v>
+        <v>2083.999769995537</v>
       </c>
       <c r="N62">
-        <v>1166.302742004462</v>
+        <v>1311.300230004462</v>
       </c>
       <c r="O62">
-        <v>244.923575820937</v>
+        <v>275.3730483009371</v>
       </c>
       <c r="P62">
-        <v>921.3791661835248</v>
+        <v>1035.927181703525</v>
       </c>
       <c r="Q62">
-        <v>3035.079166183525</v>
+        <v>3149.627181703525</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1035498704184609</v>
+        <v>0.1035303194758255</v>
       </c>
       <c r="T62">
         <v>0.9734161229868645</v>
       </c>
       <c r="U62">
-        <v>0.09377323332506821</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V62">
         <v>0.21</v>
       </c>
       <c r="W62">
-        <v>0.07408085432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.523240994496906</v>
+        <v>1.629222828564549</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09395073599878105</v>
+        <v>0.08314837441210654</v>
       </c>
       <c r="C63">
-        <v>435.1245480360012</v>
+        <v>6935.949550100766</v>
       </c>
       <c r="D63">
-        <v>22502.872548036</v>
+        <v>29003.69755010077</v>
       </c>
       <c r="E63">
         <v>-2125.552</v>
@@ -6459,45 +6459,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M63">
-        <v>2660.057054695463</v>
+        <v>2118.733099495463</v>
       </c>
       <c r="N63">
-        <v>735.2429453045361</v>
+        <v>1276.566900504537</v>
       </c>
       <c r="O63">
-        <v>154.4010185139526</v>
+        <v>268.0790491059527</v>
       </c>
       <c r="P63">
-        <v>580.8419267905836</v>
+        <v>1008.487851398584</v>
       </c>
       <c r="Q63">
-        <v>2694.541926790584</v>
+        <v>3122.187851398584</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1048883201523864</v>
+        <v>0.1048683160839902</v>
       </c>
       <c r="T63">
         <v>0.9959766679953616</v>
       </c>
       <c r="U63">
-        <v>0.1100732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V63">
         <v>0.21</v>
       </c>
       <c r="W63">
-        <v>0.08695785432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.276401193728798</v>
+        <v>1.602514257604475</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09430681123409543</v>
+        <v>0.08332750843780055</v>
       </c>
       <c r="C64">
-        <v>-126.2308851086273</v>
+        <v>6401.335132567543</v>
       </c>
       <c r="D64">
-        <v>22337.68511489137</v>
+        <v>28865.25113256754</v>
       </c>
       <c r="E64">
         <v>-1729.383999999998</v>
@@ -6541,45 +6541,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M64">
-        <v>2703.664547395389</v>
+        <v>2153.466428995388</v>
       </c>
       <c r="N64">
-        <v>691.6354526046102</v>
+        <v>1241.833571004611</v>
       </c>
       <c r="O64">
-        <v>145.2434450469681</v>
+        <v>260.7850499109683</v>
       </c>
       <c r="P64">
-        <v>546.392007557642</v>
+        <v>981.0485210936425</v>
       </c>
       <c r="Q64">
-        <v>2660.092007557642</v>
+        <v>3094.748521093642</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.10629721460915</v>
+        <v>0.1062767335662688</v>
       </c>
       <c r="T64">
         <v>1.019724610109569</v>
       </c>
       <c r="U64">
-        <v>0.1100732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V64">
         <v>0.21</v>
       </c>
       <c r="W64">
-        <v>0.08695785432680389</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.255814077700914</v>
+        <v>1.576667253449564</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1119938023278742</v>
+        <v>0.08350664246349457</v>
       </c>
       <c r="C65">
-        <v>-6491.030747737674</v>
+        <v>5868.036157751852</v>
       </c>
       <c r="D65">
-        <v>16369.05325226233</v>
+        <v>28728.12015775186</v>
       </c>
       <c r="E65">
         <v>-1333.215999999997</v>
@@ -6623,45 +6623,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M65">
-        <v>3563.417736895314</v>
+        <v>2188.199758495314</v>
       </c>
       <c r="N65">
-        <v>-168.1177368953149</v>
+        <v>1207.100241504685</v>
       </c>
       <c r="O65">
-        <v>-35.30472474801613</v>
+        <v>253.4910507159838</v>
       </c>
       <c r="P65">
-        <v>-132.8130121472988</v>
+        <v>953.6091907887012</v>
       </c>
       <c r="Q65">
-        <v>1980.886987852701</v>
+        <v>3067.309190788701</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1082281316612889</v>
+        <v>0.1077612817232652</v>
       </c>
       <c r="T65">
-        <v>1.052271623238475</v>
+        <v>1.04475622477049</v>
       </c>
       <c r="U65">
-        <v>0.1427732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V65">
-        <v>0.2000924541115474</v>
+        <v>0.21</v>
       </c>
       <c r="W65">
-        <v>0.1142053866876147</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.9528212100549878</v>
+        <v>1.551640789109094</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1129635346611249</v>
+        <v>0.0836857764891886</v>
       </c>
       <c r="C66">
-        <v>-7123.541285150448</v>
+        <v>5336.033966364794</v>
       </c>
       <c r="D66">
-        <v>16132.71071484956</v>
+        <v>28592.2859663648</v>
       </c>
       <c r="E66">
         <v>-937.0479999999952</v>
@@ -6705,45 +6705,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M66">
-        <v>3619.97992319524</v>
+        <v>2222.93308799524</v>
       </c>
       <c r="N66">
-        <v>-224.6799231952409</v>
+        <v>1172.366912004759</v>
       </c>
       <c r="O66">
-        <v>-47.18278387100059</v>
+        <v>246.1970515209995</v>
       </c>
       <c r="P66">
-        <v>-177.4971393242403</v>
+        <v>926.1698604837599</v>
       </c>
       <c r="Q66">
-        <v>1936.202860675759</v>
+        <v>3039.86986048376</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1099622464296581</v>
+        <v>0.1093283047778725</v>
       </c>
       <c r="T66">
-        <v>1.081501390550655</v>
+        <v>1.071178484690351</v>
       </c>
       <c r="U66">
-        <v>0.1427732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V66">
-        <v>0.1969660095160545</v>
+        <v>0.21</v>
       </c>
       <c r="W66">
-        <v>0.1146517592913249</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.9379333786478785</v>
+        <v>1.527396401779265</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1139332669943755</v>
+        <v>0.08386491051488261</v>
       </c>
       <c r="C67">
-        <v>-7749.324154557198</v>
+        <v>4805.310250361028</v>
       </c>
       <c r="D67">
-        <v>15903.0958454428</v>
+        <v>28457.73025036103</v>
       </c>
       <c r="E67">
         <v>-540.8799999999974</v>
@@ -6787,45 +6787,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M67">
-        <v>3676.542109495165</v>
+        <v>2257.666417495165</v>
       </c>
       <c r="N67">
-        <v>-281.242109495166</v>
+        <v>1137.633582504834</v>
       </c>
       <c r="O67">
-        <v>-59.06084299398486</v>
+        <v>238.9030523260151</v>
       </c>
       <c r="P67">
-        <v>-222.1812665011811</v>
+        <v>898.730530178819</v>
       </c>
       <c r="Q67">
-        <v>1891.518733498819</v>
+        <v>3012.430530178819</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1117954534705055</v>
+        <v>0.1109848720070288</v>
       </c>
       <c r="T67">
-        <v>1.112401430280674</v>
+        <v>1.099110588034204</v>
       </c>
       <c r="U67">
-        <v>0.1427732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V67">
-        <v>0.1939357632158075</v>
+        <v>0.21</v>
       </c>
       <c r="W67">
-        <v>0.1150843973533825</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.9235036343609881</v>
+        <v>1.503897995598046</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1149029993276262</v>
+        <v>0.09144792454057663</v>
       </c>
       <c r="C68">
-        <v>-8368.662586957598</v>
+        <v>-318.2439298383215</v>
       </c>
       <c r="D68">
-        <v>15679.92541304241</v>
+        <v>23730.34407016168</v>
       </c>
       <c r="E68">
         <v>-144.7119999999959</v>
@@ -6869,45 +6869,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M68">
-        <v>3733.104295795091</v>
+        <v>2663.688396595091</v>
       </c>
       <c r="N68">
-        <v>-337.804295795092</v>
+        <v>731.6116034049082</v>
       </c>
       <c r="O68">
-        <v>-70.93890211696932</v>
+        <v>153.6384367150307</v>
       </c>
       <c r="P68">
-        <v>-266.8653936781227</v>
+        <v>577.9731666898775</v>
       </c>
       <c r="Q68">
-        <v>1846.834606321877</v>
+        <v>2691.673166689877</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.113736496219638</v>
+        <v>0.112738884367312</v>
       </c>
       <c r="T68">
-        <v>1.145119119406576</v>
+        <v>1.128685756280637</v>
       </c>
       <c r="U68">
-        <v>0.1427732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V68">
-        <v>0.1909973425610225</v>
+        <v>0.21</v>
       </c>
       <c r="W68">
-        <v>0.1155039251711353</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.9095111550524883</v>
+        <v>1.274661106884763</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1158727316608769</v>
+        <v>0.09173923856627066</v>
       </c>
       <c r="C69">
-        <v>-8981.824134883969</v>
+        <v>-864.8929190304007</v>
       </c>
       <c r="D69">
-        <v>15462.93186511603</v>
+        <v>23579.8630809696</v>
       </c>
       <c r="E69">
         <v>251.4560000000056</v>
@@ -6951,45 +6951,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M69">
-        <v>3789.666482095017</v>
+        <v>2704.047311695017</v>
       </c>
       <c r="N69">
-        <v>-394.3664820950175</v>
+        <v>691.2526883049823</v>
       </c>
       <c r="O69">
-        <v>-82.81696123995368</v>
+        <v>145.1630645440463</v>
       </c>
       <c r="P69">
-        <v>-311.5495208550639</v>
+        <v>546.089623760936</v>
       </c>
       <c r="Q69">
-        <v>1802.150479144936</v>
+        <v>2659.789623760936</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1157951779232634</v>
+        <v>0.1145992005070062</v>
       </c>
       <c r="T69">
-        <v>1.179819698782533</v>
+        <v>1.160053358966248</v>
       </c>
       <c r="U69">
-        <v>0.1427732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V69">
-        <v>0.1881466359556341</v>
+        <v>0.21</v>
       </c>
       <c r="W69">
-        <v>0.1159109297704478</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8959363616934959</v>
+        <v>1.255636314244692</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1168424639941276</v>
+        <v>0.108156660175534</v>
       </c>
       <c r="C70">
-        <v>-9589.061742459726</v>
+        <v>-7469.227818913067</v>
       </c>
       <c r="D70">
-        <v>15251.86225754028</v>
+        <v>17371.69618108694</v>
       </c>
       <c r="E70">
         <v>647.6240000000034</v>
@@ -7033,37 +7033,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M70">
-        <v>3846.228668394942</v>
+        <v>3514.873753194943</v>
       </c>
       <c r="N70">
-        <v>-450.9286683949431</v>
+        <v>-119.5737531949435</v>
       </c>
       <c r="O70">
-        <v>-94.69502036293804</v>
+        <v>-25.11048817093813</v>
       </c>
       <c r="P70">
-        <v>-356.233648032005</v>
+        <v>-94.46326502400535</v>
       </c>
       <c r="Q70">
-        <v>1757.466351967995</v>
+        <v>2019.236734975995</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1179825272333653</v>
+        <v>0.1169768903002604</v>
       </c>
       <c r="T70">
-        <v>1.216689064369487</v>
+        <v>1.20014462472105</v>
       </c>
       <c r="U70">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V70">
-        <v>0.1853797736621689</v>
+        <v>0.2028559345415711</v>
       </c>
       <c r="W70">
-        <v>0.116305963646251</v>
+        <v>0.104005963646251</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8827608269627092</v>
+        <v>0.9659806406741483</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1178121963273783</v>
+        <v>0.1090033925087847</v>
       </c>
       <c r="C71">
-        <v>-10190.61472899983</v>
+        <v>-8098.123466212852</v>
       </c>
       <c r="D71">
-        <v>15046.47727100017</v>
+        <v>17138.96853378715</v>
       </c>
       <c r="E71">
         <v>1043.792000000005</v>
@@ -7115,37 +7115,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M71">
-        <v>3902.790854694868</v>
+        <v>3566.563073094869</v>
       </c>
       <c r="N71">
-        <v>-507.4908546948686</v>
+        <v>-171.2630730948695</v>
       </c>
       <c r="O71">
-        <v>-106.5730794859224</v>
+        <v>-35.96524534992259</v>
       </c>
       <c r="P71">
-        <v>-400.9177752089462</v>
+        <v>-135.2978277449469</v>
       </c>
       <c r="Q71">
-        <v>1712.782224791054</v>
+        <v>1978.402172255053</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1203109958537965</v>
+        <v>0.1192729190196237</v>
       </c>
       <c r="T71">
-        <v>1.255937098703987</v>
+        <v>1.238858967453987</v>
       </c>
       <c r="U71">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V71">
-        <v>0.1826931102757607</v>
+        <v>0.1999159934612585</v>
       </c>
       <c r="W71">
-        <v>0.1166895472647846</v>
+        <v>0.1043895472647846</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8699671917893367</v>
+        <v>0.9519809212440882</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.118781928660629</v>
+        <v>0.1098501248420354</v>
       </c>
       <c r="C72">
-        <v>-10786.70969419501</v>
+        <v>-8720.865869493315</v>
       </c>
       <c r="D72">
-        <v>14846.55030580499</v>
+        <v>16912.39413050669</v>
       </c>
       <c r="E72">
         <v>1439.960000000006</v>
@@ -7197,37 +7197,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M72">
-        <v>3959.353040994794</v>
+        <v>3618.252392994795</v>
       </c>
       <c r="N72">
-        <v>-564.0530409947946</v>
+        <v>-222.9523929947954</v>
       </c>
       <c r="O72">
-        <v>-118.4511386089069</v>
+        <v>-46.82000252890704</v>
       </c>
       <c r="P72">
-        <v>-445.6019023858877</v>
+        <v>-176.1323904658884</v>
       </c>
       <c r="Q72">
-        <v>1668.098097614112</v>
+        <v>1937.567609534111</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1227946957155897</v>
+        <v>0.1217220163202778</v>
       </c>
       <c r="T72">
-        <v>1.297801668660786</v>
+        <v>1.28015426636912</v>
       </c>
       <c r="U72">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V72">
-        <v>0.1800832087003927</v>
+        <v>0.1970600506975262</v>
       </c>
       <c r="W72">
-        <v>0.1170621713513601</v>
+        <v>0.1047621713513601</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8575390890494889</v>
+        <v>0.938381193797744</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1197516609938796</v>
+        <v>0.1106968571752861</v>
       </c>
       <c r="C73">
-        <v>-11377.56135207746</v>
+        <v>-9337.695879431631</v>
       </c>
       <c r="D73">
-        <v>14651.86664792254</v>
+        <v>16691.73212056837</v>
       </c>
       <c r="E73">
         <v>1836.128000000001</v>
@@ -7279,37 +7279,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M73">
-        <v>4015.915227294719</v>
+        <v>3669.941712894719</v>
       </c>
       <c r="N73">
-        <v>-620.6152272947193</v>
+        <v>-274.6417128947201</v>
       </c>
       <c r="O73">
-        <v>-130.329197731891</v>
+        <v>-57.67475970789121</v>
       </c>
       <c r="P73">
-        <v>-490.2860295628282</v>
+        <v>-216.9669531868288</v>
       </c>
       <c r="Q73">
-        <v>1623.413970437172</v>
+        <v>1896.733046813171</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1254496852230238</v>
+        <v>0.124340016883046</v>
       </c>
       <c r="T73">
-        <v>1.342553450338744</v>
+        <v>1.324297516933572</v>
       </c>
       <c r="U73">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V73">
-        <v>0.1775468254792604</v>
+        <v>0.1942845570257301</v>
       </c>
       <c r="W73">
-        <v>0.1174242989847926</v>
+        <v>0.1051242989847926</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.845461073710764</v>
+        <v>0.9251645572653816</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1207213933271303</v>
+        <v>0.1115435895085368</v>
       </c>
       <c r="C74">
-        <v>-11963.37330022095</v>
+        <v>-9948.841938738984</v>
       </c>
       <c r="D74">
-        <v>14462.22269977905</v>
+        <v>16476.75406126102</v>
       </c>
       <c r="E74">
         <v>2232.296000000002</v>
@@ -7361,37 +7361,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M74">
-        <v>4072.477413594645</v>
+        <v>3721.631032794645</v>
       </c>
       <c r="N74">
-        <v>-677.1774135946453</v>
+        <v>-326.331032794646</v>
       </c>
       <c r="O74">
-        <v>-142.2072568548755</v>
+        <v>-68.52951688687567</v>
       </c>
       <c r="P74">
-        <v>-534.9701567397698</v>
+        <v>-257.8015159077704</v>
       </c>
       <c r="Q74">
-        <v>1578.72984326023</v>
+        <v>1855.898484092229</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1282943168381318</v>
+        <v>0.1271450174860119</v>
       </c>
       <c r="T74">
-        <v>1.390501787850842</v>
+        <v>1.371593856824057</v>
       </c>
       <c r="U74">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V74">
-        <v>0.175080897347604</v>
+        <v>0.1915861604003728</v>
       </c>
       <c r="W74">
-        <v>0.1177763675172964</v>
+        <v>0.1054763675172964</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8337185587981144</v>
+        <v>0.9123150495255845</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.121691125660381</v>
+        <v>0.1123903218417875</v>
       </c>
       <c r="C75">
-        <v>-12544.33872996798</v>
+        <v>-10554.52087103087</v>
       </c>
       <c r="D75">
-        <v>14277.42527003202</v>
+        <v>16267.24312896913</v>
       </c>
       <c r="E75">
         <v>2628.464000000004</v>
@@ -7443,37 +7443,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M75">
-        <v>4129.039599894571</v>
+        <v>3773.320352694571</v>
       </c>
       <c r="N75">
-        <v>-733.7395998945713</v>
+        <v>-378.0203526945716</v>
       </c>
       <c r="O75">
-        <v>-154.0853159778599</v>
+        <v>-79.38427406586003</v>
       </c>
       <c r="P75">
-        <v>-579.6542839167113</v>
+        <v>-298.6360786287115</v>
       </c>
       <c r="Q75">
-        <v>1534.045716083288</v>
+        <v>1815.063921371288</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1313496619062108</v>
+        <v>0.1301577959114197</v>
       </c>
       <c r="T75">
-        <v>1.44200185406754</v>
+        <v>1.422393629299022</v>
       </c>
       <c r="U75">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V75">
-        <v>0.1726825288907875</v>
+        <v>0.1889616924496827</v>
       </c>
       <c r="W75">
-        <v>0.118118790336581</v>
+        <v>0.105818790336581</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8222977566227976</v>
+        <v>0.8998175830937273</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1226608579936317</v>
+        <v>0.1132370541750381</v>
       </c>
       <c r="C76">
-        <v>-13120.64108289269</v>
+        <v>-11154.93861026764</v>
       </c>
       <c r="D76">
-        <v>14097.29091710731</v>
+        <v>16062.99338973236</v>
       </c>
       <c r="E76">
         <v>3024.632000000001</v>
@@ -7525,37 +7525,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M76">
-        <v>4185.601786194496</v>
+        <v>3825.009672594496</v>
       </c>
       <c r="N76">
-        <v>-790.3017861944963</v>
+        <v>-429.7096725944971</v>
       </c>
       <c r="O76">
-        <v>-165.9633751008442</v>
+        <v>-90.23903124484438</v>
       </c>
       <c r="P76">
-        <v>-624.3384110936521</v>
+        <v>-339.4706413496527</v>
       </c>
       <c r="Q76">
-        <v>1489.361588906348</v>
+        <v>1774.229358650347</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1346400335179881</v>
+        <v>0.1334023265233975</v>
       </c>
       <c r="T76">
-        <v>1.497463463839368</v>
+        <v>1.477101076579754</v>
       </c>
       <c r="U76">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V76">
-        <v>0.1703489812030742</v>
+        <v>0.1864081560652276</v>
       </c>
       <c r="W76">
-        <v>0.118451958485074</v>
+        <v>0.1061519584850741</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8111856247765437</v>
+        <v>0.8876578860248932</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1236305903268824</v>
+        <v>0.1140837865082888</v>
       </c>
       <c r="C77">
-        <v>-13692.45465818828</v>
+        <v>-11750.29087592385</v>
       </c>
       <c r="D77">
-        <v>13921.64534181173</v>
+        <v>15863.80912407616</v>
       </c>
       <c r="E77">
         <v>3420.800000000003</v>
@@ -7607,37 +7607,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M77">
-        <v>4242.163972494422</v>
+        <v>3876.698992494422</v>
       </c>
       <c r="N77">
-        <v>-846.8639724944223</v>
+        <v>-481.3989924944231</v>
       </c>
       <c r="O77">
-        <v>-177.8414342238287</v>
+        <v>-101.0937884238288</v>
       </c>
       <c r="P77">
-        <v>-669.0225382705937</v>
+        <v>-380.3052040705942</v>
       </c>
       <c r="Q77">
-        <v>1444.677461729406</v>
+        <v>1733.394795929406</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1381936348587076</v>
+        <v>0.1369064195843334</v>
       </c>
       <c r="T77">
-        <v>1.557362002392943</v>
+        <v>1.536185119642944</v>
       </c>
       <c r="U77">
-        <v>0.1427732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V77">
-        <v>0.1680776614536998</v>
+        <v>0.1839227139843578</v>
       </c>
       <c r="W77">
-        <v>0.1187762421496073</v>
+        <v>0.1064762421496073</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8003698164461898</v>
+        <v>0.8758224475445612</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.190366737265134</v>
+        <v>0.1149305188415395</v>
       </c>
       <c r="C78">
-        <v>-20515.25292410799</v>
+        <v>-12340.76379853932</v>
       </c>
       <c r="D78">
-        <v>7495.01507589201</v>
+        <v>15669.50420146068</v>
       </c>
       <c r="E78">
         <v>3816.968000000004</v>
@@ -7689,45 +7689,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M78">
-        <v>6854.960561994349</v>
+        <v>3928.388312394348</v>
       </c>
       <c r="N78">
-        <v>-3459.660561994349</v>
+        <v>-533.0883123943486</v>
       </c>
       <c r="O78">
-        <v>-726.5287180188134</v>
+        <v>-111.9485456028132</v>
       </c>
       <c r="P78">
-        <v>-2733.131843975536</v>
+        <v>-421.1397667915354</v>
       </c>
       <c r="Q78">
-        <v>-619.4318439755361</v>
+        <v>1692.560233208465</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1472200971653244</v>
+        <v>0.1407025204003473</v>
       </c>
       <c r="T78">
-        <v>1.709509598207898</v>
+        <v>1.6001928329614</v>
       </c>
       <c r="U78">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V78">
-        <v>0.1040141651511645</v>
+        <v>0.1815026782740373</v>
       </c>
       <c r="W78">
-        <v>0.2039919920334949</v>
+        <v>0.106791992033495</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4953055483388787</v>
+        <v>0.8642984679716064</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1921854695983847</v>
+        <v>0.1157772511747902</v>
       </c>
       <c r="C79">
-        <v>-21004.54100149084</v>
+        <v>-12926.53449985497</v>
       </c>
       <c r="D79">
-        <v>7401.894998509161</v>
+        <v>15479.90150014504</v>
       </c>
       <c r="E79">
         <v>4213.136000000002</v>
@@ -7771,45 +7771,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M79">
-        <v>6945.157411494274</v>
+        <v>3980.077632294273</v>
       </c>
       <c r="N79">
-        <v>-3549.857411494275</v>
+        <v>-584.7776322942741</v>
       </c>
       <c r="O79">
-        <v>-745.4700564137977</v>
+        <v>-122.8033027817976</v>
       </c>
       <c r="P79">
-        <v>-2804.387355080477</v>
+        <v>-461.9743295124765</v>
       </c>
       <c r="Q79">
-        <v>-690.6873550804776</v>
+        <v>1651.725670487523</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.151629666607295</v>
+        <v>0.1448287169394928</v>
       </c>
       <c r="T79">
-        <v>1.783836102477806</v>
+        <v>1.669766434394504</v>
       </c>
       <c r="U79">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V79">
-        <v>0.1026633318375131</v>
+        <v>0.1791455006341148</v>
       </c>
       <c r="W79">
-        <v>0.2042995406216972</v>
+        <v>0.1070995406216972</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4888730087500621</v>
+        <v>0.8530738125434038</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1940042019316354</v>
+        <v>0.1166239835080409</v>
       </c>
       <c r="C80">
-        <v>-21491.5435769324</v>
+        <v>-13507.77163133386</v>
       </c>
       <c r="D80">
-        <v>7311.060423067602</v>
+        <v>15294.83236866614</v>
       </c>
       <c r="E80">
         <v>4609.304000000004</v>
@@ -7853,45 +7853,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M80">
-        <v>7035.3542609942</v>
+        <v>4031.766952194199</v>
       </c>
       <c r="N80">
-        <v>-3640.0542609942</v>
+        <v>-636.4669521942001</v>
       </c>
       <c r="O80">
-        <v>-764.411394808782</v>
+        <v>-133.658059960782</v>
       </c>
       <c r="P80">
-        <v>-2875.642866185418</v>
+        <v>-502.8088922334181</v>
       </c>
       <c r="Q80">
-        <v>-761.9428661854186</v>
+        <v>1610.891107766582</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1564401059985357</v>
+        <v>0.1493300222549243</v>
       </c>
       <c r="T80">
-        <v>1.864919561681343</v>
+        <v>1.745664908685163</v>
       </c>
       <c r="U80">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V80">
-        <v>0.1013471352754937</v>
+        <v>0.1768487634464979</v>
       </c>
       <c r="W80">
-        <v>0.2045992033486635</v>
+        <v>0.1073992033486635</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4826054060737793</v>
+        <v>0.8421369687928473</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1958229342648861</v>
+        <v>0.1174707158412915</v>
       </c>
       <c r="C81">
-        <v>-21976.34377204935</v>
+        <v>-14084.63587450906</v>
       </c>
       <c r="D81">
-        <v>7222.428227950655</v>
+        <v>15114.13612549094</v>
       </c>
       <c r="E81">
         <v>5005.472000000005</v>
@@ -7935,45 +7935,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M81">
-        <v>7125.551110494126</v>
+        <v>4083.456272094125</v>
       </c>
       <c r="N81">
-        <v>-3730.251110494127</v>
+        <v>-688.1562720941256</v>
       </c>
       <c r="O81">
-        <v>-783.3527332037665</v>
+        <v>-144.5128171397664</v>
       </c>
       <c r="P81">
-        <v>-2946.89837729036</v>
+        <v>-543.6434549543592</v>
       </c>
       <c r="Q81">
-        <v>-833.1983772903604</v>
+        <v>1570.056545045641</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1617086824746565</v>
+        <v>0.1542600233146826</v>
       </c>
       <c r="T81">
-        <v>1.953725255094741</v>
+        <v>1.828791809098743</v>
       </c>
       <c r="U81">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V81">
-        <v>0.1000642601454241</v>
+        <v>0.1746101715041372</v>
       </c>
       <c r="W81">
-        <v>0.2048912796774787</v>
+        <v>0.1076912796774788</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4764964768829719</v>
+        <v>0.831477007162558</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1976416665981368</v>
+        <v>0.1183174481745422</v>
       </c>
       <c r="C82">
-        <v>-22459.02072599491</v>
+        <v>-14657.28040627839</v>
       </c>
       <c r="D82">
-        <v>7135.919274005089</v>
+        <v>14937.65959372161</v>
       </c>
       <c r="E82">
         <v>5401.640000000003</v>
@@ -8017,45 +8017,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M82">
-        <v>7215.747959994051</v>
+        <v>4135.14559199405</v>
       </c>
       <c r="N82">
-        <v>-3820.447959994051</v>
+        <v>-739.8455919940507</v>
       </c>
       <c r="O82">
-        <v>-802.2940715987507</v>
+        <v>-155.3675743187506</v>
       </c>
       <c r="P82">
-        <v>-3018.153888395301</v>
+        <v>-584.4780176753001</v>
       </c>
       <c r="Q82">
-        <v>-904.453888395301</v>
+        <v>1529.2219823247</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1675041165983893</v>
+        <v>0.1596830244804167</v>
       </c>
       <c r="T82">
-        <v>2.051411517849478</v>
+        <v>1.92023139955368</v>
       </c>
       <c r="U82">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V82">
-        <v>0.09881345689360631</v>
+        <v>0.1724275443603355</v>
       </c>
       <c r="W82">
-        <v>0.2051760540980736</v>
+        <v>0.1079760540980736</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4705402709219348</v>
+        <v>0.8210835445730262</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1994603989313875</v>
+        <v>0.1191641805077929</v>
       </c>
       <c r="C83">
-        <v>-22939.64983114208</v>
+        <v>-15225.85133197798</v>
       </c>
       <c r="D83">
-        <v>7051.458168857919</v>
+        <v>14765.25666802202</v>
       </c>
       <c r="E83">
         <v>5797.808000000005</v>
@@ -8099,45 +8099,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M83">
-        <v>7305.944809493977</v>
+        <v>4186.834911893976</v>
       </c>
       <c r="N83">
-        <v>-3910.644809493978</v>
+        <v>-791.5349118939766</v>
       </c>
       <c r="O83">
-        <v>-821.2354099937353</v>
+        <v>-166.2223314977351</v>
       </c>
       <c r="P83">
-        <v>-3089.409399500243</v>
+        <v>-625.3125803962415</v>
       </c>
       <c r="Q83">
-        <v>-975.7093995002429</v>
+        <v>1488.387419603758</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1739095964193572</v>
+        <v>0.1656768678741229</v>
       </c>
       <c r="T83">
-        <v>2.159380545104714</v>
+        <v>2.021296210056506</v>
       </c>
       <c r="U83">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V83">
-        <v>0.09759353767269757</v>
+        <v>0.1702988092447758</v>
       </c>
       <c r="W83">
-        <v>0.2054537970514933</v>
+        <v>0.1082537970514933</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.4647311317747504</v>
+        <v>0.8109467106894085</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2012791312646381</v>
+        <v>0.1200109128410436</v>
       </c>
       <c r="C84">
-        <v>-23418.30295222524</v>
+        <v>-15790.48808880811</v>
       </c>
       <c r="D84">
-        <v>6968.97304777477</v>
+        <v>14596.7879111919</v>
       </c>
       <c r="E84">
         <v>6193.976000000006</v>
@@ -8181,45 +8181,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M84">
-        <v>7396.141658993903</v>
+        <v>4238.524231793902</v>
       </c>
       <c r="N84">
-        <v>-4000.841658993903</v>
+        <v>-843.2242317939026</v>
       </c>
       <c r="O84">
-        <v>-840.1767483887197</v>
+        <v>-177.0770886767195</v>
       </c>
       <c r="P84">
-        <v>-3160.664910605184</v>
+        <v>-666.1471431171831</v>
       </c>
       <c r="Q84">
-        <v>-1046.964910605184</v>
+        <v>1447.552856882817</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1810267962204326</v>
+        <v>0.1723366938671297</v>
       </c>
       <c r="T84">
-        <v>2.279346130943864</v>
+        <v>2.133590443948534</v>
       </c>
       <c r="U84">
-        <v>0.2276732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V84">
-        <v>0.09640337257912811</v>
+        <v>0.1682219944978883</v>
       </c>
       <c r="W84">
-        <v>0.2057247657865369</v>
+        <v>0.1085247657865369</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.4590636789482291</v>
+        <v>0.8010571166566107</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2030978635978888</v>
+        <v>0.1449113760309691</v>
       </c>
       <c r="C85">
-        <v>-23895.04863027903</v>
+        <v>-19853.91200461955</v>
       </c>
       <c r="D85">
-        <v>6888.395369720974</v>
+        <v>10929.53199538046</v>
       </c>
       <c r="E85">
         <v>6590.144000000004</v>
@@ -8263,45 +8263,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M85">
-        <v>7486.338508493828</v>
+        <v>5217.484372493827</v>
       </c>
       <c r="N85">
-        <v>-4091.038508493829</v>
+        <v>-1822.184372493828</v>
       </c>
       <c r="O85">
-        <v>-859.118086783704</v>
+        <v>-382.6587182237039</v>
       </c>
       <c r="P85">
-        <v>-3231.920421710125</v>
+        <v>-1439.525654270124</v>
       </c>
       <c r="Q85">
-        <v>-1118.220421710125</v>
+        <v>674.1743457298758</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1889813136451639</v>
+        <v>0.1835902103103419</v>
       </c>
       <c r="T85">
-        <v>2.413425315117033</v>
+        <v>2.32334089822599</v>
       </c>
       <c r="U85">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V85">
-        <v>0.0952418861625121</v>
+        <v>0.1366583872793082</v>
       </c>
       <c r="W85">
-        <v>0.205989205154471</v>
+        <v>0.136989205154471</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.4535327912500576</v>
+        <v>0.6507542251395629</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2049165959311395</v>
+        <v>0.192161043835217</v>
       </c>
       <c r="C86">
-        <v>-24369.95227259096</v>
+        <v>-23778.45574249035</v>
       </c>
       <c r="D86">
-        <v>6809.659727409047</v>
+        <v>7401.15625750965</v>
       </c>
       <c r="E86">
         <v>6986.312000000002</v>
@@ -8345,37 +8345,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M86">
-        <v>7576.535357993753</v>
+        <v>7077.363677993752</v>
       </c>
       <c r="N86">
-        <v>-4181.235357993753</v>
+        <v>-3682.063677993753</v>
       </c>
       <c r="O86">
-        <v>-878.0594251786882</v>
+        <v>-773.2333723786882</v>
       </c>
       <c r="P86">
-        <v>-3303.175932815065</v>
+        <v>-2908.830305615065</v>
       </c>
       <c r="Q86">
-        <v>-1189.475932815065</v>
+        <v>-795.130305615065</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1979301457479866</v>
+        <v>0.1969579451484709</v>
       </c>
       <c r="T86">
-        <v>2.564264397311846</v>
+        <v>2.548740111973576</v>
       </c>
       <c r="U86">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V86">
-        <v>0.09410805418438697</v>
+        <v>0.1007455646538317</v>
       </c>
       <c r="W86">
-        <v>0.2062473483469781</v>
+        <v>0.1912473483469781</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4481335913542237</v>
+        <v>0.4797407840658653</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2067353282643902</v>
+        <v>0.1938297761684676</v>
       </c>
       <c r="C87">
-        <v>-24843.07632977392</v>
+        <v>-24258.0566103229</v>
       </c>
       <c r="D87">
-        <v>6732.703670226078</v>
+        <v>7317.723389677095</v>
       </c>
       <c r="E87">
         <v>7382.48</v>
@@ -8427,37 +8427,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M87">
-        <v>7666.732207493678</v>
+        <v>7161.618007493677</v>
       </c>
       <c r="N87">
-        <v>-4271.432207493679</v>
+        <v>-3766.318007493678</v>
       </c>
       <c r="O87">
-        <v>-897.0007635736725</v>
+        <v>-790.9267815736724</v>
       </c>
       <c r="P87">
-        <v>-3374.431443920007</v>
+        <v>-2975.391225920006</v>
       </c>
       <c r="Q87">
-        <v>-1260.731443920007</v>
+        <v>-861.6912259200058</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.208072155464519</v>
+        <v>0.2070351414917023</v>
       </c>
       <c r="T87">
-        <v>2.735215357132636</v>
+        <v>2.718656119438481</v>
       </c>
       <c r="U87">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V87">
-        <v>0.09300090060574713</v>
+        <v>0.09956032271672782</v>
       </c>
       <c r="W87">
-        <v>0.2064994175820145</v>
+        <v>0.1914994175820144</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4428614314559387</v>
+        <v>0.4740967748415611</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2085540605976409</v>
+        <v>0.1954985085017183</v>
       </c>
       <c r="C88">
-        <v>-25314.48046096642</v>
+        <v>-24735.79737780308</v>
       </c>
       <c r="D88">
-        <v>6657.467539033581</v>
+        <v>7236.150622196923</v>
       </c>
       <c r="E88">
         <v>7778.648000000005</v>
@@ -8509,37 +8509,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M88">
-        <v>7756.929056993605</v>
+        <v>7245.872336993604</v>
       </c>
       <c r="N88">
-        <v>-4361.629056993605</v>
+        <v>-3850.572336993605</v>
       </c>
       <c r="O88">
-        <v>-915.9421019686571</v>
+        <v>-808.620190768657</v>
       </c>
       <c r="P88">
-        <v>-3445.686955024948</v>
+        <v>-3041.952146224948</v>
       </c>
       <c r="Q88">
-        <v>-1331.986955024949</v>
+        <v>-928.2521462249479</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2196630237119847</v>
+        <v>0.2185519373125382</v>
       </c>
       <c r="T88">
-        <v>2.930587882642111</v>
+        <v>2.912845842255515</v>
       </c>
       <c r="U88">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V88">
-        <v>0.09191949478475006</v>
+        <v>0.09840264454560306</v>
       </c>
       <c r="W88">
-        <v>0.2067456247418174</v>
+        <v>0.1917456247418174</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4377118799273813</v>
+        <v>0.4685840216457289</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2103727929308915</v>
+        <v>0.197167240834969</v>
       </c>
       <c r="C89">
-        <v>-25784.2216880787</v>
+        <v>-25211.73956437689</v>
       </c>
       <c r="D89">
-        <v>6583.894311921303</v>
+        <v>7156.37643562311</v>
       </c>
       <c r="E89">
         <v>8174.816000000003</v>
@@ -8591,37 +8591,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M89">
-        <v>7847.12590649353</v>
+        <v>7330.126666493529</v>
       </c>
       <c r="N89">
-        <v>-4451.825906493531</v>
+        <v>-3934.82666649353</v>
       </c>
       <c r="O89">
-        <v>-934.8834403636415</v>
+        <v>-826.3135999636413</v>
       </c>
       <c r="P89">
-        <v>-3516.942466129889</v>
+        <v>-3108.513066529888</v>
       </c>
       <c r="Q89">
-        <v>-1403.24246612989</v>
+        <v>-994.8130665298886</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2330371024590604</v>
+        <v>0.2318405478750411</v>
       </c>
       <c r="T89">
-        <v>3.156017719768426</v>
+        <v>3.136910907044401</v>
       </c>
       <c r="U89">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V89">
-        <v>0.09086294886768397</v>
+        <v>0.09727157966576855</v>
       </c>
       <c r="W89">
-        <v>0.2069861719669123</v>
+        <v>0.1919861719669123</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4326807088937332</v>
+        <v>0.4631979984084217</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2121915252641422</v>
+        <v>0.1988359731682197</v>
       </c>
       <c r="C90">
-        <v>-26252.35453992309</v>
+        <v>-25685.94200621307</v>
       </c>
       <c r="D90">
-        <v>6511.929460076908</v>
+        <v>7078.341993786935</v>
       </c>
       <c r="E90">
         <v>8570.984</v>
@@ -8673,37 +8673,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M90">
-        <v>7937.322755993455</v>
+        <v>7414.380995993455</v>
       </c>
       <c r="N90">
-        <v>-4542.022755993456</v>
+        <v>-4019.080995993456</v>
       </c>
       <c r="O90">
-        <v>-953.8247787586256</v>
+        <v>-844.0070091586257</v>
       </c>
       <c r="P90">
-        <v>-3588.19797723483</v>
+        <v>-3175.07398683483</v>
       </c>
       <c r="Q90">
-        <v>-1474.49797723483</v>
+        <v>-1061.37398683483</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2486401943306489</v>
+        <v>0.2473439268646279</v>
       </c>
       <c r="T90">
-        <v>3.419019196415796</v>
+        <v>3.398320149298101</v>
       </c>
       <c r="U90">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V90">
-        <v>0.08983041535782393</v>
+        <v>0.09616622080593026</v>
       </c>
       <c r="W90">
-        <v>0.2072212522096186</v>
+        <v>0.1922212522096186</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4277638826563045</v>
+        <v>0.4579343847901441</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2140102575973929</v>
+        <v>0.2005047055014704</v>
       </c>
       <c r="C91">
-        <v>-26718.93118699405</v>
+        <v>-26158.46100091973</v>
       </c>
       <c r="D91">
-        <v>6441.520813005951</v>
+        <v>7001.990999080273</v>
       </c>
       <c r="E91">
         <v>8967.152000000006</v>
@@ -8755,37 +8755,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M91">
-        <v>8027.519605493382</v>
+        <v>7498.635325493381</v>
       </c>
       <c r="N91">
-        <v>-4632.219605493383</v>
+        <v>-4103.335325493382</v>
       </c>
       <c r="O91">
-        <v>-972.7661171536104</v>
+        <v>-861.7004183536102</v>
       </c>
       <c r="P91">
-        <v>-3659.453488339773</v>
+        <v>-3241.634907139772</v>
       </c>
       <c r="Q91">
-        <v>-1545.753488339773</v>
+        <v>-1127.934907139772</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2670802119970714</v>
+        <v>0.2656661020341396</v>
       </c>
       <c r="T91">
-        <v>3.729839123362686</v>
+        <v>3.707258344688839</v>
       </c>
       <c r="U91">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V91">
-        <v>0.08882108484818543</v>
+        <v>0.09508570147103217</v>
       </c>
       <c r="W91">
-        <v>0.2074510497502416</v>
+        <v>0.1924510497502416</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4229575468961212</v>
+        <v>0.4527890546239628</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2158289899306436</v>
+        <v>0.2021734378347211</v>
       </c>
       <c r="C92">
-        <v>-27184.00156759809</v>
+        <v>-26629.35044299511</v>
       </c>
       <c r="D92">
-        <v>6372.618432401913</v>
+        <v>6927.269557004893</v>
       </c>
       <c r="E92">
         <v>9363.320000000003</v>
@@ -8837,37 +8837,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M92">
-        <v>8117.716454993307</v>
+        <v>7582.889654993307</v>
       </c>
       <c r="N92">
-        <v>-4722.416454993308</v>
+        <v>-4187.589654993308</v>
       </c>
       <c r="O92">
-        <v>-991.7074555485946</v>
+        <v>-879.3938275485946</v>
       </c>
       <c r="P92">
-        <v>-3730.708999444713</v>
+        <v>-3308.195827444713</v>
       </c>
       <c r="Q92">
-        <v>-1617.008999444713</v>
+        <v>-1194.495827444714</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2892082331967786</v>
+        <v>0.2876527122375535</v>
       </c>
       <c r="T92">
-        <v>4.102823035698956</v>
+        <v>4.077984179157722</v>
       </c>
       <c r="U92">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V92">
-        <v>0.08783418390542783</v>
+        <v>0.09402919367690959</v>
       </c>
       <c r="W92">
-        <v>0.2076757406788508</v>
+        <v>0.1926757406788508</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4182580185972754</v>
+        <v>0.447758065128141</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2176477222638943</v>
+        <v>0.2038421701679717</v>
       </c>
       <c r="C93">
-        <v>-27647.61350597441</v>
+        <v>-27098.66195069708</v>
       </c>
       <c r="D93">
-        <v>6305.174494025587</v>
+        <v>6854.126049302923</v>
       </c>
       <c r="E93">
         <v>9759.488000000001</v>
@@ -8919,37 +8919,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M93">
-        <v>8207.913304493231</v>
+        <v>7667.143984493232</v>
       </c>
       <c r="N93">
-        <v>-4812.613304493232</v>
+        <v>-4271.843984493233</v>
       </c>
       <c r="O93">
-        <v>-1010.648793943579</v>
+        <v>-897.0872367435788</v>
       </c>
       <c r="P93">
-        <v>-3801.964510549653</v>
+        <v>-3374.756747749654</v>
       </c>
       <c r="Q93">
-        <v>-1688.264510549654</v>
+        <v>-1261.056747749654</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3162535924408651</v>
+        <v>0.314525235819504</v>
       </c>
       <c r="T93">
-        <v>4.558692261887728</v>
+        <v>4.53109353239747</v>
       </c>
       <c r="U93">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V93">
-        <v>0.08686897309328029</v>
+        <v>0.0929959058343062</v>
       </c>
       <c r="W93">
-        <v>0.2078954933452927</v>
+        <v>0.1928954933452927</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4136617766346681</v>
+        <v>0.4428376468300296</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2194664545971449</v>
+        <v>0.2055109025012224</v>
       </c>
       <c r="C94">
-        <v>-28109.81282299343</v>
+        <v>-27566.44498495913</v>
       </c>
       <c r="D94">
-        <v>6239.143177006574</v>
+        <v>6782.511015040874</v>
       </c>
       <c r="E94">
         <v>10155.65600000001</v>
@@ -9001,37 +9001,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M94">
-        <v>8298.110153993159</v>
+        <v>7751.398313993159</v>
       </c>
       <c r="N94">
-        <v>-4902.810153993159</v>
+        <v>-4356.09831399316</v>
       </c>
       <c r="O94">
-        <v>-1029.590132338564</v>
+        <v>-914.7806459385635</v>
       </c>
       <c r="P94">
-        <v>-3873.220021654596</v>
+        <v>-3441.317668054596</v>
       </c>
       <c r="Q94">
-        <v>-1759.520021654596</v>
+        <v>-1327.617668054596</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3500602914959735</v>
+        <v>0.3481158902969421</v>
       </c>
       <c r="T94">
-        <v>5.128528794623697</v>
+        <v>5.097480223947155</v>
       </c>
       <c r="U94">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V94">
-        <v>0.08592474512487505</v>
+        <v>0.09198508077088982</v>
       </c>
       <c r="W94">
-        <v>0.2081104687798555</v>
+        <v>0.1931104687798555</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4091654529755955</v>
+        <v>0.4380241941470944</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2212851869303956</v>
+        <v>0.2071796348344731</v>
       </c>
       <c r="C95">
-        <v>-28570.64343997149</v>
+        <v>-28032.7469609285</v>
       </c>
       <c r="D95">
-        <v>6174.48056002852</v>
+        <v>6712.3770390715</v>
       </c>
       <c r="E95">
         <v>10551.824</v>
@@ -9083,37 +9083,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M95">
-        <v>8388.307003493084</v>
+        <v>7835.652643493084</v>
       </c>
       <c r="N95">
-        <v>-4993.007003493085</v>
+        <v>-4440.352643493085</v>
       </c>
       <c r="O95">
-        <v>-1048.531470733548</v>
+        <v>-932.4740551335477</v>
       </c>
       <c r="P95">
-        <v>-3944.475532759537</v>
+        <v>-3507.878588359537</v>
       </c>
       <c r="Q95">
-        <v>-1830.775532759537</v>
+        <v>-1394.178588359537</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3935260474239697</v>
+        <v>0.3913038746250767</v>
       </c>
       <c r="T95">
-        <v>5.861175765284225</v>
+        <v>5.825691684511035</v>
       </c>
       <c r="U95">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V95">
-        <v>0.08500082313428499</v>
+        <v>0.09099599388088025</v>
       </c>
       <c r="W95">
-        <v>0.2083208210867933</v>
+        <v>0.1933208210867933</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4047658244489762</v>
+        <v>0.4333142565756203</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2231039192636463</v>
+        <v>0.2088483671677238</v>
       </c>
       <c r="C96">
-        <v>-29030.14747609629</v>
+        <v>-28497.61335265509</v>
       </c>
       <c r="D96">
-        <v>6111.144523903718</v>
+        <v>6643.678647344913</v>
       </c>
       <c r="E96">
         <v>10947.99200000001</v>
@@ -9165,37 +9165,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M96">
-        <v>8478.503852993012</v>
+        <v>7919.906972993011</v>
       </c>
       <c r="N96">
-        <v>-5083.203852993012</v>
+        <v>-4524.606972993011</v>
       </c>
       <c r="O96">
-        <v>-1067.472809128533</v>
+        <v>-950.1674643285323</v>
       </c>
       <c r="P96">
-        <v>-4015.73104386448</v>
+        <v>-3574.439508664479</v>
       </c>
       <c r="Q96">
-        <v>-1902.03104386448</v>
+        <v>-1460.739508664479</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4514803886612981</v>
+        <v>0.4488878537292563</v>
       </c>
       <c r="T96">
-        <v>6.838038392831598</v>
+        <v>6.79664029859621</v>
       </c>
       <c r="U96">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V96">
-        <v>0.08409655905838832</v>
+        <v>0.09002795139278576</v>
       </c>
       <c r="W96">
-        <v>0.2085266978127324</v>
+        <v>0.1935266978127324</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4004598050399445</v>
+        <v>0.428704530441837</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.224922651596897</v>
+        <v>0.2105170995009745</v>
       </c>
       <c r="C97">
-        <v>-29488.365339917</v>
+        <v>-28961.0877914167</v>
       </c>
       <c r="D97">
-        <v>6049.094660083008</v>
+        <v>6576.372208583308</v>
       </c>
       <c r="E97">
         <v>11344.16000000001</v>
@@ -9247,37 +9247,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M97">
-        <v>8568.700702492935</v>
+        <v>8004.161302492936</v>
       </c>
       <c r="N97">
-        <v>-5173.400702492936</v>
+        <v>-4608.861302492936</v>
       </c>
       <c r="O97">
-        <v>-1086.414147523516</v>
+        <v>-967.8608735235166</v>
       </c>
       <c r="P97">
-        <v>-4086.98655496942</v>
+        <v>-3641.00042896942</v>
       </c>
       <c r="Q97">
-        <v>-1973.28655496942</v>
+        <v>-1527.30042896942</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5326164663935579</v>
+        <v>0.5295054244751077</v>
       </c>
       <c r="T97">
-        <v>8.20564607139792</v>
+        <v>8.155968358315455</v>
       </c>
       <c r="U97">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V97">
-        <v>0.08321133212093164</v>
+        <v>0.08908028874654593</v>
       </c>
       <c r="W97">
-        <v>0.2087282402918096</v>
+        <v>0.1937282402918096</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.396244438671103</v>
+        <v>0.4241918511740282</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2267413839301477</v>
+        <v>0.2121858318342252</v>
       </c>
       <c r="C98">
-        <v>-29945.33581531662</v>
+        <v>-29423.21215812758</v>
       </c>
       <c r="D98">
-        <v>5988.292184683384</v>
+        <v>6510.415841872425</v>
       </c>
       <c r="E98">
         <v>11740.328</v>
@@ -9329,37 +9329,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M98">
-        <v>8658.897551992861</v>
+        <v>8088.415631992861</v>
       </c>
       <c r="N98">
-        <v>-5263.597551992862</v>
+        <v>-4693.115631992861</v>
       </c>
       <c r="O98">
-        <v>-1105.355485918501</v>
+        <v>-985.5542827185009</v>
       </c>
       <c r="P98">
-        <v>-4158.242066074361</v>
+        <v>-3707.561349274361</v>
       </c>
       <c r="Q98">
-        <v>-2044.542066074361</v>
+        <v>-1593.861349274361</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.654320582991946</v>
+        <v>0.6504317805938832</v>
       </c>
       <c r="T98">
-        <v>10.25705758924738</v>
+        <v>10.1949604478943</v>
       </c>
       <c r="U98">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V98">
-        <v>0.08234454741133859</v>
+        <v>0.08815236907210275</v>
       </c>
       <c r="W98">
-        <v>0.2089255839692394</v>
+        <v>0.1939255839692394</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3921168924349457</v>
+        <v>0.4197731860576321</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2285601162633984</v>
+        <v>0.2138545641674758</v>
       </c>
       <c r="C99">
-        <v>-30401.09614235114</v>
+        <v>-29884.02667024143</v>
       </c>
       <c r="D99">
-        <v>5928.69985764886</v>
+        <v>6445.769329758575</v>
       </c>
       <c r="E99">
         <v>12136.496</v>
@@ -9411,37 +9411,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M99">
-        <v>8749.094401492786</v>
+        <v>8172.669961492786</v>
       </c>
       <c r="N99">
-        <v>-5353.794401492787</v>
+        <v>-4777.369961492786</v>
       </c>
       <c r="O99">
-        <v>-1124.296824313485</v>
+        <v>-1003.247691913485</v>
       </c>
       <c r="P99">
-        <v>-4229.497577179302</v>
+        <v>-3774.122269579301</v>
       </c>
       <c r="Q99">
-        <v>-2115.797577179302</v>
+        <v>-1660.422269579301</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8571607773225945</v>
+        <v>0.851975707458511</v>
       </c>
       <c r="T99">
-        <v>13.67607678566317</v>
+        <v>13.5932805971924</v>
       </c>
       <c r="U99">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V99">
-        <v>0.08149563455142789</v>
+        <v>0.08724358176208107</v>
       </c>
       <c r="W99">
-        <v>0.2091188587048665</v>
+        <v>0.1941188587048665</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3880744502448947</v>
+        <v>0.4154456274384813</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.230378848596649</v>
+        <v>0.2155232965007265</v>
       </c>
       <c r="C100">
-        <v>-30855.68209330937</v>
+        <v>-30343.56996352768</v>
       </c>
       <c r="D100">
-        <v>5870.281906690634</v>
+        <v>6382.394036472321</v>
       </c>
       <c r="E100">
         <v>12532.664</v>
@@ -9493,37 +9493,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M100">
-        <v>8839.291250992712</v>
+        <v>8256.924290992711</v>
       </c>
       <c r="N100">
-        <v>-5443.991250992713</v>
+        <v>-4861.624290992711</v>
       </c>
       <c r="O100">
-        <v>-1143.23816270847</v>
+        <v>-1020.941101108469</v>
       </c>
       <c r="P100">
-        <v>-4300.753088284243</v>
+        <v>-3840.683189884242</v>
       </c>
       <c r="Q100">
-        <v>-2187.053088284243</v>
+        <v>-1726.983189884242</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.262841165983892</v>
+        <v>1.255063561187767</v>
       </c>
       <c r="T100">
-        <v>20.51411517849476</v>
+        <v>20.38992089578859</v>
       </c>
       <c r="U100">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V100">
-        <v>0.08066404644376027</v>
+        <v>0.08635334113185576</v>
       </c>
       <c r="W100">
-        <v>0.2093081890581339</v>
+        <v>0.1943081890581339</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3841145068750489</v>
+        <v>0.4112063863421703</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2321975809298998</v>
+        <v>0.2171920288339772</v>
       </c>
       <c r="C101">
-        <v>-31309.12804431996</v>
+        <v>-30801.87916907071</v>
       </c>
       <c r="D101">
-        <v>5813.003955680045</v>
+        <v>6320.252830929297</v>
       </c>
       <c r="E101">
         <v>12928.83200000001</v>
@@ -9575,37 +9575,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M101">
-        <v>8929.488100492639</v>
+        <v>8341.178620492637</v>
       </c>
       <c r="N101">
-        <v>-5534.18810049264</v>
+        <v>-4945.878620492638</v>
       </c>
       <c r="O101">
-        <v>-1162.179501103454</v>
+        <v>-1038.634510303454</v>
       </c>
       <c r="P101">
-        <v>-4372.008599389185</v>
+        <v>-3907.244110189185</v>
       </c>
       <c r="Q101">
-        <v>-2258.308599389185</v>
+        <v>-1793.544110189185</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.479882331967784</v>
+        <v>2.464327122375533</v>
       </c>
       <c r="T101">
-        <v>41.02823035698951</v>
+        <v>40.77984179157718</v>
       </c>
       <c r="U101">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V101">
-        <v>0.07984925809584348</v>
+        <v>0.08548108516082689</v>
       </c>
       <c r="W101">
-        <v>0.2094936945557797</v>
+        <v>0.1944936945557797</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3802345623611594</v>
+        <v>0.4070527864801281</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/portugal/portugal_power.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_power.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07222119884477138</v>
+        <v>0.0721988828704654</v>
       </c>
       <c r="C2">
-        <v>43097.43278124389</v>
+        <v>42735.92273002939</v>
       </c>
       <c r="D2">
-        <v>40998.93278124389</v>
+        <v>41033.59073002938</v>
       </c>
       <c r="E2">
-        <v>-26291.8</v>
+        <v>-25895.632</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>396.1680000000001</v>
       </c>
       <c r="G2">
         <v>2098.5</v>
@@ -1457,28 +1457,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>24.63104549992562</v>
       </c>
       <c r="N2">
-        <v>3395.299999999999</v>
+        <v>3370.668954500074</v>
       </c>
       <c r="O2">
-        <v>713.0129999999998</v>
+        <v>707.8404804450154</v>
       </c>
       <c r="P2">
-        <v>2682.286999999999</v>
+        <v>2662.828474055058</v>
       </c>
       <c r="Q2">
-        <v>4795.986999999999</v>
+        <v>4776.528474055058</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07222119884477138</v>
+        <v>0.07243203467393673</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880388</v>
+        <v>0.4490543647590746</v>
       </c>
       <c r="U2">
         <v>0.0621732333250682</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>137.8463614145105</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0721988828704654</v>
+        <v>0.07217656689615942</v>
       </c>
       <c r="C3">
-        <v>42735.92273002939</v>
+        <v>42374.47132373994</v>
       </c>
       <c r="D3">
-        <v>41033.59073002938</v>
+        <v>41068.30732373994</v>
       </c>
       <c r="E3">
-        <v>-25895.632</v>
+        <v>-25499.464</v>
       </c>
       <c r="F3">
-        <v>396.1680000000001</v>
+        <v>792.3360000000001</v>
       </c>
       <c r="G3">
         <v>2098.5</v>
@@ -1539,28 +1539,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M3">
-        <v>24.63104549992562</v>
+        <v>49.26209099985125</v>
       </c>
       <c r="N3">
-        <v>3370.668954500074</v>
+        <v>3346.037909000148</v>
       </c>
       <c r="O3">
-        <v>707.8404804450154</v>
+        <v>702.6679608900311</v>
       </c>
       <c r="P3">
-        <v>2662.828474055058</v>
+        <v>2643.369948110117</v>
       </c>
       <c r="Q3">
-        <v>4776.528474055058</v>
+        <v>4757.069948110116</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07243203467393673</v>
+        <v>0.07264717327512586</v>
       </c>
       <c r="T3">
-        <v>0.4490543647590746</v>
+        <v>0.4526819106478868</v>
       </c>
       <c r="U3">
         <v>0.0621732333250682</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>137.8463614145105</v>
+        <v>68.92318070725524</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07217656689615942</v>
+        <v>0.07215425092185344</v>
       </c>
       <c r="C4">
-        <v>42374.47132373994</v>
+        <v>42013.07871135177</v>
       </c>
       <c r="D4">
-        <v>41068.30732373994</v>
+        <v>41103.08271135177</v>
       </c>
       <c r="E4">
-        <v>-25499.464</v>
+        <v>-25103.296</v>
       </c>
       <c r="F4">
-        <v>792.3360000000001</v>
+        <v>1188.504</v>
       </c>
       <c r="G4">
         <v>2098.5</v>
@@ -1621,28 +1621,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M4">
-        <v>49.26209099985125</v>
+        <v>73.89313649977687</v>
       </c>
       <c r="N4">
-        <v>3346.037909000148</v>
+        <v>3321.406863500222</v>
       </c>
       <c r="O4">
-        <v>702.6679608900311</v>
+        <v>697.4954413350466</v>
       </c>
       <c r="P4">
-        <v>2643.369948110117</v>
+        <v>2623.911422165176</v>
       </c>
       <c r="Q4">
-        <v>4757.069948110116</v>
+        <v>4737.611422165175</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07264717327512586</v>
+        <v>0.0728667477237622</v>
       </c>
       <c r="T4">
-        <v>0.4526819106478868</v>
+        <v>0.4563842512972929</v>
       </c>
       <c r="U4">
         <v>0.0621732333250682</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>68.92318070725524</v>
+        <v>45.94878713817015</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07215425092185344</v>
+        <v>0.07213193494754747</v>
       </c>
       <c r="C5">
-        <v>42013.07871135177</v>
+        <v>41651.74504234605</v>
       </c>
       <c r="D5">
-        <v>41103.08271135177</v>
+        <v>41137.91704234605</v>
       </c>
       <c r="E5">
-        <v>-25103.296</v>
+        <v>-24707.128</v>
       </c>
       <c r="F5">
-        <v>1188.504</v>
+        <v>1584.672</v>
       </c>
       <c r="G5">
         <v>2098.5</v>
@@ -1703,28 +1703,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M5">
-        <v>73.89313649977687</v>
+        <v>98.52418199970249</v>
       </c>
       <c r="N5">
-        <v>3321.406863500222</v>
+        <v>3296.775818000297</v>
       </c>
       <c r="O5">
-        <v>697.4954413350466</v>
+        <v>692.3229217800623</v>
       </c>
       <c r="P5">
-        <v>2623.911422165176</v>
+        <v>2604.452896220234</v>
       </c>
       <c r="Q5">
-        <v>4737.611422165175</v>
+        <v>4718.152896220234</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0728667477237622</v>
+        <v>0.07309089664007845</v>
       </c>
       <c r="T5">
-        <v>0.4563842512972929</v>
+        <v>0.4601637240435618</v>
       </c>
       <c r="U5">
         <v>0.0621732333250682</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.94878713817015</v>
+        <v>34.46159035362761</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07213193494754747</v>
+        <v>0.07210961897324147</v>
       </c>
       <c r="C6">
-        <v>41651.74504234605</v>
+        <v>41290.47046671121</v>
       </c>
       <c r="D6">
-        <v>41137.91704234605</v>
+        <v>41172.81046671121</v>
       </c>
       <c r="E6">
-        <v>-24707.128</v>
+        <v>-24310.96</v>
       </c>
       <c r="F6">
-        <v>1584.672</v>
+        <v>1980.84</v>
       </c>
       <c r="G6">
         <v>2098.5</v>
@@ -1785,28 +1785,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M6">
-        <v>98.52418199970249</v>
+        <v>123.1552274996281</v>
       </c>
       <c r="N6">
-        <v>3296.775818000297</v>
+        <v>3272.144772500371</v>
       </c>
       <c r="O6">
-        <v>692.3229217800623</v>
+        <v>687.150402225078</v>
       </c>
       <c r="P6">
-        <v>2604.452896220234</v>
+        <v>2584.994370275293</v>
       </c>
       <c r="Q6">
-        <v>4718.152896220234</v>
+        <v>4698.694370275293</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07309089664007845</v>
+        <v>0.07331976448094872</v>
       </c>
       <c r="T6">
-        <v>0.4601637240435618</v>
+        <v>0.4640227646371204</v>
       </c>
       <c r="U6">
         <v>0.0621732333250682</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.46159035362761</v>
+        <v>27.5692722829021</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07210961897324147</v>
+        <v>0.07208730299893551</v>
       </c>
       <c r="C7">
-        <v>41290.47046671121</v>
+        <v>40929.25513494487</v>
       </c>
       <c r="D7">
-        <v>41172.81046671121</v>
+        <v>41207.76313494487</v>
       </c>
       <c r="E7">
-        <v>-24310.96</v>
+        <v>-23914.792</v>
       </c>
       <c r="F7">
-        <v>1980.84</v>
+        <v>2377.008</v>
       </c>
       <c r="G7">
         <v>2098.5</v>
@@ -1867,28 +1867,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M7">
-        <v>123.1552274996281</v>
+        <v>147.7862729995537</v>
       </c>
       <c r="N7">
-        <v>3272.144772500371</v>
+        <v>3247.513727000446</v>
       </c>
       <c r="O7">
-        <v>687.150402225078</v>
+        <v>681.9778826700935</v>
       </c>
       <c r="P7">
-        <v>2584.994370275293</v>
+        <v>2565.535844330352</v>
       </c>
       <c r="Q7">
-        <v>4698.694370275293</v>
+        <v>4679.235844330352</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07331976448094872</v>
+        <v>0.07355350185034816</v>
       </c>
       <c r="T7">
-        <v>0.4640227646371204</v>
+        <v>0.4679639124773505</v>
       </c>
       <c r="U7">
         <v>0.0621732333250682</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.5692722829021</v>
+        <v>22.97439356908508</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07208730299893551</v>
+        <v>0.07206498702462952</v>
       </c>
       <c r="C8">
-        <v>40929.25513494487</v>
+        <v>40568.09919805628</v>
       </c>
       <c r="D8">
-        <v>41207.76313494487</v>
+        <v>41242.77519805628</v>
       </c>
       <c r="E8">
-        <v>-23914.792</v>
+        <v>-23518.624</v>
       </c>
       <c r="F8">
-        <v>2377.008</v>
+        <v>2773.176</v>
       </c>
       <c r="G8">
         <v>2098.5</v>
@@ -1949,28 +1949,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M8">
-        <v>147.7862729995537</v>
+        <v>172.4173184994793</v>
       </c>
       <c r="N8">
-        <v>3247.513727000446</v>
+        <v>3222.88268150052</v>
       </c>
       <c r="O8">
-        <v>681.9778826700935</v>
+        <v>676.8053631151091</v>
       </c>
       <c r="P8">
-        <v>2565.535844330352</v>
+        <v>2546.077318385411</v>
       </c>
       <c r="Q8">
-        <v>4679.235844330352</v>
+        <v>4659.777318385411</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07355350185034816</v>
+        <v>0.0737922658298422</v>
       </c>
       <c r="T8">
-        <v>0.4679639124773505</v>
+        <v>0.4719898161851125</v>
       </c>
       <c r="U8">
         <v>0.0621732333250682</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.97439356908508</v>
+        <v>19.69233734493007</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07206498702462952</v>
+        <v>0.07204267105032354</v>
       </c>
       <c r="C9">
-        <v>40568.09919805628</v>
+        <v>40207.00280756822</v>
       </c>
       <c r="D9">
-        <v>41242.77519805628</v>
+        <v>41277.84680756822</v>
       </c>
       <c r="E9">
-        <v>-23518.624</v>
+        <v>-23122.456</v>
       </c>
       <c r="F9">
-        <v>2773.176</v>
+        <v>3169.344000000001</v>
       </c>
       <c r="G9">
         <v>2098.5</v>
@@ -2031,28 +2031,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M9">
-        <v>172.4173184994794</v>
+        <v>197.048363999405</v>
       </c>
       <c r="N9">
-        <v>3222.88268150052</v>
+        <v>3198.251636000594</v>
       </c>
       <c r="O9">
-        <v>676.8053631151091</v>
+        <v>671.6328435601248</v>
       </c>
       <c r="P9">
-        <v>2546.077318385411</v>
+        <v>2526.618792440469</v>
       </c>
       <c r="Q9">
-        <v>4659.777318385411</v>
+        <v>4640.318792440469</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0737922658298422</v>
+        <v>0.07403622033062959</v>
       </c>
       <c r="T9">
-        <v>0.4719898161851125</v>
+        <v>0.4761032395386954</v>
       </c>
       <c r="U9">
         <v>0.0621732333250682</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.69233734493007</v>
+        <v>17.23079517681381</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07204267105032354</v>
+        <v>0.07202035507601756</v>
       </c>
       <c r="C10">
-        <v>40207.00280756822</v>
+        <v>39845.96611551935</v>
       </c>
       <c r="D10">
-        <v>41277.84680756822</v>
+        <v>41312.97811551936</v>
       </c>
       <c r="E10">
-        <v>-23122.456</v>
+        <v>-22726.288</v>
       </c>
       <c r="F10">
-        <v>3169.344000000001</v>
+        <v>3565.512</v>
       </c>
       <c r="G10">
         <v>2098.5</v>
@@ -2113,28 +2113,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M10">
-        <v>197.048363999405</v>
+        <v>221.6794094993306</v>
       </c>
       <c r="N10">
-        <v>3198.251636000594</v>
+        <v>3173.620590500669</v>
       </c>
       <c r="O10">
-        <v>671.6328435601248</v>
+        <v>666.4603240051404</v>
       </c>
       <c r="P10">
-        <v>2526.618792440469</v>
+        <v>2507.160266495528</v>
       </c>
       <c r="Q10">
-        <v>4640.318792440469</v>
+        <v>4620.860266495528</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07403622033062959</v>
+        <v>0.07428553646879693</v>
       </c>
       <c r="T10">
-        <v>0.4761032395386954</v>
+        <v>0.4803070678011482</v>
       </c>
       <c r="U10">
         <v>0.0621732333250682</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.23079517681381</v>
+        <v>15.31626237939006</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07202035507601756</v>
+        <v>0.07199803910171157</v>
       </c>
       <c r="C11">
-        <v>39845.96611551935</v>
+        <v>39484.98927446642</v>
       </c>
       <c r="D11">
-        <v>41312.97811551936</v>
+        <v>41348.16927446643</v>
       </c>
       <c r="E11">
-        <v>-22726.288</v>
+        <v>-22330.12</v>
       </c>
       <c r="F11">
-        <v>3565.512</v>
+        <v>3961.68</v>
       </c>
       <c r="G11">
         <v>2098.5</v>
@@ -2195,28 +2195,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M11">
-        <v>221.6794094993306</v>
+        <v>246.3104549992562</v>
       </c>
       <c r="N11">
-        <v>3173.620590500669</v>
+        <v>3148.989545000743</v>
       </c>
       <c r="O11">
-        <v>666.4603240051404</v>
+        <v>661.287804450156</v>
       </c>
       <c r="P11">
-        <v>2507.160266495528</v>
+        <v>2487.701740550587</v>
       </c>
       <c r="Q11">
-        <v>4620.860266495528</v>
+        <v>4601.401740550587</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07428553646879693</v>
+        <v>0.0745403929655902</v>
       </c>
       <c r="T11">
-        <v>0.4803070678011482</v>
+        <v>0.4846043144694333</v>
       </c>
       <c r="U11">
         <v>0.0621732333250682</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.31626237939006</v>
+        <v>13.78463614145105</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07199803910171157</v>
+        <v>0.07197572312740559</v>
       </c>
       <c r="C12">
-        <v>39484.98927446642</v>
+        <v>39124.07243748635</v>
       </c>
       <c r="D12">
-        <v>41348.16927446643</v>
+        <v>41383.42043748635</v>
       </c>
       <c r="E12">
-        <v>-22330.12</v>
+        <v>-21933.952</v>
       </c>
       <c r="F12">
-        <v>3961.68</v>
+        <v>4357.848</v>
       </c>
       <c r="G12">
         <v>2098.5</v>
@@ -2277,28 +2277,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M12">
-        <v>246.3104549992562</v>
+        <v>270.9415004991818</v>
       </c>
       <c r="N12">
-        <v>3148.989545000743</v>
+        <v>3124.358499500817</v>
       </c>
       <c r="O12">
-        <v>661.287804450156</v>
+        <v>656.1152848951716</v>
       </c>
       <c r="P12">
-        <v>2487.701740550587</v>
+        <v>2468.243214605646</v>
       </c>
       <c r="Q12">
-        <v>4601.401740550587</v>
+        <v>4581.943214605646</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0745403929655902</v>
+        <v>0.07480097657467097</v>
       </c>
       <c r="T12">
-        <v>0.4846043144694333</v>
+        <v>0.4889981284785787</v>
       </c>
       <c r="U12">
         <v>0.0621732333250682</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.78463614145105</v>
+        <v>12.53148740131913</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07197572312740559</v>
+        <v>0.0719534071530996</v>
       </c>
       <c r="C13">
-        <v>39124.07243748635</v>
+        <v>38763.21575817855</v>
       </c>
       <c r="D13">
-        <v>41383.42043748635</v>
+        <v>41418.73175817855</v>
       </c>
       <c r="E13">
-        <v>-21933.952</v>
+        <v>-21537.784</v>
       </c>
       <c r="F13">
-        <v>4357.848</v>
+        <v>4754.016000000001</v>
       </c>
       <c r="G13">
         <v>2098.5</v>
@@ -2359,28 +2359,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M13">
-        <v>270.9415004991818</v>
+        <v>295.5725459991075</v>
       </c>
       <c r="N13">
-        <v>3124.358499500817</v>
+        <v>3099.727454000892</v>
       </c>
       <c r="O13">
-        <v>656.1152848951716</v>
+        <v>650.9427653401872</v>
       </c>
       <c r="P13">
-        <v>2468.243214605646</v>
+        <v>2448.784688660704</v>
       </c>
       <c r="Q13">
-        <v>4581.943214605646</v>
+        <v>4562.484688660705</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07480097657467097</v>
+        <v>0.07506748253850357</v>
       </c>
       <c r="T13">
-        <v>0.4889981284785787</v>
+        <v>0.4934918018970229</v>
       </c>
       <c r="U13">
         <v>0.0621732333250682</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.53148740131913</v>
+        <v>11.48719678454254</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0719534071530996</v>
+        <v>0.07193109117879364</v>
       </c>
       <c r="C14">
-        <v>38763.21575817855</v>
+        <v>38402.41939066711</v>
       </c>
       <c r="D14">
-        <v>41418.73175817855</v>
+        <v>41454.10339066711</v>
       </c>
       <c r="E14">
-        <v>-21537.784</v>
+        <v>-21141.616</v>
       </c>
       <c r="F14">
-        <v>4754.016000000001</v>
+        <v>5150.184</v>
       </c>
       <c r="G14">
         <v>2098.5</v>
@@ -2441,28 +2441,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M14">
-        <v>295.5725459991075</v>
+        <v>320.2035914990331</v>
       </c>
       <c r="N14">
-        <v>3099.727454000892</v>
+        <v>3075.096408500966</v>
       </c>
       <c r="O14">
-        <v>650.9427653401872</v>
+        <v>645.770245785203</v>
       </c>
       <c r="P14">
-        <v>2448.784688660704</v>
+        <v>2429.326162715764</v>
       </c>
       <c r="Q14">
-        <v>4562.484688660705</v>
+        <v>4543.026162715763</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07506748253850357</v>
+        <v>0.07534011507621739</v>
       </c>
       <c r="T14">
-        <v>0.4934918018970229</v>
+        <v>0.4980887781526728</v>
       </c>
       <c r="U14">
         <v>0.0621732333250682</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.48719678454254</v>
+        <v>10.60356626265465</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07193109117879364</v>
+        <v>0.07190877520448766</v>
       </c>
       <c r="C15">
-        <v>38402.41939066711</v>
+        <v>38041.68348960312</v>
       </c>
       <c r="D15">
-        <v>41454.10339066711</v>
+        <v>41489.53548960312</v>
       </c>
       <c r="E15">
-        <v>-21141.616</v>
+        <v>-20745.448</v>
       </c>
       <c r="F15">
-        <v>5150.184</v>
+        <v>5546.352000000001</v>
       </c>
       <c r="G15">
         <v>2098.5</v>
@@ -2523,28 +2523,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M15">
-        <v>320.2035914990331</v>
+        <v>344.8346369989587</v>
       </c>
       <c r="N15">
-        <v>3075.096408500966</v>
+        <v>3050.465363001041</v>
       </c>
       <c r="O15">
-        <v>645.770245785203</v>
+        <v>640.5977262302185</v>
       </c>
       <c r="P15">
-        <v>2429.326162715764</v>
+        <v>2409.867636770822</v>
       </c>
       <c r="Q15">
-        <v>4543.026162715763</v>
+        <v>4523.567636770822</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07534011507621739</v>
+        <v>0.07561908790550595</v>
       </c>
       <c r="T15">
-        <v>0.4980887781526728</v>
+        <v>0.5027926608328727</v>
       </c>
       <c r="U15">
         <v>0.0621732333250682</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.60356626265465</v>
+        <v>9.846168672465033</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07190877520448766</v>
+        <v>0.07188645923018167</v>
       </c>
       <c r="C16">
-        <v>38041.68348960312</v>
+        <v>37681.00821016682</v>
       </c>
       <c r="D16">
-        <v>41489.53548960312</v>
+        <v>41525.02821016683</v>
       </c>
       <c r="E16">
-        <v>-20745.448</v>
+        <v>-20349.28</v>
       </c>
       <c r="F16">
-        <v>5546.352000000001</v>
+        <v>5942.520000000001</v>
       </c>
       <c r="G16">
         <v>2098.5</v>
@@ -2605,28 +2605,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M16">
-        <v>344.8346369989587</v>
+        <v>369.4656824988844</v>
       </c>
       <c r="N16">
-        <v>3050.465363001041</v>
+        <v>3025.834317501115</v>
       </c>
       <c r="O16">
-        <v>640.5977262302185</v>
+        <v>635.4252066752341</v>
       </c>
       <c r="P16">
-        <v>2409.867636770822</v>
+        <v>2390.409110825881</v>
       </c>
       <c r="Q16">
-        <v>4523.567636770822</v>
+        <v>4504.109110825881</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07561908790550595</v>
+        <v>0.07590462480136598</v>
       </c>
       <c r="T16">
-        <v>0.5027926608328727</v>
+        <v>0.5076072231055477</v>
       </c>
       <c r="U16">
         <v>0.0621732333250682</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.846168672465033</v>
+        <v>9.189757427634031</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07188645923018167</v>
+        <v>0.07205374325587569</v>
       </c>
       <c r="C17">
-        <v>37681.00821016682</v>
+        <v>37020.2503641265</v>
       </c>
       <c r="D17">
-        <v>41525.02821016683</v>
+        <v>41260.4383641265</v>
       </c>
       <c r="E17">
-        <v>-20349.28</v>
+        <v>-19953.112</v>
       </c>
       <c r="F17">
-        <v>5942.52</v>
+        <v>6338.688000000001</v>
       </c>
       <c r="G17">
         <v>2098.5</v>
@@ -2687,45 +2687,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M17">
-        <v>369.4656824988843</v>
+        <v>403.6047599988099</v>
       </c>
       <c r="N17">
-        <v>3025.834317501115</v>
+        <v>2991.695240001189</v>
       </c>
       <c r="O17">
-        <v>635.4252066752341</v>
+        <v>628.2560004002497</v>
       </c>
       <c r="P17">
-        <v>2390.409110825881</v>
+        <v>2363.439239600939</v>
       </c>
       <c r="Q17">
-        <v>4504.109110825881</v>
+        <v>4477.13923960094</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07590462480136598</v>
+        <v>0.0761969601947465</v>
       </c>
       <c r="T17">
-        <v>0.5076072231055477</v>
+        <v>0.5125364178132865</v>
       </c>
       <c r="U17">
-        <v>0.0621732333250682</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V17">
         <v>0.21</v>
       </c>
       <c r="W17">
-        <v>0.04911685432680388</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.189757427634031</v>
+        <v>8.412437950459282</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07205374325587569</v>
+        <v>0.0720432772815697</v>
       </c>
       <c r="C18">
-        <v>37020.2503641265</v>
+        <v>36640.53727115428</v>
       </c>
       <c r="D18">
-        <v>41260.4383641265</v>
+        <v>41276.89327115428</v>
       </c>
       <c r="E18">
-        <v>-19953.112</v>
+        <v>-19556.944</v>
       </c>
       <c r="F18">
-        <v>6338.688000000001</v>
+        <v>6734.856000000001</v>
       </c>
       <c r="G18">
         <v>2098.5</v>
@@ -2769,28 +2769,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M18">
-        <v>403.6047599988099</v>
+        <v>428.8300574987355</v>
       </c>
       <c r="N18">
-        <v>2991.695240001189</v>
+        <v>2966.469942501264</v>
       </c>
       <c r="O18">
-        <v>628.2560004002497</v>
+        <v>622.9586879252654</v>
       </c>
       <c r="P18">
-        <v>2363.439239600939</v>
+        <v>2343.511254575998</v>
       </c>
       <c r="Q18">
-        <v>4477.13923960094</v>
+        <v>4457.211254575998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0761969601947465</v>
+        <v>0.07649633981447354</v>
       </c>
       <c r="T18">
-        <v>0.5125364178132865</v>
+        <v>0.5175843882971154</v>
       </c>
       <c r="U18">
         <v>0.06367323332506819</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.412437950459282</v>
+        <v>7.917588659255797</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0720432772815697</v>
+        <v>0.0720328113072637</v>
       </c>
       <c r="C19">
-        <v>36640.53727115428</v>
+        <v>36260.83730804699</v>
       </c>
       <c r="D19">
-        <v>41276.89327115428</v>
+        <v>41293.36130804699</v>
       </c>
       <c r="E19">
-        <v>-19556.944</v>
+        <v>-19160.776</v>
       </c>
       <c r="F19">
-        <v>6734.856000000001</v>
+        <v>7131.024000000001</v>
       </c>
       <c r="G19">
         <v>2098.5</v>
@@ -2851,28 +2851,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M19">
-        <v>428.8300574987355</v>
+        <v>454.0553549986611</v>
       </c>
       <c r="N19">
-        <v>2966.469942501264</v>
+        <v>2941.244645001338</v>
       </c>
       <c r="O19">
-        <v>622.9586879252654</v>
+        <v>617.661375450281</v>
       </c>
       <c r="P19">
-        <v>2343.511254575998</v>
+        <v>2323.583269551057</v>
       </c>
       <c r="Q19">
-        <v>4457.211254575998</v>
+        <v>4437.283269551057</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07649633981447354</v>
+        <v>0.07680302137614514</v>
       </c>
       <c r="T19">
-        <v>0.5175843882971154</v>
+        <v>0.5227554800122571</v>
       </c>
       <c r="U19">
         <v>0.06367323332506819</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.917588659255797</v>
+        <v>7.477722622630474</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07203281130726372</v>
+        <v>0.07202234533295775</v>
       </c>
       <c r="C20">
-        <v>36260.83730804697</v>
+        <v>35881.15049052586</v>
       </c>
       <c r="D20">
-        <v>41293.36130804697</v>
+        <v>41309.84249052587</v>
       </c>
       <c r="E20">
-        <v>-19160.776</v>
+        <v>-18764.608</v>
       </c>
       <c r="F20">
-        <v>7131.024</v>
+        <v>7527.192000000001</v>
       </c>
       <c r="G20">
         <v>2098.5</v>
@@ -2933,28 +2933,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M20">
-        <v>454.0553549986611</v>
+        <v>479.2806524985867</v>
       </c>
       <c r="N20">
-        <v>2941.244645001338</v>
+        <v>2916.019347501413</v>
       </c>
       <c r="O20">
-        <v>617.661375450281</v>
+        <v>612.3640629752966</v>
       </c>
       <c r="P20">
-        <v>2323.583269551057</v>
+        <v>2303.655284526116</v>
       </c>
       <c r="Q20">
-        <v>4437.283269551057</v>
+        <v>4417.355284526116</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07680302137614514</v>
+        <v>0.07711727532205556</v>
       </c>
       <c r="T20">
-        <v>0.5227554800122571</v>
+        <v>0.5280542530043161</v>
       </c>
       <c r="U20">
         <v>0.06367323332506819</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.477722622630475</v>
+        <v>7.084158274070976</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07202234533295775</v>
+        <v>0.07201187935865176</v>
       </c>
       <c r="C21">
-        <v>35881.15049052586</v>
+        <v>35501.47683433748</v>
       </c>
       <c r="D21">
-        <v>41309.84249052587</v>
+        <v>41326.33683433748</v>
       </c>
       <c r="E21">
-        <v>-18764.608</v>
+        <v>-18368.44</v>
       </c>
       <c r="F21">
-        <v>7527.192000000001</v>
+        <v>7923.360000000001</v>
       </c>
       <c r="G21">
         <v>2098.5</v>
@@ -3015,28 +3015,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M21">
-        <v>479.2806524985867</v>
+        <v>504.5059499985123</v>
       </c>
       <c r="N21">
-        <v>2916.019347501413</v>
+        <v>2890.794050001487</v>
       </c>
       <c r="O21">
-        <v>612.3640629752966</v>
+        <v>607.0667505003122</v>
       </c>
       <c r="P21">
-        <v>2303.655284526116</v>
+        <v>2283.727299501175</v>
       </c>
       <c r="Q21">
-        <v>4417.355284526116</v>
+        <v>4397.427299501174</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07711727532205556</v>
+        <v>0.07743938561661373</v>
       </c>
       <c r="T21">
-        <v>0.5280542530043161</v>
+        <v>0.5334854953211764</v>
       </c>
       <c r="U21">
         <v>0.06367323332506819</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.084158274070976</v>
+        <v>6.729950360367427</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07201187935865176</v>
+        <v>0.07228344338434578</v>
       </c>
       <c r="C22">
-        <v>35501.47683433748</v>
+        <v>34681.54421147301</v>
       </c>
       <c r="D22">
-        <v>41326.33683433748</v>
+        <v>40902.57221147301</v>
       </c>
       <c r="E22">
-        <v>-18368.44</v>
+        <v>-17972.272</v>
       </c>
       <c r="F22">
-        <v>7923.360000000001</v>
+        <v>8319.528000000002</v>
       </c>
       <c r="G22">
         <v>2098.5</v>
@@ -3097,45 +3097,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M22">
-        <v>504.5059499985123</v>
+        <v>543.8744450984381</v>
       </c>
       <c r="N22">
-        <v>2890.794050001487</v>
+        <v>2851.425554901561</v>
       </c>
       <c r="O22">
-        <v>607.0667505003122</v>
+        <v>598.7993665293278</v>
       </c>
       <c r="P22">
-        <v>2283.727299501175</v>
+        <v>2252.626188372233</v>
       </c>
       <c r="Q22">
-        <v>4397.427299501174</v>
+        <v>4366.326188372233</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07743938561661373</v>
+        <v>0.07776965060217338</v>
       </c>
       <c r="T22">
-        <v>0.5334854953211764</v>
+        <v>0.5390542374435269</v>
       </c>
       <c r="U22">
-        <v>0.06367323332506819</v>
+        <v>0.0653732333250682</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.05030185432680388</v>
+        <v>0.05164485432680388</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.729950360367427</v>
+        <v>6.242801129193467</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07228344338434578</v>
+        <v>0.07228640741003979</v>
       </c>
       <c r="C23">
-        <v>34681.54421147301</v>
+        <v>34280.79890987415</v>
       </c>
       <c r="D23">
-        <v>40902.57221147301</v>
+        <v>40897.99490987416</v>
       </c>
       <c r="E23">
-        <v>-17972.272</v>
+        <v>-17576.104</v>
       </c>
       <c r="F23">
-        <v>8319.528</v>
+        <v>8715.696</v>
       </c>
       <c r="G23">
         <v>2098.5</v>
@@ -3179,28 +3179,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M23">
-        <v>543.8744450984379</v>
+        <v>569.7732281983635</v>
       </c>
       <c r="N23">
-        <v>2851.425554901562</v>
+        <v>2825.526771801636</v>
       </c>
       <c r="O23">
-        <v>598.7993665293279</v>
+        <v>593.3606220783435</v>
       </c>
       <c r="P23">
-        <v>2252.626188372234</v>
+        <v>2232.166149723292</v>
       </c>
       <c r="Q23">
-        <v>4366.326188372233</v>
+        <v>4345.866149723292</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07776965060217338</v>
+        <v>0.07810838392069608</v>
       </c>
       <c r="T23">
-        <v>0.5390542374435269</v>
+        <v>0.5447657678254249</v>
       </c>
       <c r="U23">
         <v>0.0653732333250682</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.242801129193468</v>
+        <v>5.959037441502856</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07228640741003979</v>
+        <v>0.07228937143573382</v>
       </c>
       <c r="C24">
-        <v>34280.79890987415</v>
+        <v>33880.05463262873</v>
       </c>
       <c r="D24">
-        <v>40897.99490987416</v>
+        <v>40893.41863262873</v>
       </c>
       <c r="E24">
-        <v>-17576.104</v>
+        <v>-17179.936</v>
       </c>
       <c r="F24">
-        <v>8715.696</v>
+        <v>9111.864000000001</v>
       </c>
       <c r="G24">
         <v>2098.5</v>
@@ -3261,28 +3261,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M24">
-        <v>569.7732281983635</v>
+        <v>595.6720112982892</v>
       </c>
       <c r="N24">
-        <v>2825.526771801636</v>
+        <v>2799.62798870171</v>
       </c>
       <c r="O24">
-        <v>593.3606220783435</v>
+        <v>587.9218776273591</v>
       </c>
       <c r="P24">
-        <v>2232.166149723292</v>
+        <v>2211.706111074351</v>
       </c>
       <c r="Q24">
-        <v>4345.866149723292</v>
+        <v>4325.406111074351</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07810838392069608</v>
+        <v>0.07845591550723237</v>
       </c>
       <c r="T24">
-        <v>0.5447657678254249</v>
+        <v>0.5506256496458136</v>
       </c>
       <c r="U24">
         <v>0.0653732333250682</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.959037441502856</v>
+        <v>5.699948857089687</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07228937143573382</v>
+        <v>0.07244401546142784</v>
       </c>
       <c r="C25">
-        <v>33880.05463262873</v>
+        <v>33246.53791576975</v>
       </c>
       <c r="D25">
-        <v>40893.41863262873</v>
+        <v>40656.06991576975</v>
       </c>
       <c r="E25">
-        <v>-17179.936</v>
+        <v>-16783.768</v>
       </c>
       <c r="F25">
-        <v>9111.864000000001</v>
+        <v>9508.032000000001</v>
       </c>
       <c r="G25">
         <v>2098.5</v>
@@ -3343,45 +3343,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M25">
-        <v>595.6720112982892</v>
+        <v>629.1772199982148</v>
       </c>
       <c r="N25">
-        <v>2799.62798870171</v>
+        <v>2766.122780001785</v>
       </c>
       <c r="O25">
-        <v>587.9218776273591</v>
+        <v>580.8857838003747</v>
       </c>
       <c r="P25">
-        <v>2211.706111074351</v>
+        <v>2185.23699620141</v>
       </c>
       <c r="Q25">
-        <v>4325.406111074351</v>
+        <v>4298.93699620141</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07845591550723237</v>
+        <v>0.07881259266183541</v>
       </c>
       <c r="T25">
-        <v>0.5506256496458136</v>
+        <v>0.5566397388825285</v>
       </c>
       <c r="U25">
-        <v>0.0653732333250682</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V25">
         <v>0.21</v>
       </c>
       <c r="W25">
-        <v>0.05164485432680388</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.699948857089687</v>
+        <v>5.396412794489974</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07244401546142784</v>
+        <v>0.07245329948712186</v>
       </c>
       <c r="C26">
-        <v>33246.53791576975</v>
+        <v>32836.20836710677</v>
       </c>
       <c r="D26">
-        <v>40656.06991576975</v>
+        <v>40641.90836710677</v>
       </c>
       <c r="E26">
-        <v>-16783.768</v>
+        <v>-16387.6</v>
       </c>
       <c r="F26">
-        <v>9508.032000000001</v>
+        <v>9904.200000000001</v>
       </c>
       <c r="G26">
         <v>2098.5</v>
@@ -3425,28 +3425,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M26">
-        <v>629.1772199982148</v>
+        <v>655.3929374981404</v>
       </c>
       <c r="N26">
-        <v>2766.122780001785</v>
+        <v>2739.907062501859</v>
       </c>
       <c r="O26">
-        <v>580.8857838003747</v>
+        <v>575.3804831253904</v>
       </c>
       <c r="P26">
-        <v>2185.23699620141</v>
+        <v>2164.526579376468</v>
       </c>
       <c r="Q26">
-        <v>4298.93699620141</v>
+        <v>4278.226579376468</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07881259266183541</v>
+        <v>0.07917878120722785</v>
       </c>
       <c r="T26">
-        <v>0.5566397388825285</v>
+        <v>0.5628142038322222</v>
       </c>
       <c r="U26">
         <v>0.06617323332506819</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.396412794489974</v>
+        <v>5.180556282710374</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07245329948712186</v>
+        <v>0.07246258351281587</v>
       </c>
       <c r="C27">
-        <v>32836.20836710677</v>
+        <v>32425.88868066751</v>
       </c>
       <c r="D27">
-        <v>40641.90836710677</v>
+        <v>40627.75668066752</v>
       </c>
       <c r="E27">
-        <v>-16387.6</v>
+        <v>-15991.432</v>
       </c>
       <c r="F27">
-        <v>9904.200000000001</v>
+        <v>10300.368</v>
       </c>
       <c r="G27">
         <v>2098.5</v>
@@ -3507,28 +3507,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M27">
-        <v>655.3929374981404</v>
+        <v>681.6086549980661</v>
       </c>
       <c r="N27">
-        <v>2739.907062501859</v>
+        <v>2713.691345001933</v>
       </c>
       <c r="O27">
-        <v>575.3804831253904</v>
+        <v>569.875182450406</v>
       </c>
       <c r="P27">
-        <v>2164.526579376468</v>
+        <v>2143.816162551527</v>
       </c>
       <c r="Q27">
-        <v>4278.226579376468</v>
+        <v>4257.516162551527</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07917878120722785</v>
+        <v>0.0795548667403336</v>
       </c>
       <c r="T27">
-        <v>0.5628142038322222</v>
+        <v>0.569155546212989</v>
       </c>
       <c r="U27">
         <v>0.06617323332506819</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.180556282710374</v>
+        <v>4.981304117990745</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07246258351281587</v>
+        <v>0.0724718675385099</v>
       </c>
       <c r="C28">
-        <v>32425.88868066751</v>
+        <v>32015.57884615332</v>
       </c>
       <c r="D28">
-        <v>40627.75668066752</v>
+        <v>40613.61484615332</v>
       </c>
       <c r="E28">
-        <v>-15991.432</v>
+        <v>-15595.264</v>
       </c>
       <c r="F28">
-        <v>10300.368</v>
+        <v>10696.536</v>
       </c>
       <c r="G28">
         <v>2098.5</v>
@@ -3589,28 +3589,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M28">
-        <v>681.6086549980661</v>
+        <v>707.8243724979917</v>
       </c>
       <c r="N28">
-        <v>2713.691345001933</v>
+        <v>2687.475627502008</v>
       </c>
       <c r="O28">
-        <v>569.875182450406</v>
+        <v>564.3698817754216</v>
       </c>
       <c r="P28">
-        <v>2143.816162551527</v>
+        <v>2123.105745726586</v>
       </c>
       <c r="Q28">
-        <v>4257.516162551527</v>
+        <v>4236.805745726586</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0795548667403336</v>
+        <v>0.07994125598667515</v>
       </c>
       <c r="T28">
-        <v>0.569155546212989</v>
+        <v>0.575670624001448</v>
       </c>
       <c r="U28">
         <v>0.06617323332506819</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.981304117990745</v>
+        <v>4.796811372879977</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0724718675385099</v>
+        <v>0.07248115156420391</v>
       </c>
       <c r="C29">
-        <v>32015.57884615332</v>
+        <v>31605.27885327996</v>
       </c>
       <c r="D29">
-        <v>40613.61484615332</v>
+        <v>40599.48285327996</v>
       </c>
       <c r="E29">
-        <v>-15595.264</v>
+        <v>-15199.096</v>
       </c>
       <c r="F29">
-        <v>10696.536</v>
+        <v>11092.704</v>
       </c>
       <c r="G29">
         <v>2098.5</v>
@@ -3671,28 +3671,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M29">
-        <v>707.8243724979917</v>
+        <v>734.0400899979173</v>
       </c>
       <c r="N29">
-        <v>2687.475627502008</v>
+        <v>2661.259910002082</v>
       </c>
       <c r="O29">
-        <v>564.3698817754216</v>
+        <v>558.8645811004372</v>
       </c>
       <c r="P29">
-        <v>2123.105745726586</v>
+        <v>2102.395328901645</v>
       </c>
       <c r="Q29">
-        <v>4236.805745726586</v>
+        <v>4216.095328901645</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07994125598667515</v>
+        <v>0.08033837826763726</v>
       </c>
       <c r="T29">
-        <v>0.575670624001448</v>
+        <v>0.5823666761729196</v>
       </c>
       <c r="U29">
         <v>0.06617323332506819</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.796811372879977</v>
+        <v>4.625496680991406</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07248115156420391</v>
+        <v>0.07249043558989793</v>
       </c>
       <c r="C30">
-        <v>31605.27885327996</v>
+        <v>31194.98869177741</v>
       </c>
       <c r="D30">
-        <v>40599.48285327996</v>
+        <v>40585.36069177742</v>
       </c>
       <c r="E30">
-        <v>-15199.096</v>
+        <v>-14802.928</v>
       </c>
       <c r="F30">
-        <v>11092.704</v>
+        <v>11488.872</v>
       </c>
       <c r="G30">
         <v>2098.5</v>
@@ -3753,28 +3753,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M30">
-        <v>734.0400899979173</v>
+        <v>760.2558074978431</v>
       </c>
       <c r="N30">
-        <v>2661.259910002082</v>
+        <v>2635.044192502156</v>
       </c>
       <c r="O30">
-        <v>558.8645811004372</v>
+        <v>553.3592804254528</v>
       </c>
       <c r="P30">
-        <v>2102.395328901645</v>
+        <v>2081.684912076703</v>
       </c>
       <c r="Q30">
-        <v>4216.095328901645</v>
+        <v>4195.384912076703</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08033837826763726</v>
+        <v>0.08074668709172508</v>
       </c>
       <c r="T30">
-        <v>0.5823666761729196</v>
+        <v>0.5892513495323201</v>
       </c>
       <c r="U30">
         <v>0.06617323332506819</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.625496680991406</v>
+        <v>4.465996795439977</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07249043558989793</v>
+        <v>0.07249971961559196</v>
       </c>
       <c r="C31">
-        <v>31194.98869177742</v>
+        <v>30784.70835139</v>
       </c>
       <c r="D31">
-        <v>40585.36069177742</v>
+        <v>40571.24835139</v>
       </c>
       <c r="E31">
-        <v>-14802.928</v>
+        <v>-14406.76</v>
       </c>
       <c r="F31">
-        <v>11488.872</v>
+        <v>11885.04</v>
       </c>
       <c r="G31">
         <v>2098.5</v>
@@ -3835,28 +3835,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M31">
-        <v>760.2558074978429</v>
+        <v>786.4715249977685</v>
       </c>
       <c r="N31">
-        <v>2635.044192502156</v>
+        <v>2608.828475002231</v>
       </c>
       <c r="O31">
-        <v>553.3592804254529</v>
+        <v>547.8539797504684</v>
       </c>
       <c r="P31">
-        <v>2081.684912076704</v>
+        <v>2060.974495251762</v>
       </c>
       <c r="Q31">
-        <v>4195.384912076704</v>
+        <v>4174.674495251762</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08074668709172508</v>
+        <v>0.08116666188221541</v>
       </c>
       <c r="T31">
-        <v>0.5892513495323201</v>
+        <v>0.5963327278448461</v>
       </c>
       <c r="U31">
         <v>0.06617323332506819</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.465996795439978</v>
+        <v>4.317130235591979</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07249971961559196</v>
+        <v>0.07275390364128596</v>
       </c>
       <c r="C32">
-        <v>30784.70835139</v>
+        <v>30005.94036251152</v>
       </c>
       <c r="D32">
-        <v>40571.24835139</v>
+        <v>40188.64836251152</v>
       </c>
       <c r="E32">
-        <v>-14406.76</v>
+        <v>-14010.592</v>
       </c>
       <c r="F32">
-        <v>11885.04</v>
+        <v>12281.208</v>
       </c>
       <c r="G32">
         <v>2098.5</v>
@@ -3917,45 +3917,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M32">
-        <v>786.4715249977685</v>
+        <v>824.9684504976941</v>
       </c>
       <c r="N32">
-        <v>2608.828475002231</v>
+        <v>2570.331549502305</v>
       </c>
       <c r="O32">
-        <v>547.8539797504684</v>
+        <v>539.7696253954841</v>
       </c>
       <c r="P32">
-        <v>2060.974495251762</v>
+        <v>2030.561924106821</v>
       </c>
       <c r="Q32">
-        <v>4174.674495251762</v>
+        <v>4144.261924106821</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08116666188221541</v>
+        <v>0.0815988098550388</v>
       </c>
       <c r="T32">
-        <v>0.5963327278448461</v>
+        <v>0.6036193634997645</v>
       </c>
       <c r="U32">
-        <v>0.06617323332506819</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.05227685432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.317130235591979</v>
+        <v>4.115672542327713</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07275390364128596</v>
+        <v>0.07277108766697998</v>
       </c>
       <c r="C33">
-        <v>30005.94036251152</v>
+        <v>29584.16706343732</v>
       </c>
       <c r="D33">
-        <v>40188.64836251152</v>
+        <v>40163.04306343733</v>
       </c>
       <c r="E33">
-        <v>-14010.592</v>
+        <v>-13614.424</v>
       </c>
       <c r="F33">
-        <v>12281.208</v>
+        <v>12677.376</v>
       </c>
       <c r="G33">
         <v>2098.5</v>
@@ -3999,28 +3999,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M33">
-        <v>824.9684504976941</v>
+        <v>851.5803359976198</v>
       </c>
       <c r="N33">
-        <v>2570.331549502305</v>
+        <v>2543.719664002379</v>
       </c>
       <c r="O33">
-        <v>539.7696253954841</v>
+        <v>534.1811294404997</v>
       </c>
       <c r="P33">
-        <v>2030.561924106821</v>
+        <v>2009.53853456188</v>
       </c>
       <c r="Q33">
-        <v>4144.261924106821</v>
+        <v>4123.23853456188</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0815988098550388</v>
+        <v>0.08204366806235698</v>
       </c>
       <c r="T33">
-        <v>0.6036193634997645</v>
+        <v>0.6111203119680626</v>
       </c>
       <c r="U33">
         <v>0.06717323332506819</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.115672542327713</v>
+        <v>3.987057775379972</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07277108766697998</v>
+        <v>0.072788271692674</v>
       </c>
       <c r="C34">
-        <v>29584.16706343732</v>
+        <v>29162.42637127641</v>
       </c>
       <c r="D34">
-        <v>40163.04306343733</v>
+        <v>40137.47037127641</v>
       </c>
       <c r="E34">
-        <v>-13614.424</v>
+        <v>-13218.256</v>
       </c>
       <c r="F34">
-        <v>12677.376</v>
+        <v>13073.544</v>
       </c>
       <c r="G34">
         <v>2098.5</v>
@@ -4081,28 +4081,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M34">
-        <v>851.5803359976198</v>
+        <v>878.1922214975455</v>
       </c>
       <c r="N34">
-        <v>2543.719664002379</v>
+        <v>2517.107778502454</v>
       </c>
       <c r="O34">
-        <v>534.1811294404997</v>
+        <v>528.5926334855152</v>
       </c>
       <c r="P34">
-        <v>2009.53853456188</v>
+        <v>1988.515145016938</v>
       </c>
       <c r="Q34">
-        <v>4123.23853456188</v>
+        <v>4102.215145016939</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08204366806235698</v>
+        <v>0.08250180561914736</v>
       </c>
       <c r="T34">
-        <v>0.6111203119680626</v>
+        <v>0.6188451693458622</v>
       </c>
       <c r="U34">
         <v>0.06717323332506819</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.987057775379972</v>
+        <v>3.8662378427927</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.072788271692674</v>
+        <v>0.07280545571836802</v>
       </c>
       <c r="C35">
-        <v>29162.42637127641</v>
+        <v>28740.71822378377</v>
       </c>
       <c r="D35">
-        <v>40137.47037127641</v>
+        <v>40111.93022378377</v>
       </c>
       <c r="E35">
-        <v>-13218.256</v>
+        <v>-12822.088</v>
       </c>
       <c r="F35">
-        <v>13073.544</v>
+        <v>13469.712</v>
       </c>
       <c r="G35">
         <v>2098.5</v>
@@ -4163,28 +4163,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M35">
-        <v>878.1922214975455</v>
+        <v>904.8041069974711</v>
       </c>
       <c r="N35">
-        <v>2517.107778502454</v>
+        <v>2490.495893002528</v>
       </c>
       <c r="O35">
-        <v>528.5926334855152</v>
+        <v>523.0041375305309</v>
       </c>
       <c r="P35">
-        <v>1988.515145016938</v>
+        <v>1967.491755471997</v>
       </c>
       <c r="Q35">
-        <v>4102.215145016939</v>
+        <v>4081.191755471997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08250180561914736</v>
+        <v>0.08297382613220411</v>
       </c>
       <c r="T35">
-        <v>0.6188451693458622</v>
+        <v>0.626804113310868</v>
       </c>
       <c r="U35">
         <v>0.06717323332506819</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.8662378427927</v>
+        <v>3.752524965063503</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07280545571836802</v>
+        <v>0.07282263974406204</v>
       </c>
       <c r="C36">
-        <v>28740.71822378377</v>
+        <v>28319.04255887276</v>
       </c>
       <c r="D36">
-        <v>40111.93022378377</v>
+        <v>40086.42255887276</v>
       </c>
       <c r="E36">
-        <v>-12822.088</v>
+        <v>-12425.92</v>
       </c>
       <c r="F36">
-        <v>13469.712</v>
+        <v>13865.88</v>
       </c>
       <c r="G36">
         <v>2098.5</v>
@@ -4245,28 +4245,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M36">
-        <v>904.8041069974711</v>
+        <v>931.4159924973967</v>
       </c>
       <c r="N36">
-        <v>2490.495893002528</v>
+        <v>2463.884007502603</v>
       </c>
       <c r="O36">
-        <v>523.0041375305309</v>
+        <v>517.4156415755466</v>
       </c>
       <c r="P36">
-        <v>1967.491755471997</v>
+        <v>1946.468365927056</v>
       </c>
       <c r="Q36">
-        <v>4081.191755471997</v>
+        <v>4060.168365927056</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08297382613220411</v>
+        <v>0.08346037035335491</v>
       </c>
       <c r="T36">
-        <v>0.626804113310868</v>
+        <v>0.6350079478594123</v>
       </c>
       <c r="U36">
         <v>0.06717323332506819</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.752524965063503</v>
+        <v>3.645309966061689</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07282263974406204</v>
+        <v>0.07283982376975606</v>
       </c>
       <c r="C37">
-        <v>28319.04255887276</v>
+        <v>27897.39931461457</v>
       </c>
       <c r="D37">
-        <v>40086.42255887276</v>
+        <v>40060.94731461458</v>
       </c>
       <c r="E37">
-        <v>-12425.92</v>
+        <v>-12029.752</v>
       </c>
       <c r="F37">
-        <v>13865.88</v>
+        <v>14262.048</v>
       </c>
       <c r="G37">
         <v>2098.5</v>
@@ -4327,28 +4327,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M37">
-        <v>931.4159924973967</v>
+        <v>958.0278779973223</v>
       </c>
       <c r="N37">
-        <v>2463.884007502603</v>
+        <v>2437.272122002677</v>
       </c>
       <c r="O37">
-        <v>517.4156415755466</v>
+        <v>511.8271456205621</v>
       </c>
       <c r="P37">
-        <v>1946.468365927056</v>
+        <v>1925.444976382115</v>
       </c>
       <c r="Q37">
-        <v>4060.168365927056</v>
+        <v>4039.144976382115</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08346037035335491</v>
+        <v>0.08396211908141668</v>
       </c>
       <c r="T37">
-        <v>0.6350079478594123</v>
+        <v>0.6434681522375986</v>
       </c>
       <c r="U37">
         <v>0.06717323332506819</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.645309966061689</v>
+        <v>3.544051355893309</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07283982376975606</v>
+        <v>0.0728570077954501</v>
       </c>
       <c r="C38">
-        <v>27897.39931461457</v>
+        <v>27475.78842923767</v>
       </c>
       <c r="D38">
-        <v>40060.94731461458</v>
+        <v>40035.50442923767</v>
       </c>
       <c r="E38">
-        <v>-12029.752</v>
+        <v>-11633.584</v>
       </c>
       <c r="F38">
-        <v>14262.048</v>
+        <v>14658.216</v>
       </c>
       <c r="G38">
         <v>2098.5</v>
@@ -4409,28 +4409,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M38">
-        <v>958.0278779973222</v>
+        <v>984.6397634972478</v>
       </c>
       <c r="N38">
-        <v>2437.272122002677</v>
+        <v>2410.660236502752</v>
       </c>
       <c r="O38">
-        <v>511.8271456205621</v>
+        <v>506.2386496655778</v>
       </c>
       <c r="P38">
-        <v>1925.444976382115</v>
+        <v>1904.421586837174</v>
       </c>
       <c r="Q38">
-        <v>4039.144976382115</v>
+        <v>4018.121586837174</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08396211908141667</v>
+        <v>0.08447979634052802</v>
       </c>
       <c r="T38">
-        <v>0.6434681522375985</v>
+        <v>0.6521969345325527</v>
       </c>
       <c r="U38">
         <v>0.06717323332506819</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.544051355893309</v>
+        <v>3.448266184112409</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0728570077954501</v>
+        <v>0.0728741918211441</v>
       </c>
       <c r="C39">
-        <v>27475.78842923767</v>
+        <v>27054.20984112744</v>
       </c>
       <c r="D39">
-        <v>40035.50442923767</v>
+        <v>40010.09384112744</v>
       </c>
       <c r="E39">
-        <v>-11633.584</v>
+        <v>-11237.416</v>
       </c>
       <c r="F39">
-        <v>14658.216</v>
+        <v>15054.384</v>
       </c>
       <c r="G39">
         <v>2098.5</v>
@@ -4491,28 +4491,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M39">
-        <v>984.6397634972478</v>
+        <v>1011.251648997174</v>
       </c>
       <c r="N39">
-        <v>2410.660236502752</v>
+        <v>2384.048351002826</v>
       </c>
       <c r="O39">
-        <v>506.2386496655778</v>
+        <v>500.6501537105934</v>
       </c>
       <c r="P39">
-        <v>1904.421586837174</v>
+        <v>1883.398197292232</v>
       </c>
       <c r="Q39">
-        <v>4018.121586837174</v>
+        <v>3997.098197292232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08447979634052802</v>
+        <v>0.0850141728660623</v>
       </c>
       <c r="T39">
-        <v>0.6521969345325527</v>
+        <v>0.6612072904499248</v>
       </c>
       <c r="U39">
         <v>0.06717323332506819</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.448266184112409</v>
+        <v>3.357522337162082</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0728741918211441</v>
+        <v>0.07289137584683812</v>
       </c>
       <c r="C40">
-        <v>27054.20984112744</v>
+        <v>26632.66348882546</v>
       </c>
       <c r="D40">
-        <v>40010.09384112744</v>
+        <v>39984.71548882547</v>
       </c>
       <c r="E40">
-        <v>-11237.416</v>
+        <v>-10841.248</v>
       </c>
       <c r="F40">
-        <v>15054.384</v>
+        <v>15450.552</v>
       </c>
       <c r="G40">
         <v>2098.5</v>
@@ -4573,28 +4573,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M40">
-        <v>1011.251648997174</v>
+        <v>1037.863534497099</v>
       </c>
       <c r="N40">
-        <v>2384.048351002826</v>
+        <v>2357.4364655029</v>
       </c>
       <c r="O40">
-        <v>500.6501537105934</v>
+        <v>495.0616577556091</v>
       </c>
       <c r="P40">
-        <v>1883.398197292232</v>
+        <v>1862.374807747291</v>
       </c>
       <c r="Q40">
-        <v>3997.098197292232</v>
+        <v>3976.074807747291</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0850141728660623</v>
+        <v>0.08556606993341739</v>
       </c>
       <c r="T40">
-        <v>0.6612072904499248</v>
+        <v>0.6705130678727843</v>
       </c>
       <c r="U40">
         <v>0.06717323332506819</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.357522337162082</v>
+        <v>3.271432020824593</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07289137584683812</v>
+        <v>0.07290855987253214</v>
       </c>
       <c r="C41">
-        <v>26632.66348882546</v>
+        <v>26211.14931102927</v>
       </c>
       <c r="D41">
-        <v>39984.71548882547</v>
+        <v>39959.36931102927</v>
       </c>
       <c r="E41">
-        <v>-10841.248</v>
+        <v>-10445.08</v>
       </c>
       <c r="F41">
-        <v>15450.552</v>
+        <v>15846.72</v>
       </c>
       <c r="G41">
         <v>2098.5</v>
@@ -4655,28 +4655,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M41">
-        <v>1037.863534497099</v>
+        <v>1064.475419997025</v>
       </c>
       <c r="N41">
-        <v>2357.4364655029</v>
+        <v>2330.824580002974</v>
       </c>
       <c r="O41">
-        <v>495.0616577556091</v>
+        <v>489.4731618006246</v>
       </c>
       <c r="P41">
-        <v>1862.374807747291</v>
+        <v>1841.35141820235</v>
       </c>
       <c r="Q41">
-        <v>3976.074807747291</v>
+        <v>3955.05141820235</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08556606993341739</v>
+        <v>0.08613636356968432</v>
       </c>
       <c r="T41">
-        <v>0.6705130678727843</v>
+        <v>0.680129037876406</v>
       </c>
       <c r="U41">
         <v>0.06717323332506819</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.271432020824593</v>
+        <v>3.189646220303977</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07290855987253214</v>
+        <v>0.07292574389822616</v>
       </c>
       <c r="C42">
-        <v>26211.14931102927</v>
+        <v>25789.66724659167</v>
       </c>
       <c r="D42">
-        <v>39959.36931102927</v>
+        <v>39934.05524659168</v>
       </c>
       <c r="E42">
-        <v>-10445.08</v>
+        <v>-10048.912</v>
       </c>
       <c r="F42">
-        <v>15846.72</v>
+        <v>16242.888</v>
       </c>
       <c r="G42">
         <v>2098.5</v>
@@ -4737,28 +4737,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M42">
-        <v>1064.475419997025</v>
+        <v>1091.08730549695</v>
       </c>
       <c r="N42">
-        <v>2330.824580002974</v>
+        <v>2304.212694503049</v>
       </c>
       <c r="O42">
-        <v>489.4731618006246</v>
+        <v>483.8846658456402</v>
       </c>
       <c r="P42">
-        <v>1841.35141820235</v>
+        <v>1820.328028657408</v>
       </c>
       <c r="Q42">
-        <v>3955.05141820235</v>
+        <v>3934.028028657408</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08613636356968432</v>
+        <v>0.0867259891936213</v>
       </c>
       <c r="T42">
-        <v>0.680129037876406</v>
+        <v>0.6900709729648959</v>
       </c>
       <c r="U42">
         <v>0.06717323332506819</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.189646220303977</v>
+        <v>3.111849971028271</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07292574389822616</v>
+        <v>0.07294292792392018</v>
       </c>
       <c r="C43">
-        <v>25789.66724659167</v>
+        <v>25368.21723452034</v>
       </c>
       <c r="D43">
-        <v>39934.05524659168</v>
+        <v>39908.77323452034</v>
       </c>
       <c r="E43">
-        <v>-10048.912</v>
+        <v>-9652.743999999995</v>
       </c>
       <c r="F43">
-        <v>16242.888</v>
+        <v>16639.056</v>
       </c>
       <c r="G43">
         <v>2098.5</v>
@@ -4819,28 +4819,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M43">
-        <v>1091.08730549695</v>
+        <v>1117.699190996876</v>
       </c>
       <c r="N43">
-        <v>2304.212694503049</v>
+        <v>2277.600809003123</v>
       </c>
       <c r="O43">
-        <v>483.8846658456402</v>
+        <v>478.2961698906558</v>
       </c>
       <c r="P43">
-        <v>1820.328028657408</v>
+        <v>1799.304639112467</v>
       </c>
       <c r="Q43">
-        <v>3934.028028657408</v>
+        <v>3913.004639112467</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0867259891936213</v>
+        <v>0.08733594673562509</v>
       </c>
       <c r="T43">
-        <v>0.6900709729648959</v>
+        <v>0.7003557334012651</v>
       </c>
       <c r="U43">
         <v>0.06717323332506819</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.111849971028271</v>
+        <v>3.037758305051407</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07294292792392018</v>
+        <v>0.0738093619496142</v>
       </c>
       <c r="C44">
-        <v>25368.21723452034</v>
+        <v>23737.52203906699</v>
       </c>
       <c r="D44">
-        <v>39908.77323452034</v>
+        <v>38674.24603906699</v>
       </c>
       <c r="E44">
-        <v>-9652.743999999999</v>
+        <v>-9256.575999999997</v>
       </c>
       <c r="F44">
-        <v>16639.056</v>
+        <v>17035.224</v>
       </c>
       <c r="G44">
         <v>2098.5</v>
@@ -4901,45 +4901,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M44">
-        <v>1117.699190996876</v>
+        <v>1186.899136496802</v>
       </c>
       <c r="N44">
-        <v>2277.600809003124</v>
+        <v>2208.400863503198</v>
       </c>
       <c r="O44">
-        <v>478.296169890656</v>
+        <v>463.7641813356715</v>
       </c>
       <c r="P44">
-        <v>1799.304639112468</v>
+        <v>1744.636682167526</v>
       </c>
       <c r="Q44">
-        <v>3913.004639112467</v>
+        <v>3858.336682167526</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08733594673562509</v>
+        <v>0.08796730629664654</v>
       </c>
       <c r="T44">
-        <v>0.7003557334012651</v>
+        <v>0.7110013626248751</v>
       </c>
       <c r="U44">
-        <v>0.06717323332506819</v>
+        <v>0.0696732333250682</v>
       </c>
       <c r="V44">
         <v>0.21</v>
       </c>
       <c r="W44">
-        <v>0.05306685432680387</v>
+        <v>0.05504185432680388</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.037758305051408</v>
+        <v>2.860647459919311</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0738093619496142</v>
+        <v>0.07384629597530823</v>
       </c>
       <c r="C45">
-        <v>23737.52203906699</v>
+        <v>23290.42411954529</v>
       </c>
       <c r="D45">
-        <v>38674.24603906699</v>
+        <v>38623.31611954529</v>
       </c>
       <c r="E45">
-        <v>-9256.575999999997</v>
+        <v>-8860.407999999999</v>
       </c>
       <c r="F45">
-        <v>17035.224</v>
+        <v>17431.392</v>
       </c>
       <c r="G45">
         <v>2098.5</v>
@@ -4983,28 +4983,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M45">
-        <v>1186.899136496802</v>
+        <v>1214.501441996727</v>
       </c>
       <c r="N45">
-        <v>2208.400863503198</v>
+        <v>2180.798558003272</v>
       </c>
       <c r="O45">
-        <v>463.7641813356715</v>
+        <v>457.9676971806871</v>
       </c>
       <c r="P45">
-        <v>1744.636682167526</v>
+        <v>1722.830860822585</v>
       </c>
       <c r="Q45">
-        <v>3858.336682167526</v>
+        <v>3836.530860822585</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08796730629664654</v>
+        <v>0.08862121441341878</v>
       </c>
       <c r="T45">
-        <v>0.7110013626248751</v>
+        <v>0.7220271928921858</v>
       </c>
       <c r="U45">
         <v>0.0696732333250682</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.860647459919311</v>
+        <v>2.795632744921145</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07384629597530823</v>
+        <v>0.07388323000100225</v>
       </c>
       <c r="C46">
-        <v>23290.42411954529</v>
+        <v>22843.46016231756</v>
       </c>
       <c r="D46">
-        <v>38623.31611954529</v>
+        <v>38572.52016231756</v>
       </c>
       <c r="E46">
-        <v>-8860.407999999999</v>
+        <v>-8464.239999999998</v>
       </c>
       <c r="F46">
-        <v>17431.392</v>
+        <v>17827.56</v>
       </c>
       <c r="G46">
         <v>2098.5</v>
@@ -5065,28 +5065,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M46">
-        <v>1214.501441996727</v>
+        <v>1242.103747496653</v>
       </c>
       <c r="N46">
-        <v>2180.798558003272</v>
+        <v>2153.196252503346</v>
       </c>
       <c r="O46">
-        <v>457.9676971806871</v>
+        <v>452.1712130257027</v>
       </c>
       <c r="P46">
-        <v>1722.830860822585</v>
+        <v>1701.025039477644</v>
       </c>
       <c r="Q46">
-        <v>3836.530860822585</v>
+        <v>3814.725039477643</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08862121441341878</v>
+        <v>0.08929890100716453</v>
       </c>
       <c r="T46">
-        <v>0.7220271928921858</v>
+        <v>0.7334539624419439</v>
       </c>
       <c r="U46">
         <v>0.0696732333250682</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.795632744921145</v>
+        <v>2.733507572811786</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07388323000100225</v>
+        <v>0.07392016402669625</v>
       </c>
       <c r="C47">
-        <v>22843.46016231756</v>
+        <v>22396.62963953124</v>
       </c>
       <c r="D47">
-        <v>38572.52016231756</v>
+        <v>38521.85763953124</v>
       </c>
       <c r="E47">
-        <v>-8464.239999999998</v>
+        <v>-8068.071999999996</v>
       </c>
       <c r="F47">
-        <v>17827.56</v>
+        <v>18223.728</v>
       </c>
       <c r="G47">
         <v>2098.5</v>
@@ -5147,28 +5147,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M47">
-        <v>1242.103747496653</v>
+        <v>1269.706052996579</v>
       </c>
       <c r="N47">
-        <v>2153.196252503346</v>
+        <v>2125.593947003421</v>
       </c>
       <c r="O47">
-        <v>452.1712130257027</v>
+        <v>446.3747288707184</v>
       </c>
       <c r="P47">
-        <v>1701.025039477644</v>
+        <v>1679.219218132703</v>
       </c>
       <c r="Q47">
-        <v>3814.725039477643</v>
+        <v>3792.919218132703</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08929890100716453</v>
+        <v>0.09000168710438235</v>
       </c>
       <c r="T47">
-        <v>0.7334539624419439</v>
+        <v>0.74530394567873</v>
       </c>
       <c r="U47">
         <v>0.0696732333250682</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.733507572811786</v>
+        <v>2.674083495141965</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07392016402669625</v>
+        <v>0.07395709805239027</v>
       </c>
       <c r="C48">
-        <v>22396.62963953124</v>
+        <v>21949.9320261033</v>
       </c>
       <c r="D48">
-        <v>38521.85763953124</v>
+        <v>38471.3280261033</v>
       </c>
       <c r="E48">
-        <v>-8068.071999999996</v>
+        <v>-7671.903999999995</v>
       </c>
       <c r="F48">
-        <v>18223.728</v>
+        <v>18619.896</v>
       </c>
       <c r="G48">
         <v>2098.5</v>
@@ -5229,28 +5229,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M48">
-        <v>1269.706052996579</v>
+        <v>1297.308358496504</v>
       </c>
       <c r="N48">
-        <v>2125.593947003421</v>
+        <v>2097.991641503495</v>
       </c>
       <c r="O48">
-        <v>446.3747288707184</v>
+        <v>440.5782447157339</v>
       </c>
       <c r="P48">
-        <v>1679.219218132703</v>
+        <v>1657.413396787761</v>
       </c>
       <c r="Q48">
-        <v>3792.919218132703</v>
+        <v>3771.113396787761</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09000168710438235</v>
+        <v>0.09073099343168387</v>
       </c>
       <c r="T48">
-        <v>0.74530394567873</v>
+        <v>0.757601098094263</v>
       </c>
       <c r="U48">
         <v>0.0696732333250682</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.674083495141965</v>
+        <v>2.617188101628305</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07395709805239027</v>
+        <v>0.0739940320780843</v>
       </c>
       <c r="C49">
-        <v>21949.9320261033</v>
+        <v>21503.36679970218</v>
       </c>
       <c r="D49">
-        <v>38471.3280261033</v>
+        <v>38420.93079970218</v>
       </c>
       <c r="E49">
-        <v>-7671.903999999995</v>
+        <v>-7275.735999999997</v>
       </c>
       <c r="F49">
-        <v>18619.896</v>
+        <v>19016.064</v>
       </c>
       <c r="G49">
         <v>2098.5</v>
@@ -5311,28 +5311,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M49">
-        <v>1297.308358496504</v>
+        <v>1324.91066399643</v>
       </c>
       <c r="N49">
-        <v>2097.991641503495</v>
+        <v>2070.389336003569</v>
       </c>
       <c r="O49">
-        <v>440.5782447157339</v>
+        <v>434.7817605607496</v>
       </c>
       <c r="P49">
-        <v>1657.413396787761</v>
+        <v>1635.60757544282</v>
       </c>
       <c r="Q49">
-        <v>3771.113396787761</v>
+        <v>3749.30757544282</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09073099343168387</v>
+        <v>0.09148835000234315</v>
       </c>
       <c r="T49">
-        <v>0.757601098094263</v>
+        <v>0.7703712179103933</v>
       </c>
       <c r="U49">
         <v>0.0696732333250682</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.617188101628305</v>
+        <v>2.562663349511049</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07399403207808429</v>
+        <v>0.07403096610377831</v>
       </c>
       <c r="C50">
-        <v>21503.36679970219</v>
+        <v>21056.93344072979</v>
       </c>
       <c r="D50">
-        <v>38420.9307997022</v>
+        <v>38370.66544072979</v>
       </c>
       <c r="E50">
-        <v>-7275.735999999997</v>
+        <v>-6879.567999999999</v>
       </c>
       <c r="F50">
-        <v>19016.064</v>
+        <v>19412.232</v>
       </c>
       <c r="G50">
         <v>2098.5</v>
@@ -5393,28 +5393,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M50">
-        <v>1324.91066399643</v>
+        <v>1352.512969496355</v>
       </c>
       <c r="N50">
-        <v>2070.389336003569</v>
+        <v>2042.787030503644</v>
       </c>
       <c r="O50">
-        <v>434.7817605607496</v>
+        <v>428.9852764057652</v>
       </c>
       <c r="P50">
-        <v>1635.60757544282</v>
+        <v>1613.801754097879</v>
       </c>
       <c r="Q50">
-        <v>3749.30757544282</v>
+        <v>3727.501754097879</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09148835000234314</v>
+        <v>0.09227540683067531</v>
       </c>
       <c r="T50">
-        <v>0.7703712179103932</v>
+        <v>0.7836421267389208</v>
       </c>
       <c r="U50">
         <v>0.0696732333250682</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.562663349511049</v>
+        <v>2.510364097480212</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07403096610377831</v>
+        <v>0.07545040012947232</v>
       </c>
       <c r="C51">
-        <v>21056.93344072979</v>
+        <v>18823.87191223552</v>
       </c>
       <c r="D51">
-        <v>38370.66544072979</v>
+        <v>36533.77191223552</v>
       </c>
       <c r="E51">
-        <v>-6879.567999999999</v>
+        <v>-6483.399999999998</v>
       </c>
       <c r="F51">
-        <v>19412.232</v>
+        <v>19808.4</v>
       </c>
       <c r="G51">
         <v>2098.5</v>
@@ -5475,45 +5475,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M51">
-        <v>1352.512969496355</v>
+        <v>1449.444674996281</v>
       </c>
       <c r="N51">
-        <v>2042.787030503644</v>
+        <v>1945.855325003718</v>
       </c>
       <c r="O51">
-        <v>428.9852764057652</v>
+        <v>408.6296182507808</v>
       </c>
       <c r="P51">
-        <v>1613.801754097879</v>
+        <v>1537.225706752937</v>
       </c>
       <c r="Q51">
-        <v>3727.501754097879</v>
+        <v>3650.925706752937</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09227540683067531</v>
+        <v>0.09309394593214078</v>
       </c>
       <c r="T51">
-        <v>0.7836421267389208</v>
+        <v>0.7974438719205894</v>
       </c>
       <c r="U51">
-        <v>0.0696732333250682</v>
+        <v>0.0731732333250682</v>
       </c>
       <c r="V51">
         <v>0.21</v>
       </c>
       <c r="W51">
-        <v>0.05504185432680388</v>
+        <v>0.05780685432680388</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.510364097480212</v>
+        <v>2.342483337633229</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07545040012947232</v>
+        <v>0.07551498415516635</v>
       </c>
       <c r="C52">
-        <v>18823.87191223552</v>
+        <v>18348.29959380955</v>
       </c>
       <c r="D52">
-        <v>36533.77191223552</v>
+        <v>36454.36759380955</v>
       </c>
       <c r="E52">
-        <v>-6483.399999999998</v>
+        <v>-6087.231999999996</v>
       </c>
       <c r="F52">
-        <v>19808.4</v>
+        <v>20204.568</v>
       </c>
       <c r="G52">
         <v>2098.5</v>
@@ -5557,28 +5557,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M52">
-        <v>1449.444674996281</v>
+        <v>1478.433568496207</v>
       </c>
       <c r="N52">
-        <v>1945.855325003718</v>
+        <v>1916.866431503792</v>
       </c>
       <c r="O52">
-        <v>408.6296182507808</v>
+        <v>402.5419506157964</v>
       </c>
       <c r="P52">
-        <v>1537.225706752937</v>
+        <v>1514.324480887996</v>
       </c>
       <c r="Q52">
-        <v>3650.925706752937</v>
+        <v>3628.024480887996</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09309394593214078</v>
+        <v>0.09394589479284973</v>
       </c>
       <c r="T52">
-        <v>0.7974438719205894</v>
+        <v>0.8118089536402855</v>
       </c>
       <c r="U52">
         <v>0.0731732333250682</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.342483337633229</v>
+        <v>2.296552291797283</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07551498415516635</v>
+        <v>0.07557956818086037</v>
       </c>
       <c r="C53">
-        <v>18348.29959380955</v>
+        <v>17873.07168941339</v>
       </c>
       <c r="D53">
-        <v>36454.36759380955</v>
+        <v>36375.30768941339</v>
       </c>
       <c r="E53">
-        <v>-6087.231999999996</v>
+        <v>-5691.063999999998</v>
       </c>
       <c r="F53">
-        <v>20204.568</v>
+        <v>20600.736</v>
       </c>
       <c r="G53">
         <v>2098.5</v>
@@ -5639,28 +5639,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M53">
-        <v>1478.433568496207</v>
+        <v>1507.422461996132</v>
       </c>
       <c r="N53">
-        <v>1916.866431503792</v>
+        <v>1887.877538003867</v>
       </c>
       <c r="O53">
-        <v>402.5419506157964</v>
+        <v>396.4542829808121</v>
       </c>
       <c r="P53">
-        <v>1514.324480887996</v>
+        <v>1491.423255023055</v>
       </c>
       <c r="Q53">
-        <v>3628.024480887996</v>
+        <v>3605.123255023055</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09394589479284973</v>
+        <v>0.0948333415227549</v>
       </c>
       <c r="T53">
-        <v>0.8118089536402855</v>
+        <v>0.8267725804316354</v>
       </c>
       <c r="U53">
         <v>0.0731732333250682</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.296552291797283</v>
+        <v>2.252387824647336</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07557956818086037</v>
+        <v>0.07681651220655439</v>
       </c>
       <c r="C54">
-        <v>17873.07168941339</v>
+        <v>16026.24994635025</v>
       </c>
       <c r="D54">
-        <v>36375.30768941339</v>
+        <v>34924.65394635025</v>
       </c>
       <c r="E54">
-        <v>-5691.063999999998</v>
+        <v>-5294.895999999997</v>
       </c>
       <c r="F54">
-        <v>20600.736</v>
+        <v>20996.904</v>
       </c>
       <c r="G54">
         <v>2098.5</v>
@@ -5721,45 +5721,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M54">
-        <v>1507.422461996132</v>
+        <v>1595.202686696058</v>
       </c>
       <c r="N54">
-        <v>1887.877538003867</v>
+        <v>1800.097313303941</v>
       </c>
       <c r="O54">
-        <v>396.4542829808121</v>
+        <v>378.0204357938276</v>
       </c>
       <c r="P54">
-        <v>1491.423255023055</v>
+        <v>1422.076877510114</v>
       </c>
       <c r="Q54">
-        <v>3605.123255023055</v>
+        <v>3535.776877510114</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0948333415227549</v>
+        <v>0.09575855194329433</v>
       </c>
       <c r="T54">
-        <v>0.8267725804316354</v>
+        <v>0.8423729572992129</v>
       </c>
       <c r="U54">
-        <v>0.0731732333250682</v>
+        <v>0.0759732333250682</v>
       </c>
       <c r="V54">
         <v>0.21</v>
       </c>
       <c r="W54">
-        <v>0.05780685432680388</v>
+        <v>0.06001885432680388</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.252387824647336</v>
+        <v>2.128444258724423</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07681651220655439</v>
+        <v>0.0769032162322484</v>
       </c>
       <c r="C55">
-        <v>16026.24994635025</v>
+        <v>15532.72519486488</v>
       </c>
       <c r="D55">
-        <v>34924.65394635025</v>
+        <v>34827.29719486488</v>
       </c>
       <c r="E55">
-        <v>-5294.895999999997</v>
+        <v>-4898.727999999996</v>
       </c>
       <c r="F55">
-        <v>20996.904</v>
+        <v>21393.072</v>
       </c>
       <c r="G55">
         <v>2098.5</v>
@@ -5803,28 +5803,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M55">
-        <v>1595.202686696058</v>
+        <v>1625.300850595984</v>
       </c>
       <c r="N55">
-        <v>1800.097313303941</v>
+        <v>1769.999149404016</v>
       </c>
       <c r="O55">
-        <v>378.0204357938276</v>
+        <v>371.6998213748433</v>
       </c>
       <c r="P55">
-        <v>1422.076877510114</v>
+        <v>1398.299328029173</v>
       </c>
       <c r="Q55">
-        <v>3535.776877510114</v>
+        <v>3511.999328029172</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09575855194329433</v>
+        <v>0.09672398890385719</v>
       </c>
       <c r="T55">
-        <v>0.8423729572992129</v>
+        <v>0.8586516114219026</v>
       </c>
       <c r="U55">
         <v>0.0759732333250682</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.128444258724423</v>
+        <v>2.089028624303601</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0769032162322484</v>
+        <v>0.07698992025794243</v>
       </c>
       <c r="C56">
-        <v>15532.72519486488</v>
+        <v>15039.74172224217</v>
       </c>
       <c r="D56">
-        <v>34827.29719486488</v>
+        <v>34730.48172224217</v>
       </c>
       <c r="E56">
-        <v>-4898.727999999996</v>
+        <v>-4502.559999999998</v>
       </c>
       <c r="F56">
-        <v>21393.072</v>
+        <v>21789.24</v>
       </c>
       <c r="G56">
         <v>2098.5</v>
@@ -5885,28 +5885,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M56">
-        <v>1625.300850595984</v>
+        <v>1655.399014495909</v>
       </c>
       <c r="N56">
-        <v>1769.999149404016</v>
+        <v>1739.90098550409</v>
       </c>
       <c r="O56">
-        <v>371.6998213748433</v>
+        <v>365.3792069558589</v>
       </c>
       <c r="P56">
-        <v>1398.299328029173</v>
+        <v>1374.521778548231</v>
       </c>
       <c r="Q56">
-        <v>3511.999328029172</v>
+        <v>3488.221778548231</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09672398890385719</v>
+        <v>0.09773233417377844</v>
       </c>
       <c r="T56">
-        <v>0.8586516114219026</v>
+        <v>0.8756537612833786</v>
       </c>
       <c r="U56">
         <v>0.0759732333250682</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.089028624303601</v>
+        <v>2.051046285679899</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07698992025794243</v>
+        <v>0.07707662428363644</v>
       </c>
       <c r="C57">
-        <v>15039.74172224217</v>
+        <v>14547.29502693597</v>
       </c>
       <c r="D57">
-        <v>34730.48172224217</v>
+        <v>34634.20302693597</v>
       </c>
       <c r="E57">
-        <v>-4502.559999999998</v>
+        <v>-4106.391999999996</v>
       </c>
       <c r="F57">
-        <v>21789.24</v>
+        <v>22185.408</v>
       </c>
       <c r="G57">
         <v>2098.5</v>
@@ -5967,28 +5967,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M57">
-        <v>1655.399014495909</v>
+        <v>1685.497178395835</v>
       </c>
       <c r="N57">
-        <v>1739.90098550409</v>
+        <v>1709.802821604165</v>
       </c>
       <c r="O57">
-        <v>365.3792069558589</v>
+        <v>359.0585925368745</v>
       </c>
       <c r="P57">
-        <v>1374.521778548231</v>
+        <v>1350.74422906729</v>
       </c>
       <c r="Q57">
-        <v>3488.221778548231</v>
+        <v>3464.44422906729</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09773233417377844</v>
+        <v>0.09878651331960517</v>
       </c>
       <c r="T57">
-        <v>0.8756537612833786</v>
+        <v>0.8934287361385579</v>
       </c>
       <c r="U57">
         <v>0.0759732333250682</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.051046285679899</v>
+        <v>2.014420459149901</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07707662428363644</v>
+        <v>0.08067566830933047</v>
       </c>
       <c r="C58">
-        <v>14547.29502693597</v>
+        <v>10577.00135332359</v>
       </c>
       <c r="D58">
-        <v>34634.20302693597</v>
+        <v>31060.07735332359</v>
       </c>
       <c r="E58">
-        <v>-4106.391999999996</v>
+        <v>-3710.223999999995</v>
       </c>
       <c r="F58">
-        <v>22185.408</v>
+        <v>22581.576</v>
       </c>
       <c r="G58">
         <v>2098.5</v>
@@ -6049,45 +6049,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M58">
-        <v>1685.497178395835</v>
+        <v>1891.731635095761</v>
       </c>
       <c r="N58">
-        <v>1709.802821604165</v>
+        <v>1503.568364904239</v>
       </c>
       <c r="O58">
-        <v>359.0585925368745</v>
+        <v>315.7493566298901</v>
       </c>
       <c r="P58">
-        <v>1350.74422906729</v>
+        <v>1187.819008274349</v>
       </c>
       <c r="Q58">
-        <v>3464.44422906729</v>
+        <v>3301.519008274348</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09878651331960517</v>
+        <v>0.09988972405360991</v>
       </c>
       <c r="T58">
-        <v>0.8934287361385579</v>
+        <v>0.9120304540102573</v>
       </c>
       <c r="U58">
-        <v>0.0759732333250682</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V58">
         <v>0.21</v>
       </c>
       <c r="W58">
-        <v>0.06001885432680388</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.014420459149901</v>
+        <v>1.794810604744223</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08067566830933047</v>
+        <v>0.08082399233502448</v>
       </c>
       <c r="C59">
-        <v>10577.00135332359</v>
+        <v>10049.29621537129</v>
       </c>
       <c r="D59">
-        <v>31060.07735332359</v>
+        <v>30928.54021537129</v>
       </c>
       <c r="E59">
-        <v>-3710.223999999995</v>
+        <v>-3314.055999999993</v>
       </c>
       <c r="F59">
-        <v>22581.576</v>
+        <v>22977.74400000001</v>
       </c>
       <c r="G59">
         <v>2098.5</v>
@@ -6131,28 +6131,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M59">
-        <v>1891.731635095761</v>
+        <v>1924.919909395686</v>
       </c>
       <c r="N59">
-        <v>1503.568364904239</v>
+        <v>1470.380090604313</v>
       </c>
       <c r="O59">
-        <v>315.7493566298901</v>
+        <v>308.7798190269057</v>
       </c>
       <c r="P59">
-        <v>1187.819008274349</v>
+        <v>1161.600271577407</v>
       </c>
       <c r="Q59">
-        <v>3301.519008274348</v>
+        <v>3275.300271577407</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09988972405360991</v>
+        <v>0.101045468632091</v>
       </c>
       <c r="T59">
-        <v>0.9120304540102573</v>
+        <v>0.9315179679710851</v>
       </c>
       <c r="U59">
         <v>0.0837732333250682</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.794810604744223</v>
+        <v>1.763865594317598</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08082399233502446</v>
+        <v>0.0827901063607185</v>
       </c>
       <c r="C60">
-        <v>10049.29621537131</v>
+        <v>8009.201157722735</v>
       </c>
       <c r="D60">
-        <v>30928.5402153713</v>
+        <v>29284.61315772274</v>
       </c>
       <c r="E60">
-        <v>-3314.056</v>
+        <v>-2917.887999999999</v>
       </c>
       <c r="F60">
-        <v>22977.744</v>
+        <v>23373.912</v>
       </c>
       <c r="G60">
         <v>2098.5</v>
@@ -6213,45 +6213,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M60">
-        <v>1924.919909395686</v>
+        <v>2049.266440495611</v>
       </c>
       <c r="N60">
-        <v>1470.380090604314</v>
+        <v>1346.033559504388</v>
       </c>
       <c r="O60">
-        <v>308.7798190269058</v>
+        <v>282.6670474959215</v>
       </c>
       <c r="P60">
-        <v>1161.600271577408</v>
+        <v>1063.366512008467</v>
       </c>
       <c r="Q60">
-        <v>3275.300271577407</v>
+        <v>3177.066512008466</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.101045468632091</v>
+        <v>0.1022575909948883</v>
       </c>
       <c r="T60">
-        <v>0.9315179679710849</v>
+        <v>0.9519560923690262</v>
       </c>
       <c r="U60">
-        <v>0.0837732333250682</v>
+        <v>0.0876732333250682</v>
       </c>
       <c r="V60">
         <v>0.21</v>
       </c>
       <c r="W60">
-        <v>0.06618085432680387</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.763865594317599</v>
+        <v>1.656836774811406</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0827901063607185</v>
+        <v>0.08296924038641251</v>
       </c>
       <c r="C61">
-        <v>8009.201157722735</v>
+        <v>7471.898429347912</v>
       </c>
       <c r="D61">
-        <v>29284.61315772274</v>
+        <v>29143.47842934791</v>
       </c>
       <c r="E61">
-        <v>-2917.887999999999</v>
+        <v>-2521.719999999998</v>
       </c>
       <c r="F61">
-        <v>23373.912</v>
+        <v>23770.08</v>
       </c>
       <c r="G61">
         <v>2098.5</v>
@@ -6295,28 +6295,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M61">
-        <v>2049.266440495611</v>
+        <v>2083.999769995537</v>
       </c>
       <c r="N61">
-        <v>1346.033559504388</v>
+        <v>1311.300230004462</v>
       </c>
       <c r="O61">
-        <v>282.6670474959215</v>
+        <v>275.3730483009371</v>
       </c>
       <c r="P61">
-        <v>1063.366512008467</v>
+        <v>1035.927181703525</v>
       </c>
       <c r="Q61">
-        <v>3177.066512008466</v>
+        <v>3149.627181703525</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1022575909948883</v>
+        <v>0.1035303194758255</v>
       </c>
       <c r="T61">
-        <v>0.9519560923690262</v>
+        <v>0.9734161229868645</v>
       </c>
       <c r="U61">
         <v>0.0876732333250682</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.656836774811406</v>
+        <v>1.629222828564549</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08296924038641251</v>
+        <v>0.08314837441210654</v>
       </c>
       <c r="C62">
-        <v>7471.898429347912</v>
+        <v>6935.949550100766</v>
       </c>
       <c r="D62">
-        <v>29143.47842934791</v>
+        <v>29003.69755010077</v>
       </c>
       <c r="E62">
-        <v>-2521.719999999998</v>
+        <v>-2125.552</v>
       </c>
       <c r="F62">
-        <v>23770.08</v>
+        <v>24166.248</v>
       </c>
       <c r="G62">
         <v>2098.5</v>
@@ -6377,28 +6377,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M62">
-        <v>2083.999769995537</v>
+        <v>2118.733099495463</v>
       </c>
       <c r="N62">
-        <v>1311.300230004462</v>
+        <v>1276.566900504537</v>
       </c>
       <c r="O62">
-        <v>275.3730483009371</v>
+        <v>268.0790491059527</v>
       </c>
       <c r="P62">
-        <v>1035.927181703525</v>
+        <v>1008.487851398584</v>
       </c>
       <c r="Q62">
-        <v>3149.627181703525</v>
+        <v>3122.187851398584</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1035303194758255</v>
+        <v>0.1048683160839902</v>
       </c>
       <c r="T62">
-        <v>0.9734161229868645</v>
+        <v>0.9959766679953616</v>
       </c>
       <c r="U62">
         <v>0.0876732333250682</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.629222828564549</v>
+        <v>1.602514257604475</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08314837441210654</v>
+        <v>0.08332750843780055</v>
       </c>
       <c r="C63">
-        <v>6935.949550100766</v>
+        <v>6401.335132567543</v>
       </c>
       <c r="D63">
-        <v>29003.69755010077</v>
+        <v>28865.25113256754</v>
       </c>
       <c r="E63">
-        <v>-2125.552</v>
+        <v>-1729.383999999998</v>
       </c>
       <c r="F63">
-        <v>24166.248</v>
+        <v>24562.416</v>
       </c>
       <c r="G63">
         <v>2098.5</v>
@@ -6459,28 +6459,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M63">
-        <v>2118.733099495463</v>
+        <v>2153.466428995388</v>
       </c>
       <c r="N63">
-        <v>1276.566900504537</v>
+        <v>1241.833571004611</v>
       </c>
       <c r="O63">
-        <v>268.0790491059527</v>
+        <v>260.7850499109683</v>
       </c>
       <c r="P63">
-        <v>1008.487851398584</v>
+        <v>981.0485210936425</v>
       </c>
       <c r="Q63">
-        <v>3122.187851398584</v>
+        <v>3094.748521093642</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1048683160839902</v>
+        <v>0.1062767335662688</v>
       </c>
       <c r="T63">
-        <v>0.9959766679953616</v>
+        <v>1.019724610109569</v>
       </c>
       <c r="U63">
         <v>0.0876732333250682</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.602514257604475</v>
+        <v>1.576667253449564</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08332750843780055</v>
+        <v>0.08350664246349457</v>
       </c>
       <c r="C64">
-        <v>6401.335132567543</v>
+        <v>5868.036157751852</v>
       </c>
       <c r="D64">
-        <v>28865.25113256754</v>
+        <v>28728.12015775186</v>
       </c>
       <c r="E64">
-        <v>-1729.383999999998</v>
+        <v>-1333.215999999997</v>
       </c>
       <c r="F64">
-        <v>24562.416</v>
+        <v>24958.584</v>
       </c>
       <c r="G64">
         <v>2098.5</v>
@@ -6541,28 +6541,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M64">
-        <v>2153.466428995388</v>
+        <v>2188.199758495314</v>
       </c>
       <c r="N64">
-        <v>1241.833571004611</v>
+        <v>1207.100241504685</v>
       </c>
       <c r="O64">
-        <v>260.7850499109683</v>
+        <v>253.4910507159838</v>
       </c>
       <c r="P64">
-        <v>981.0485210936425</v>
+        <v>953.6091907887012</v>
       </c>
       <c r="Q64">
-        <v>3094.748521093642</v>
+        <v>3067.309190788701</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1062767335662688</v>
+        <v>0.1077612817232652</v>
       </c>
       <c r="T64">
-        <v>1.019724610109569</v>
+        <v>1.04475622477049</v>
       </c>
       <c r="U64">
         <v>0.0876732333250682</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.576667253449564</v>
+        <v>1.551640789109094</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08350664246349457</v>
+        <v>0.0836857764891886</v>
       </c>
       <c r="C65">
-        <v>5868.036157751852</v>
+        <v>5336.033966364794</v>
       </c>
       <c r="D65">
-        <v>28728.12015775186</v>
+        <v>28592.2859663648</v>
       </c>
       <c r="E65">
-        <v>-1333.215999999997</v>
+        <v>-937.0479999999952</v>
       </c>
       <c r="F65">
-        <v>24958.584</v>
+        <v>25354.752</v>
       </c>
       <c r="G65">
         <v>2098.5</v>
@@ -6623,28 +6623,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M65">
-        <v>2188.199758495314</v>
+        <v>2222.93308799524</v>
       </c>
       <c r="N65">
-        <v>1207.100241504685</v>
+        <v>1172.366912004759</v>
       </c>
       <c r="O65">
-        <v>253.4910507159838</v>
+        <v>246.1970515209995</v>
       </c>
       <c r="P65">
-        <v>953.6091907887012</v>
+        <v>926.1698604837599</v>
       </c>
       <c r="Q65">
-        <v>3067.309190788701</v>
+        <v>3039.86986048376</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1077612817232652</v>
+        <v>0.1093283047778725</v>
       </c>
       <c r="T65">
-        <v>1.04475622477049</v>
+        <v>1.071178484690351</v>
       </c>
       <c r="U65">
         <v>0.0876732333250682</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.551640789109094</v>
+        <v>1.527396401779265</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0836857764891886</v>
+        <v>0.08386491051488261</v>
       </c>
       <c r="C66">
-        <v>5336.033966364794</v>
+        <v>4805.310250361028</v>
       </c>
       <c r="D66">
-        <v>28592.2859663648</v>
+        <v>28457.73025036103</v>
       </c>
       <c r="E66">
-        <v>-937.0479999999952</v>
+        <v>-540.8799999999974</v>
       </c>
       <c r="F66">
-        <v>25354.752</v>
+        <v>25750.92</v>
       </c>
       <c r="G66">
         <v>2098.5</v>
@@ -6705,28 +6705,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M66">
-        <v>2222.93308799524</v>
+        <v>2257.666417495165</v>
       </c>
       <c r="N66">
-        <v>1172.366912004759</v>
+        <v>1137.633582504834</v>
       </c>
       <c r="O66">
-        <v>246.1970515209995</v>
+        <v>238.9030523260151</v>
       </c>
       <c r="P66">
-        <v>926.1698604837599</v>
+        <v>898.730530178819</v>
       </c>
       <c r="Q66">
-        <v>3039.86986048376</v>
+        <v>3012.430530178819</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1093283047778725</v>
+        <v>0.1109848720070288</v>
       </c>
       <c r="T66">
-        <v>1.071178484690351</v>
+        <v>1.099110588034204</v>
       </c>
       <c r="U66">
         <v>0.0876732333250682</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.527396401779265</v>
+        <v>1.503897995598046</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08386491051488261</v>
+        <v>0.09144792454057663</v>
       </c>
       <c r="C67">
-        <v>4805.310250361028</v>
+        <v>-318.2439298383215</v>
       </c>
       <c r="D67">
-        <v>28457.73025036103</v>
+        <v>23730.34407016168</v>
       </c>
       <c r="E67">
-        <v>-540.8799999999974</v>
+        <v>-144.7119999999959</v>
       </c>
       <c r="F67">
-        <v>25750.92</v>
+        <v>26147.088</v>
       </c>
       <c r="G67">
         <v>2098.5</v>
@@ -6787,45 +6787,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M67">
-        <v>2257.666417495165</v>
+        <v>2663.688396595091</v>
       </c>
       <c r="N67">
-        <v>1137.633582504834</v>
+        <v>731.6116034049082</v>
       </c>
       <c r="O67">
-        <v>238.9030523260151</v>
+        <v>153.6384367150307</v>
       </c>
       <c r="P67">
-        <v>898.730530178819</v>
+        <v>577.9731666898775</v>
       </c>
       <c r="Q67">
-        <v>3012.430530178819</v>
+        <v>2691.673166689877</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1109848720070288</v>
+        <v>0.112738884367312</v>
       </c>
       <c r="T67">
-        <v>1.099110588034204</v>
+        <v>1.128685756280637</v>
       </c>
       <c r="U67">
-        <v>0.0876732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V67">
         <v>0.21</v>
       </c>
       <c r="W67">
-        <v>0.06926185432680387</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.503897995598046</v>
+        <v>1.274661106884763</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09144792454057663</v>
+        <v>0.09173923856627066</v>
       </c>
       <c r="C68">
-        <v>-318.2439298383215</v>
+        <v>-864.8929190304007</v>
       </c>
       <c r="D68">
-        <v>23730.34407016168</v>
+        <v>23579.8630809696</v>
       </c>
       <c r="E68">
-        <v>-144.7119999999959</v>
+        <v>251.4560000000056</v>
       </c>
       <c r="F68">
-        <v>26147.088</v>
+        <v>26543.256</v>
       </c>
       <c r="G68">
         <v>2098.5</v>
@@ -6869,28 +6869,28 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M68">
-        <v>2663.688396595091</v>
+        <v>2704.047311695017</v>
       </c>
       <c r="N68">
-        <v>731.6116034049082</v>
+        <v>691.2526883049823</v>
       </c>
       <c r="O68">
-        <v>153.6384367150307</v>
+        <v>145.1630645440463</v>
       </c>
       <c r="P68">
-        <v>577.9731666898775</v>
+        <v>546.089623760936</v>
       </c>
       <c r="Q68">
-        <v>2691.673166689877</v>
+        <v>2659.789623760936</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.112738884367312</v>
+        <v>0.1145992005070062</v>
       </c>
       <c r="T68">
-        <v>1.128685756280637</v>
+        <v>1.160053358966248</v>
       </c>
       <c r="U68">
         <v>0.1018732333250682</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.274661106884763</v>
+        <v>1.255636314244692</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09173923856627066</v>
+        <v>0.108156660175534</v>
       </c>
       <c r="C69">
-        <v>-864.8929190304007</v>
+        <v>-7469.227818913067</v>
       </c>
       <c r="D69">
-        <v>23579.8630809696</v>
+        <v>17371.69618108694</v>
       </c>
       <c r="E69">
-        <v>251.4560000000056</v>
+        <v>647.6240000000034</v>
       </c>
       <c r="F69">
-        <v>26543.256</v>
+        <v>26939.424</v>
       </c>
       <c r="G69">
         <v>2098.5</v>
@@ -6951,45 +6951,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M69">
-        <v>2704.047311695017</v>
+        <v>3514.873753194943</v>
       </c>
       <c r="N69">
-        <v>691.2526883049823</v>
+        <v>-119.5737531949435</v>
       </c>
       <c r="O69">
-        <v>145.1630645440463</v>
+        <v>-25.11048817093813</v>
       </c>
       <c r="P69">
-        <v>546.089623760936</v>
+        <v>-94.46326502400535</v>
       </c>
       <c r="Q69">
-        <v>2659.789623760936</v>
+        <v>2019.236734975995</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1145992005070062</v>
+        <v>0.1169768903002604</v>
       </c>
       <c r="T69">
-        <v>1.160053358966248</v>
+        <v>1.20014462472105</v>
       </c>
       <c r="U69">
-        <v>0.1018732333250682</v>
+        <v>0.1304732333250682</v>
       </c>
       <c r="V69">
-        <v>0.21</v>
+        <v>0.2028559345415711</v>
       </c>
       <c r="W69">
-        <v>0.08047985432680388</v>
+        <v>0.104005963646251</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.255636314244692</v>
+        <v>0.9659806406741483</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.108156660175534</v>
+        <v>0.1090033925087847</v>
       </c>
       <c r="C70">
-        <v>-7469.227818913067</v>
+        <v>-8098.123466212852</v>
       </c>
       <c r="D70">
-        <v>17371.69618108694</v>
+        <v>17138.96853378715</v>
       </c>
       <c r="E70">
-        <v>647.6240000000034</v>
+        <v>1043.792000000005</v>
       </c>
       <c r="F70">
-        <v>26939.424</v>
+        <v>27335.592</v>
       </c>
       <c r="G70">
         <v>2098.5</v>
@@ -7033,37 +7033,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M70">
-        <v>3514.873753194943</v>
+        <v>3566.563073094869</v>
       </c>
       <c r="N70">
-        <v>-119.5737531949435</v>
+        <v>-171.2630730948695</v>
       </c>
       <c r="O70">
-        <v>-25.11048817093813</v>
+        <v>-35.96524534992259</v>
       </c>
       <c r="P70">
-        <v>-94.46326502400535</v>
+        <v>-135.2978277449469</v>
       </c>
       <c r="Q70">
-        <v>2019.236734975995</v>
+        <v>1978.402172255053</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1169768903002604</v>
+        <v>0.1192729190196237</v>
       </c>
       <c r="T70">
-        <v>1.20014462472105</v>
+        <v>1.238858967453987</v>
       </c>
       <c r="U70">
         <v>0.1304732333250682</v>
       </c>
       <c r="V70">
-        <v>0.2028559345415711</v>
+        <v>0.1999159934612585</v>
       </c>
       <c r="W70">
-        <v>0.104005963646251</v>
+        <v>0.1043895472647846</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9659806406741483</v>
+        <v>0.9519809212440882</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1090033925087847</v>
+        <v>0.1098501248420354</v>
       </c>
       <c r="C71">
-        <v>-8098.123466212852</v>
+        <v>-8720.865869493315</v>
       </c>
       <c r="D71">
-        <v>17138.96853378715</v>
+        <v>16912.39413050669</v>
       </c>
       <c r="E71">
-        <v>1043.792000000005</v>
+        <v>1439.960000000006</v>
       </c>
       <c r="F71">
-        <v>27335.592</v>
+        <v>27731.76000000001</v>
       </c>
       <c r="G71">
         <v>2098.5</v>
@@ -7115,37 +7115,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M71">
-        <v>3566.563073094869</v>
+        <v>3618.252392994795</v>
       </c>
       <c r="N71">
-        <v>-171.2630730948695</v>
+        <v>-222.9523929947954</v>
       </c>
       <c r="O71">
-        <v>-35.96524534992259</v>
+        <v>-46.82000252890704</v>
       </c>
       <c r="P71">
-        <v>-135.2978277449469</v>
+        <v>-176.1323904658884</v>
       </c>
       <c r="Q71">
-        <v>1978.402172255053</v>
+        <v>1937.567609534111</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1192729190196237</v>
+        <v>0.1217220163202778</v>
       </c>
       <c r="T71">
-        <v>1.238858967453987</v>
+        <v>1.28015426636912</v>
       </c>
       <c r="U71">
         <v>0.1304732333250682</v>
       </c>
       <c r="V71">
-        <v>0.1999159934612585</v>
+        <v>0.1970600506975262</v>
       </c>
       <c r="W71">
-        <v>0.1043895472647846</v>
+        <v>0.1047621713513601</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9519809212440882</v>
+        <v>0.938381193797744</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1098501248420354</v>
+        <v>0.1106968571752861</v>
       </c>
       <c r="C72">
-        <v>-8720.865869493315</v>
+        <v>-9337.695879431634</v>
       </c>
       <c r="D72">
-        <v>16912.39413050669</v>
+        <v>16691.73212056837</v>
       </c>
       <c r="E72">
-        <v>1439.960000000006</v>
+        <v>1836.128000000004</v>
       </c>
       <c r="F72">
-        <v>27731.76000000001</v>
+        <v>28127.928</v>
       </c>
       <c r="G72">
         <v>2098.5</v>
@@ -7197,37 +7197,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M72">
-        <v>3618.252392994795</v>
+        <v>3669.94171289472</v>
       </c>
       <c r="N72">
-        <v>-222.9523929947954</v>
+        <v>-274.6417128947205</v>
       </c>
       <c r="O72">
-        <v>-46.82000252890704</v>
+        <v>-57.6747597078913</v>
       </c>
       <c r="P72">
-        <v>-176.1323904658884</v>
+        <v>-216.9669531868292</v>
       </c>
       <c r="Q72">
-        <v>1937.567609534111</v>
+        <v>1896.733046813171</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1217220163202778</v>
+        <v>0.124340016883046</v>
       </c>
       <c r="T72">
-        <v>1.28015426636912</v>
+        <v>1.324297516933572</v>
       </c>
       <c r="U72">
         <v>0.1304732333250682</v>
       </c>
       <c r="V72">
-        <v>0.1970600506975262</v>
+        <v>0.1942845570257301</v>
       </c>
       <c r="W72">
-        <v>0.1047621713513601</v>
+        <v>0.1051242989847926</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.938381193797744</v>
+        <v>0.9251645572653815</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1106968571752861</v>
+        <v>0.1115435895085368</v>
       </c>
       <c r="C73">
-        <v>-9337.695879431631</v>
+        <v>-9948.841938738984</v>
       </c>
       <c r="D73">
-        <v>16691.73212056837</v>
+        <v>16476.75406126102</v>
       </c>
       <c r="E73">
-        <v>1836.128000000001</v>
+        <v>2232.296000000002</v>
       </c>
       <c r="F73">
-        <v>28127.928</v>
+        <v>28524.096</v>
       </c>
       <c r="G73">
         <v>2098.5</v>
@@ -7279,37 +7279,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M73">
-        <v>3669.941712894719</v>
+        <v>3721.631032794645</v>
       </c>
       <c r="N73">
-        <v>-274.6417128947201</v>
+        <v>-326.331032794646</v>
       </c>
       <c r="O73">
-        <v>-57.67475970789121</v>
+        <v>-68.52951688687567</v>
       </c>
       <c r="P73">
-        <v>-216.9669531868288</v>
+        <v>-257.8015159077704</v>
       </c>
       <c r="Q73">
-        <v>1896.733046813171</v>
+        <v>1855.898484092229</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.124340016883046</v>
+        <v>0.1271450174860119</v>
       </c>
       <c r="T73">
-        <v>1.324297516933572</v>
+        <v>1.371593856824057</v>
       </c>
       <c r="U73">
         <v>0.1304732333250682</v>
       </c>
       <c r="V73">
-        <v>0.1942845570257301</v>
+        <v>0.1915861604003728</v>
       </c>
       <c r="W73">
-        <v>0.1051242989847926</v>
+        <v>0.1054763675172964</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9251645572653816</v>
+        <v>0.9123150495255845</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1115435895085368</v>
+        <v>0.1123903218417875</v>
       </c>
       <c r="C74">
-        <v>-9948.841938738984</v>
+        <v>-10554.52087103087</v>
       </c>
       <c r="D74">
-        <v>16476.75406126102</v>
+        <v>16267.24312896913</v>
       </c>
       <c r="E74">
-        <v>2232.296000000002</v>
+        <v>2628.464000000004</v>
       </c>
       <c r="F74">
-        <v>28524.096</v>
+        <v>28920.264</v>
       </c>
       <c r="G74">
         <v>2098.5</v>
@@ -7361,37 +7361,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M74">
-        <v>3721.631032794645</v>
+        <v>3773.320352694571</v>
       </c>
       <c r="N74">
-        <v>-326.331032794646</v>
+        <v>-378.0203526945716</v>
       </c>
       <c r="O74">
-        <v>-68.52951688687567</v>
+        <v>-79.38427406586003</v>
       </c>
       <c r="P74">
-        <v>-257.8015159077704</v>
+        <v>-298.6360786287115</v>
       </c>
       <c r="Q74">
-        <v>1855.898484092229</v>
+        <v>1815.063921371288</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1271450174860119</v>
+        <v>0.1301577959114197</v>
       </c>
       <c r="T74">
-        <v>1.371593856824057</v>
+        <v>1.422393629299022</v>
       </c>
       <c r="U74">
         <v>0.1304732333250682</v>
       </c>
       <c r="V74">
-        <v>0.1915861604003728</v>
+        <v>0.1889616924496827</v>
       </c>
       <c r="W74">
-        <v>0.1054763675172964</v>
+        <v>0.105818790336581</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9123150495255845</v>
+        <v>0.8998175830937273</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1123903218417875</v>
+        <v>0.1132370541750381</v>
       </c>
       <c r="C75">
-        <v>-10554.52087103087</v>
+        <v>-11154.93861026764</v>
       </c>
       <c r="D75">
-        <v>16267.24312896913</v>
+        <v>16062.99338973236</v>
       </c>
       <c r="E75">
-        <v>2628.464000000004</v>
+        <v>3024.632000000001</v>
       </c>
       <c r="F75">
-        <v>28920.264</v>
+        <v>29316.432</v>
       </c>
       <c r="G75">
         <v>2098.5</v>
@@ -7443,37 +7443,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M75">
-        <v>3773.320352694571</v>
+        <v>3825.009672594496</v>
       </c>
       <c r="N75">
-        <v>-378.0203526945716</v>
+        <v>-429.7096725944971</v>
       </c>
       <c r="O75">
-        <v>-79.38427406586003</v>
+        <v>-90.23903124484438</v>
       </c>
       <c r="P75">
-        <v>-298.6360786287115</v>
+        <v>-339.4706413496527</v>
       </c>
       <c r="Q75">
-        <v>1815.063921371288</v>
+        <v>1774.229358650347</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1301577959114197</v>
+        <v>0.1334023265233975</v>
       </c>
       <c r="T75">
-        <v>1.422393629299022</v>
+        <v>1.477101076579754</v>
       </c>
       <c r="U75">
         <v>0.1304732333250682</v>
       </c>
       <c r="V75">
-        <v>0.1889616924496827</v>
+        <v>0.1864081560652276</v>
       </c>
       <c r="W75">
-        <v>0.105818790336581</v>
+        <v>0.1061519584850741</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8998175830937273</v>
+        <v>0.8876578860248932</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1132370541750381</v>
+        <v>0.1140837865082888</v>
       </c>
       <c r="C76">
-        <v>-11154.93861026764</v>
+        <v>-11750.29087592385</v>
       </c>
       <c r="D76">
-        <v>16062.99338973236</v>
+        <v>15863.80912407616</v>
       </c>
       <c r="E76">
-        <v>3024.632000000001</v>
+        <v>3420.800000000003</v>
       </c>
       <c r="F76">
-        <v>29316.432</v>
+        <v>29712.6</v>
       </c>
       <c r="G76">
         <v>2098.5</v>
@@ -7525,37 +7525,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M76">
-        <v>3825.009672594496</v>
+        <v>3876.698992494422</v>
       </c>
       <c r="N76">
-        <v>-429.7096725944971</v>
+        <v>-481.3989924944231</v>
       </c>
       <c r="O76">
-        <v>-90.23903124484438</v>
+        <v>-101.0937884238288</v>
       </c>
       <c r="P76">
-        <v>-339.4706413496527</v>
+        <v>-380.3052040705942</v>
       </c>
       <c r="Q76">
-        <v>1774.229358650347</v>
+        <v>1733.394795929406</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1334023265233975</v>
+        <v>0.1369064195843334</v>
       </c>
       <c r="T76">
-        <v>1.477101076579754</v>
+        <v>1.536185119642944</v>
       </c>
       <c r="U76">
         <v>0.1304732333250682</v>
       </c>
       <c r="V76">
-        <v>0.1864081560652276</v>
+        <v>0.1839227139843578</v>
       </c>
       <c r="W76">
-        <v>0.1061519584850741</v>
+        <v>0.1064762421496073</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8876578860248932</v>
+        <v>0.8758224475445612</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1140837865082888</v>
+        <v>0.1149305188415395</v>
       </c>
       <c r="C77">
-        <v>-11750.29087592385</v>
+        <v>-12340.76379853932</v>
       </c>
       <c r="D77">
-        <v>15863.80912407616</v>
+        <v>15669.50420146068</v>
       </c>
       <c r="E77">
-        <v>3420.800000000003</v>
+        <v>3816.968000000004</v>
       </c>
       <c r="F77">
-        <v>29712.6</v>
+        <v>30108.768</v>
       </c>
       <c r="G77">
         <v>2098.5</v>
@@ -7607,37 +7607,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M77">
-        <v>3876.698992494422</v>
+        <v>3928.388312394348</v>
       </c>
       <c r="N77">
-        <v>-481.3989924944231</v>
+        <v>-533.0883123943486</v>
       </c>
       <c r="O77">
-        <v>-101.0937884238288</v>
+        <v>-111.9485456028132</v>
       </c>
       <c r="P77">
-        <v>-380.3052040705942</v>
+        <v>-421.1397667915354</v>
       </c>
       <c r="Q77">
-        <v>1733.394795929406</v>
+        <v>1692.560233208465</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1369064195843334</v>
+        <v>0.1407025204003473</v>
       </c>
       <c r="T77">
-        <v>1.536185119642944</v>
+        <v>1.6001928329614</v>
       </c>
       <c r="U77">
         <v>0.1304732333250682</v>
       </c>
       <c r="V77">
-        <v>0.1839227139843578</v>
+        <v>0.1815026782740373</v>
       </c>
       <c r="W77">
-        <v>0.1064762421496073</v>
+        <v>0.106791992033495</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8758224475445612</v>
+        <v>0.8642984679716064</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1149305188415395</v>
+        <v>0.1157772511747902</v>
       </c>
       <c r="C78">
-        <v>-12340.76379853932</v>
+        <v>-12926.53449985497</v>
       </c>
       <c r="D78">
-        <v>15669.50420146068</v>
+        <v>15479.90150014504</v>
       </c>
       <c r="E78">
-        <v>3816.968000000004</v>
+        <v>4213.136000000002</v>
       </c>
       <c r="F78">
-        <v>30108.768</v>
+        <v>30504.936</v>
       </c>
       <c r="G78">
         <v>2098.5</v>
@@ -7689,37 +7689,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M78">
-        <v>3928.388312394348</v>
+        <v>3980.077632294273</v>
       </c>
       <c r="N78">
-        <v>-533.0883123943486</v>
+        <v>-584.7776322942741</v>
       </c>
       <c r="O78">
-        <v>-111.9485456028132</v>
+        <v>-122.8033027817976</v>
       </c>
       <c r="P78">
-        <v>-421.1397667915354</v>
+        <v>-461.9743295124765</v>
       </c>
       <c r="Q78">
-        <v>1692.560233208465</v>
+        <v>1651.725670487523</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1407025204003473</v>
+        <v>0.1448287169394928</v>
       </c>
       <c r="T78">
-        <v>1.6001928329614</v>
+        <v>1.669766434394504</v>
       </c>
       <c r="U78">
         <v>0.1304732333250682</v>
       </c>
       <c r="V78">
-        <v>0.1815026782740373</v>
+        <v>0.1791455006341148</v>
       </c>
       <c r="W78">
-        <v>0.106791992033495</v>
+        <v>0.1070995406216972</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8642984679716064</v>
+        <v>0.8530738125434038</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1157772511747902</v>
+        <v>0.1166239835080409</v>
       </c>
       <c r="C79">
-        <v>-12926.53449985497</v>
+        <v>-13507.77163133386</v>
       </c>
       <c r="D79">
-        <v>15479.90150014504</v>
+        <v>15294.83236866614</v>
       </c>
       <c r="E79">
-        <v>4213.136000000002</v>
+        <v>4609.304000000004</v>
       </c>
       <c r="F79">
-        <v>30504.936</v>
+        <v>30901.104</v>
       </c>
       <c r="G79">
         <v>2098.5</v>
@@ -7771,37 +7771,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M79">
-        <v>3980.077632294273</v>
+        <v>4031.766952194199</v>
       </c>
       <c r="N79">
-        <v>-584.7776322942741</v>
+        <v>-636.4669521942001</v>
       </c>
       <c r="O79">
-        <v>-122.8033027817976</v>
+        <v>-133.658059960782</v>
       </c>
       <c r="P79">
-        <v>-461.9743295124765</v>
+        <v>-502.8088922334181</v>
       </c>
       <c r="Q79">
-        <v>1651.725670487523</v>
+        <v>1610.891107766582</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1448287169394928</v>
+        <v>0.1493300222549243</v>
       </c>
       <c r="T79">
-        <v>1.669766434394504</v>
+        <v>1.745664908685163</v>
       </c>
       <c r="U79">
         <v>0.1304732333250682</v>
       </c>
       <c r="V79">
-        <v>0.1791455006341148</v>
+        <v>0.1768487634464979</v>
       </c>
       <c r="W79">
-        <v>0.1070995406216972</v>
+        <v>0.1073992033486635</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8530738125434038</v>
+        <v>0.8421369687928473</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1166239835080409</v>
+        <v>0.1174707158412915</v>
       </c>
       <c r="C80">
-        <v>-13507.77163133386</v>
+        <v>-14084.63587450906</v>
       </c>
       <c r="D80">
-        <v>15294.83236866614</v>
+        <v>15114.13612549094</v>
       </c>
       <c r="E80">
-        <v>4609.304000000004</v>
+        <v>5005.472000000005</v>
       </c>
       <c r="F80">
-        <v>30901.104</v>
+        <v>31297.272</v>
       </c>
       <c r="G80">
         <v>2098.5</v>
@@ -7853,37 +7853,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M80">
-        <v>4031.766952194199</v>
+        <v>4083.456272094125</v>
       </c>
       <c r="N80">
-        <v>-636.4669521942001</v>
+        <v>-688.1562720941256</v>
       </c>
       <c r="O80">
-        <v>-133.658059960782</v>
+        <v>-144.5128171397664</v>
       </c>
       <c r="P80">
-        <v>-502.8088922334181</v>
+        <v>-543.6434549543592</v>
       </c>
       <c r="Q80">
-        <v>1610.891107766582</v>
+        <v>1570.056545045641</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1493300222549243</v>
+        <v>0.1542600233146826</v>
       </c>
       <c r="T80">
-        <v>1.745664908685163</v>
+        <v>1.828791809098743</v>
       </c>
       <c r="U80">
         <v>0.1304732333250682</v>
       </c>
       <c r="V80">
-        <v>0.1768487634464979</v>
+        <v>0.1746101715041372</v>
       </c>
       <c r="W80">
-        <v>0.1073992033486635</v>
+        <v>0.1076912796774788</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8421369687928473</v>
+        <v>0.831477007162558</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1174707158412915</v>
+        <v>0.1183174481745422</v>
       </c>
       <c r="C81">
-        <v>-14084.63587450906</v>
+        <v>-14657.28040627839</v>
       </c>
       <c r="D81">
-        <v>15114.13612549094</v>
+        <v>14937.65959372161</v>
       </c>
       <c r="E81">
-        <v>5005.472000000005</v>
+        <v>5401.640000000003</v>
       </c>
       <c r="F81">
-        <v>31297.272</v>
+        <v>31693.44</v>
       </c>
       <c r="G81">
         <v>2098.5</v>
@@ -7935,37 +7935,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M81">
-        <v>4083.456272094125</v>
+        <v>4135.14559199405</v>
       </c>
       <c r="N81">
-        <v>-688.1562720941256</v>
+        <v>-739.8455919940507</v>
       </c>
       <c r="O81">
-        <v>-144.5128171397664</v>
+        <v>-155.3675743187506</v>
       </c>
       <c r="P81">
-        <v>-543.6434549543592</v>
+        <v>-584.4780176753001</v>
       </c>
       <c r="Q81">
-        <v>1570.056545045641</v>
+        <v>1529.2219823247</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1542600233146826</v>
+        <v>0.1596830244804167</v>
       </c>
       <c r="T81">
-        <v>1.828791809098743</v>
+        <v>1.92023139955368</v>
       </c>
       <c r="U81">
         <v>0.1304732333250682</v>
       </c>
       <c r="V81">
-        <v>0.1746101715041372</v>
+        <v>0.1724275443603355</v>
       </c>
       <c r="W81">
-        <v>0.1076912796774788</v>
+        <v>0.1079760540980736</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.831477007162558</v>
+        <v>0.8210835445730262</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1183174481745422</v>
+        <v>0.1191641805077929</v>
       </c>
       <c r="C82">
-        <v>-14657.28040627839</v>
+        <v>-15225.85133197798</v>
       </c>
       <c r="D82">
-        <v>14937.65959372161</v>
+        <v>14765.25666802202</v>
       </c>
       <c r="E82">
-        <v>5401.640000000003</v>
+        <v>5797.808000000005</v>
       </c>
       <c r="F82">
-        <v>31693.44</v>
+        <v>32089.608</v>
       </c>
       <c r="G82">
         <v>2098.5</v>
@@ -8017,37 +8017,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M82">
-        <v>4135.14559199405</v>
+        <v>4186.834911893976</v>
       </c>
       <c r="N82">
-        <v>-739.8455919940507</v>
+        <v>-791.5349118939766</v>
       </c>
       <c r="O82">
-        <v>-155.3675743187506</v>
+        <v>-166.2223314977351</v>
       </c>
       <c r="P82">
-        <v>-584.4780176753001</v>
+        <v>-625.3125803962415</v>
       </c>
       <c r="Q82">
-        <v>1529.2219823247</v>
+        <v>1488.387419603758</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1596830244804167</v>
+        <v>0.1656768678741229</v>
       </c>
       <c r="T82">
-        <v>1.92023139955368</v>
+        <v>2.021296210056506</v>
       </c>
       <c r="U82">
         <v>0.1304732333250682</v>
       </c>
       <c r="V82">
-        <v>0.1724275443603355</v>
+        <v>0.1702988092447758</v>
       </c>
       <c r="W82">
-        <v>0.1079760540980736</v>
+        <v>0.1082537970514933</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8210835445730262</v>
+        <v>0.8109467106894085</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1191641805077929</v>
+        <v>0.1200109128410436</v>
       </c>
       <c r="C83">
-        <v>-15225.85133197798</v>
+        <v>-15790.48808880811</v>
       </c>
       <c r="D83">
-        <v>14765.25666802202</v>
+        <v>14596.7879111919</v>
       </c>
       <c r="E83">
-        <v>5797.808000000005</v>
+        <v>6193.976000000006</v>
       </c>
       <c r="F83">
-        <v>32089.608</v>
+        <v>32485.77600000001</v>
       </c>
       <c r="G83">
         <v>2098.5</v>
@@ -8099,37 +8099,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M83">
-        <v>4186.834911893976</v>
+        <v>4238.524231793902</v>
       </c>
       <c r="N83">
-        <v>-791.5349118939766</v>
+        <v>-843.2242317939026</v>
       </c>
       <c r="O83">
-        <v>-166.2223314977351</v>
+        <v>-177.0770886767195</v>
       </c>
       <c r="P83">
-        <v>-625.3125803962415</v>
+        <v>-666.1471431171831</v>
       </c>
       <c r="Q83">
-        <v>1488.387419603758</v>
+        <v>1447.552856882817</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1656768678741229</v>
+        <v>0.1723366938671297</v>
       </c>
       <c r="T83">
-        <v>2.021296210056506</v>
+        <v>2.133590443948534</v>
       </c>
       <c r="U83">
         <v>0.1304732333250682</v>
       </c>
       <c r="V83">
-        <v>0.1702988092447758</v>
+        <v>0.1682219944978883</v>
       </c>
       <c r="W83">
-        <v>0.1082537970514933</v>
+        <v>0.1085247657865369</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8109467106894085</v>
+        <v>0.8010571166566107</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1200109128410436</v>
+        <v>0.1449113760309691</v>
       </c>
       <c r="C84">
-        <v>-15790.48808880811</v>
+        <v>-19853.91200461955</v>
       </c>
       <c r="D84">
-        <v>14596.7879111919</v>
+        <v>10929.53199538046</v>
       </c>
       <c r="E84">
-        <v>6193.976000000006</v>
+        <v>6590.144000000004</v>
       </c>
       <c r="F84">
-        <v>32485.77600000001</v>
+        <v>32881.944</v>
       </c>
       <c r="G84">
         <v>2098.5</v>
@@ -8181,45 +8181,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M84">
-        <v>4238.524231793902</v>
+        <v>5217.484372493827</v>
       </c>
       <c r="N84">
-        <v>-843.2242317939026</v>
+        <v>-1822.184372493828</v>
       </c>
       <c r="O84">
-        <v>-177.0770886767195</v>
+        <v>-382.6587182237039</v>
       </c>
       <c r="P84">
-        <v>-666.1471431171831</v>
+        <v>-1439.525654270124</v>
       </c>
       <c r="Q84">
-        <v>1447.552856882817</v>
+        <v>674.1743457298758</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1723366938671297</v>
+        <v>0.1835902103103419</v>
       </c>
       <c r="T84">
-        <v>2.133590443948534</v>
+        <v>2.32334089822599</v>
       </c>
       <c r="U84">
-        <v>0.1304732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V84">
-        <v>0.1682219944978883</v>
+        <v>0.1366583872793082</v>
       </c>
       <c r="W84">
-        <v>0.1085247657865369</v>
+        <v>0.136989205154471</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8010571166566107</v>
+        <v>0.6507542251395629</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1449113760309691</v>
+        <v>0.192161043835217</v>
       </c>
       <c r="C85">
-        <v>-19853.91200461955</v>
+        <v>-23778.45574249036</v>
       </c>
       <c r="D85">
-        <v>10929.53199538046</v>
+        <v>7401.15625750965</v>
       </c>
       <c r="E85">
-        <v>6590.144000000004</v>
+        <v>6986.312000000009</v>
       </c>
       <c r="F85">
-        <v>32881.944</v>
+        <v>33278.11200000001</v>
       </c>
       <c r="G85">
         <v>2098.5</v>
@@ -8263,45 +8263,45 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M85">
-        <v>5217.484372493827</v>
+        <v>7077.363677993754</v>
       </c>
       <c r="N85">
-        <v>-1822.184372493828</v>
+        <v>-3682.063677993755</v>
       </c>
       <c r="O85">
-        <v>-382.6587182237039</v>
+        <v>-773.2333723786885</v>
       </c>
       <c r="P85">
-        <v>-1439.525654270124</v>
+        <v>-2908.830305615066</v>
       </c>
       <c r="Q85">
-        <v>674.1743457298758</v>
+        <v>-795.1303056150664</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1835902103103419</v>
+        <v>0.196957945148471</v>
       </c>
       <c r="T85">
-        <v>2.32334089822599</v>
+        <v>2.548740111973578</v>
       </c>
       <c r="U85">
-        <v>0.1586732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V85">
-        <v>0.1366583872793082</v>
+        <v>0.1007455646538317</v>
       </c>
       <c r="W85">
-        <v>0.136989205154471</v>
+        <v>0.1912473483469781</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.6507542251395629</v>
+        <v>0.4797407840658652</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.192161043835217</v>
+        <v>0.1938297761684676</v>
       </c>
       <c r="C86">
-        <v>-23778.45574249035</v>
+        <v>-24258.0566103229</v>
       </c>
       <c r="D86">
-        <v>7401.15625750965</v>
+        <v>7317.723389677095</v>
       </c>
       <c r="E86">
-        <v>6986.312000000002</v>
+        <v>7382.48</v>
       </c>
       <c r="F86">
-        <v>33278.112</v>
+        <v>33674.28</v>
       </c>
       <c r="G86">
         <v>2098.5</v>
@@ -8345,37 +8345,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M86">
-        <v>7077.363677993752</v>
+        <v>7161.618007493677</v>
       </c>
       <c r="N86">
-        <v>-3682.063677993753</v>
+        <v>-3766.318007493678</v>
       </c>
       <c r="O86">
-        <v>-773.2333723786882</v>
+        <v>-790.9267815736724</v>
       </c>
       <c r="P86">
-        <v>-2908.830305615065</v>
+        <v>-2975.391225920006</v>
       </c>
       <c r="Q86">
-        <v>-795.130305615065</v>
+        <v>-861.6912259200058</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1969579451484709</v>
+        <v>0.2070351414917023</v>
       </c>
       <c r="T86">
-        <v>2.548740111973576</v>
+        <v>2.718656119438481</v>
       </c>
       <c r="U86">
         <v>0.2126732333250682</v>
       </c>
       <c r="V86">
-        <v>0.1007455646538317</v>
+        <v>0.09956032271672782</v>
       </c>
       <c r="W86">
-        <v>0.1912473483469781</v>
+        <v>0.1914994175820144</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4797407840658653</v>
+        <v>0.4740967748415611</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1938297761684676</v>
+        <v>0.1954985085017183</v>
       </c>
       <c r="C87">
-        <v>-24258.0566103229</v>
+        <v>-24735.79737780308</v>
       </c>
       <c r="D87">
-        <v>7317.723389677095</v>
+        <v>7236.150622196923</v>
       </c>
       <c r="E87">
-        <v>7382.48</v>
+        <v>7778.648000000005</v>
       </c>
       <c r="F87">
-        <v>33674.28</v>
+        <v>34070.448</v>
       </c>
       <c r="G87">
         <v>2098.5</v>
@@ -8427,37 +8427,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M87">
-        <v>7161.618007493677</v>
+        <v>7245.872336993604</v>
       </c>
       <c r="N87">
-        <v>-3766.318007493678</v>
+        <v>-3850.572336993605</v>
       </c>
       <c r="O87">
-        <v>-790.9267815736724</v>
+        <v>-808.620190768657</v>
       </c>
       <c r="P87">
-        <v>-2975.391225920006</v>
+        <v>-3041.952146224948</v>
       </c>
       <c r="Q87">
-        <v>-861.6912259200058</v>
+        <v>-928.2521462249479</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2070351414917023</v>
+        <v>0.2185519373125382</v>
       </c>
       <c r="T87">
-        <v>2.718656119438481</v>
+        <v>2.912845842255515</v>
       </c>
       <c r="U87">
         <v>0.2126732333250682</v>
       </c>
       <c r="V87">
-        <v>0.09956032271672782</v>
+        <v>0.09840264454560306</v>
       </c>
       <c r="W87">
-        <v>0.1914994175820144</v>
+        <v>0.1917456247418174</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4740967748415611</v>
+        <v>0.4685840216457289</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1954985085017183</v>
+        <v>0.197167240834969</v>
       </c>
       <c r="C88">
-        <v>-24735.79737780308</v>
+        <v>-25211.73956437689</v>
       </c>
       <c r="D88">
-        <v>7236.150622196923</v>
+        <v>7156.37643562311</v>
       </c>
       <c r="E88">
-        <v>7778.648000000005</v>
+        <v>8174.816000000003</v>
       </c>
       <c r="F88">
-        <v>34070.448</v>
+        <v>34466.616</v>
       </c>
       <c r="G88">
         <v>2098.5</v>
@@ -8509,37 +8509,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M88">
-        <v>7245.872336993604</v>
+        <v>7330.126666493529</v>
       </c>
       <c r="N88">
-        <v>-3850.572336993605</v>
+        <v>-3934.82666649353</v>
       </c>
       <c r="O88">
-        <v>-808.620190768657</v>
+        <v>-826.3135999636413</v>
       </c>
       <c r="P88">
-        <v>-3041.952146224948</v>
+        <v>-3108.513066529888</v>
       </c>
       <c r="Q88">
-        <v>-928.2521462249479</v>
+        <v>-994.8130665298886</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2185519373125382</v>
+        <v>0.2318405478750411</v>
       </c>
       <c r="T88">
-        <v>2.912845842255515</v>
+        <v>3.136910907044401</v>
       </c>
       <c r="U88">
         <v>0.2126732333250682</v>
       </c>
       <c r="V88">
-        <v>0.09840264454560306</v>
+        <v>0.09727157966576855</v>
       </c>
       <c r="W88">
-        <v>0.1917456247418174</v>
+        <v>0.1919861719669123</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4685840216457289</v>
+        <v>0.4631979984084217</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.197167240834969</v>
+        <v>0.1988359731682197</v>
       </c>
       <c r="C89">
-        <v>-25211.73956437689</v>
+        <v>-25685.94200621307</v>
       </c>
       <c r="D89">
-        <v>7156.37643562311</v>
+        <v>7078.341993786935</v>
       </c>
       <c r="E89">
-        <v>8174.816000000003</v>
+        <v>8570.984</v>
       </c>
       <c r="F89">
-        <v>34466.616</v>
+        <v>34862.784</v>
       </c>
       <c r="G89">
         <v>2098.5</v>
@@ -8591,37 +8591,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M89">
-        <v>7330.126666493529</v>
+        <v>7414.380995993455</v>
       </c>
       <c r="N89">
-        <v>-3934.82666649353</v>
+        <v>-4019.080995993456</v>
       </c>
       <c r="O89">
-        <v>-826.3135999636413</v>
+        <v>-844.0070091586257</v>
       </c>
       <c r="P89">
-        <v>-3108.513066529888</v>
+        <v>-3175.07398683483</v>
       </c>
       <c r="Q89">
-        <v>-994.8130665298886</v>
+        <v>-1061.37398683483</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2318405478750411</v>
+        <v>0.2473439268646279</v>
       </c>
       <c r="T89">
-        <v>3.136910907044401</v>
+        <v>3.398320149298101</v>
       </c>
       <c r="U89">
         <v>0.2126732333250682</v>
       </c>
       <c r="V89">
-        <v>0.09727157966576855</v>
+        <v>0.09616622080593026</v>
       </c>
       <c r="W89">
-        <v>0.1919861719669123</v>
+        <v>0.1922212522096186</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4631979984084217</v>
+        <v>0.4579343847901441</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1988359731682197</v>
+        <v>0.2005047055014704</v>
       </c>
       <c r="C90">
-        <v>-25685.94200621307</v>
+        <v>-26158.46100091973</v>
       </c>
       <c r="D90">
-        <v>7078.341993786935</v>
+        <v>7001.990999080273</v>
       </c>
       <c r="E90">
-        <v>8570.984</v>
+        <v>8967.152000000006</v>
       </c>
       <c r="F90">
-        <v>34862.784</v>
+        <v>35258.952</v>
       </c>
       <c r="G90">
         <v>2098.5</v>
@@ -8673,37 +8673,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M90">
-        <v>7414.380995993455</v>
+        <v>7498.635325493381</v>
       </c>
       <c r="N90">
-        <v>-4019.080995993456</v>
+        <v>-4103.335325493382</v>
       </c>
       <c r="O90">
-        <v>-844.0070091586257</v>
+        <v>-861.7004183536102</v>
       </c>
       <c r="P90">
-        <v>-3175.07398683483</v>
+        <v>-3241.634907139772</v>
       </c>
       <c r="Q90">
-        <v>-1061.37398683483</v>
+        <v>-1127.934907139772</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2473439268646279</v>
+        <v>0.2656661020341396</v>
       </c>
       <c r="T90">
-        <v>3.398320149298101</v>
+        <v>3.707258344688839</v>
       </c>
       <c r="U90">
         <v>0.2126732333250682</v>
       </c>
       <c r="V90">
-        <v>0.09616622080593026</v>
+        <v>0.09508570147103217</v>
       </c>
       <c r="W90">
-        <v>0.1922212522096186</v>
+        <v>0.1924510497502416</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4579343847901441</v>
+        <v>0.4527890546239628</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2005047055014704</v>
+        <v>0.2021734378347211</v>
       </c>
       <c r="C91">
-        <v>-26158.46100091973</v>
+        <v>-26629.35044299511</v>
       </c>
       <c r="D91">
-        <v>7001.990999080273</v>
+        <v>6927.269557004893</v>
       </c>
       <c r="E91">
-        <v>8967.152000000006</v>
+        <v>9363.320000000003</v>
       </c>
       <c r="F91">
-        <v>35258.952</v>
+        <v>35655.12</v>
       </c>
       <c r="G91">
         <v>2098.5</v>
@@ -8755,37 +8755,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M91">
-        <v>7498.635325493381</v>
+        <v>7582.889654993307</v>
       </c>
       <c r="N91">
-        <v>-4103.335325493382</v>
+        <v>-4187.589654993308</v>
       </c>
       <c r="O91">
-        <v>-861.7004183536102</v>
+        <v>-879.3938275485946</v>
       </c>
       <c r="P91">
-        <v>-3241.634907139772</v>
+        <v>-3308.195827444713</v>
       </c>
       <c r="Q91">
-        <v>-1127.934907139772</v>
+        <v>-1194.495827444714</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2656661020341396</v>
+        <v>0.2876527122375535</v>
       </c>
       <c r="T91">
-        <v>3.707258344688839</v>
+        <v>4.077984179157722</v>
       </c>
       <c r="U91">
         <v>0.2126732333250682</v>
       </c>
       <c r="V91">
-        <v>0.09508570147103217</v>
+        <v>0.09402919367690959</v>
       </c>
       <c r="W91">
-        <v>0.1924510497502416</v>
+        <v>0.1926757406788508</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4527890546239628</v>
+        <v>0.447758065128141</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2021734378347211</v>
+        <v>0.2038421701679717</v>
       </c>
       <c r="C92">
-        <v>-26629.35044299511</v>
+        <v>-27098.66195069708</v>
       </c>
       <c r="D92">
-        <v>6927.269557004893</v>
+        <v>6854.126049302923</v>
       </c>
       <c r="E92">
-        <v>9363.320000000003</v>
+        <v>9759.488000000001</v>
       </c>
       <c r="F92">
-        <v>35655.12</v>
+        <v>36051.288</v>
       </c>
       <c r="G92">
         <v>2098.5</v>
@@ -8837,37 +8837,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M92">
-        <v>7582.889654993307</v>
+        <v>7667.143984493232</v>
       </c>
       <c r="N92">
-        <v>-4187.589654993308</v>
+        <v>-4271.843984493233</v>
       </c>
       <c r="O92">
-        <v>-879.3938275485946</v>
+        <v>-897.0872367435788</v>
       </c>
       <c r="P92">
-        <v>-3308.195827444713</v>
+        <v>-3374.756747749654</v>
       </c>
       <c r="Q92">
-        <v>-1194.495827444714</v>
+        <v>-1261.056747749654</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2876527122375535</v>
+        <v>0.314525235819504</v>
       </c>
       <c r="T92">
-        <v>4.077984179157722</v>
+        <v>4.53109353239747</v>
       </c>
       <c r="U92">
         <v>0.2126732333250682</v>
       </c>
       <c r="V92">
-        <v>0.09402919367690959</v>
+        <v>0.0929959058343062</v>
       </c>
       <c r="W92">
-        <v>0.1926757406788508</v>
+        <v>0.1928954933452927</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.447758065128141</v>
+        <v>0.4428376468300296</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2038421701679717</v>
+        <v>0.2055109025012224</v>
       </c>
       <c r="C93">
-        <v>-27098.66195069708</v>
+        <v>-27566.44498495913</v>
       </c>
       <c r="D93">
-        <v>6854.126049302923</v>
+        <v>6782.511015040874</v>
       </c>
       <c r="E93">
-        <v>9759.488000000001</v>
+        <v>10155.65600000001</v>
       </c>
       <c r="F93">
-        <v>36051.288</v>
+        <v>36447.45600000001</v>
       </c>
       <c r="G93">
         <v>2098.5</v>
@@ -8919,37 +8919,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M93">
-        <v>7667.143984493232</v>
+        <v>7751.398313993159</v>
       </c>
       <c r="N93">
-        <v>-4271.843984493233</v>
+        <v>-4356.09831399316</v>
       </c>
       <c r="O93">
-        <v>-897.0872367435788</v>
+        <v>-914.7806459385635</v>
       </c>
       <c r="P93">
-        <v>-3374.756747749654</v>
+        <v>-3441.317668054596</v>
       </c>
       <c r="Q93">
-        <v>-1261.056747749654</v>
+        <v>-1327.617668054596</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.314525235819504</v>
+        <v>0.3481158902969421</v>
       </c>
       <c r="T93">
-        <v>4.53109353239747</v>
+        <v>5.097480223947155</v>
       </c>
       <c r="U93">
         <v>0.2126732333250682</v>
       </c>
       <c r="V93">
-        <v>0.0929959058343062</v>
+        <v>0.09198508077088982</v>
       </c>
       <c r="W93">
-        <v>0.1928954933452927</v>
+        <v>0.1931104687798555</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4428376468300296</v>
+        <v>0.4380241941470944</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2055109025012224</v>
+        <v>0.2071796348344731</v>
       </c>
       <c r="C94">
-        <v>-27566.44498495913</v>
+        <v>-28032.7469609285</v>
       </c>
       <c r="D94">
-        <v>6782.511015040874</v>
+        <v>6712.3770390715</v>
       </c>
       <c r="E94">
-        <v>10155.65600000001</v>
+        <v>10551.824</v>
       </c>
       <c r="F94">
-        <v>36447.45600000001</v>
+        <v>36843.624</v>
       </c>
       <c r="G94">
         <v>2098.5</v>
@@ -9001,37 +9001,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M94">
-        <v>7751.398313993159</v>
+        <v>7835.652643493084</v>
       </c>
       <c r="N94">
-        <v>-4356.09831399316</v>
+        <v>-4440.352643493085</v>
       </c>
       <c r="O94">
-        <v>-914.7806459385635</v>
+        <v>-932.4740551335477</v>
       </c>
       <c r="P94">
-        <v>-3441.317668054596</v>
+        <v>-3507.878588359537</v>
       </c>
       <c r="Q94">
-        <v>-1327.617668054596</v>
+        <v>-1394.178588359537</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3481158902969421</v>
+        <v>0.3913038746250767</v>
       </c>
       <c r="T94">
-        <v>5.097480223947155</v>
+        <v>5.825691684511035</v>
       </c>
       <c r="U94">
         <v>0.2126732333250682</v>
       </c>
       <c r="V94">
-        <v>0.09198508077088982</v>
+        <v>0.09099599388088025</v>
       </c>
       <c r="W94">
-        <v>0.1931104687798555</v>
+        <v>0.1933208210867933</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4380241941470944</v>
+        <v>0.4333142565756203</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2071796348344731</v>
+        <v>0.2088483671677238</v>
       </c>
       <c r="C95">
-        <v>-28032.7469609285</v>
+        <v>-28497.61335265509</v>
       </c>
       <c r="D95">
-        <v>6712.3770390715</v>
+        <v>6643.678647344913</v>
       </c>
       <c r="E95">
-        <v>10551.824</v>
+        <v>10947.99200000001</v>
       </c>
       <c r="F95">
-        <v>36843.624</v>
+        <v>37239.79200000001</v>
       </c>
       <c r="G95">
         <v>2098.5</v>
@@ -9083,37 +9083,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M95">
-        <v>7835.652643493084</v>
+        <v>7919.906972993011</v>
       </c>
       <c r="N95">
-        <v>-4440.352643493085</v>
+        <v>-4524.606972993011</v>
       </c>
       <c r="O95">
-        <v>-932.4740551335477</v>
+        <v>-950.1674643285323</v>
       </c>
       <c r="P95">
-        <v>-3507.878588359537</v>
+        <v>-3574.439508664479</v>
       </c>
       <c r="Q95">
-        <v>-1394.178588359537</v>
+        <v>-1460.739508664479</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3913038746250767</v>
+        <v>0.4488878537292563</v>
       </c>
       <c r="T95">
-        <v>5.825691684511035</v>
+        <v>6.79664029859621</v>
       </c>
       <c r="U95">
         <v>0.2126732333250682</v>
       </c>
       <c r="V95">
-        <v>0.09099599388088025</v>
+        <v>0.09002795139278576</v>
       </c>
       <c r="W95">
-        <v>0.1933208210867933</v>
+        <v>0.1935266978127324</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4333142565756203</v>
+        <v>0.428704530441837</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2088483671677238</v>
+        <v>0.2105170995009745</v>
       </c>
       <c r="C96">
-        <v>-28497.61335265509</v>
+        <v>-28961.0877914167</v>
       </c>
       <c r="D96">
-        <v>6643.678647344913</v>
+        <v>6576.372208583308</v>
       </c>
       <c r="E96">
-        <v>10947.99200000001</v>
+        <v>11344.16000000001</v>
       </c>
       <c r="F96">
-        <v>37239.79200000001</v>
+        <v>37635.96000000001</v>
       </c>
       <c r="G96">
         <v>2098.5</v>
@@ -9165,37 +9165,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M96">
-        <v>7919.906972993011</v>
+        <v>8004.161302492936</v>
       </c>
       <c r="N96">
-        <v>-4524.606972993011</v>
+        <v>-4608.861302492936</v>
       </c>
       <c r="O96">
-        <v>-950.1674643285323</v>
+        <v>-967.8608735235166</v>
       </c>
       <c r="P96">
-        <v>-3574.439508664479</v>
+        <v>-3641.00042896942</v>
       </c>
       <c r="Q96">
-        <v>-1460.739508664479</v>
+        <v>-1527.30042896942</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4488878537292563</v>
+        <v>0.5295054244751077</v>
       </c>
       <c r="T96">
-        <v>6.79664029859621</v>
+        <v>8.155968358315455</v>
       </c>
       <c r="U96">
         <v>0.2126732333250682</v>
       </c>
       <c r="V96">
-        <v>0.09002795139278576</v>
+        <v>0.08908028874654593</v>
       </c>
       <c r="W96">
-        <v>0.1935266978127324</v>
+        <v>0.1937282402918096</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.428704530441837</v>
+        <v>0.4241918511740282</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2105170995009745</v>
+        <v>0.2121858318342252</v>
       </c>
       <c r="C97">
-        <v>-28961.0877914167</v>
+        <v>-29423.21215812758</v>
       </c>
       <c r="D97">
-        <v>6576.372208583308</v>
+        <v>6510.415841872425</v>
       </c>
       <c r="E97">
-        <v>11344.16000000001</v>
+        <v>11740.328</v>
       </c>
       <c r="F97">
-        <v>37635.96000000001</v>
+        <v>38032.128</v>
       </c>
       <c r="G97">
         <v>2098.5</v>
@@ -9247,37 +9247,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M97">
-        <v>8004.161302492936</v>
+        <v>8088.415631992861</v>
       </c>
       <c r="N97">
-        <v>-4608.861302492936</v>
+        <v>-4693.115631992861</v>
       </c>
       <c r="O97">
-        <v>-967.8608735235166</v>
+        <v>-985.5542827185009</v>
       </c>
       <c r="P97">
-        <v>-3641.00042896942</v>
+        <v>-3707.561349274361</v>
       </c>
       <c r="Q97">
-        <v>-1527.30042896942</v>
+        <v>-1593.861349274361</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5295054244751077</v>
+        <v>0.6504317805938848</v>
       </c>
       <c r="T97">
-        <v>8.155968358315455</v>
+        <v>10.19496044789432</v>
       </c>
       <c r="U97">
         <v>0.2126732333250682</v>
       </c>
       <c r="V97">
-        <v>0.08908028874654593</v>
+        <v>0.08815236907210275</v>
       </c>
       <c r="W97">
-        <v>0.1937282402918096</v>
+        <v>0.1939255839692394</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4241918511740282</v>
+        <v>0.4197731860576321</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2121858318342252</v>
+        <v>0.2138545641674758</v>
       </c>
       <c r="C98">
-        <v>-29423.21215812758</v>
+        <v>-29884.02667024143</v>
       </c>
       <c r="D98">
-        <v>6510.415841872425</v>
+        <v>6445.769329758575</v>
       </c>
       <c r="E98">
-        <v>11740.328</v>
+        <v>12136.496</v>
       </c>
       <c r="F98">
-        <v>38032.128</v>
+        <v>38428.296</v>
       </c>
       <c r="G98">
         <v>2098.5</v>
@@ -9329,37 +9329,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M98">
-        <v>8088.415631992861</v>
+        <v>8172.669961492786</v>
       </c>
       <c r="N98">
-        <v>-4693.115631992861</v>
+        <v>-4777.369961492786</v>
       </c>
       <c r="O98">
-        <v>-985.5542827185009</v>
+        <v>-1003.247691913485</v>
       </c>
       <c r="P98">
-        <v>-3707.561349274361</v>
+        <v>-3774.122269579301</v>
       </c>
       <c r="Q98">
-        <v>-1593.861349274361</v>
+        <v>-1660.422269579301</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6504317805938832</v>
+        <v>0.851975707458511</v>
       </c>
       <c r="T98">
-        <v>10.1949604478943</v>
+        <v>13.5932805971924</v>
       </c>
       <c r="U98">
         <v>0.2126732333250682</v>
       </c>
       <c r="V98">
-        <v>0.08815236907210275</v>
+        <v>0.08724358176208107</v>
       </c>
       <c r="W98">
-        <v>0.1939255839692394</v>
+        <v>0.1941188587048665</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4197731860576321</v>
+        <v>0.4154456274384813</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2138545641674758</v>
+        <v>0.2155232965007265</v>
       </c>
       <c r="C99">
-        <v>-29884.02667024143</v>
+        <v>-30343.56996352768</v>
       </c>
       <c r="D99">
-        <v>6445.769329758575</v>
+        <v>6382.394036472321</v>
       </c>
       <c r="E99">
-        <v>12136.496</v>
+        <v>12532.664</v>
       </c>
       <c r="F99">
-        <v>38428.296</v>
+        <v>38824.464</v>
       </c>
       <c r="G99">
         <v>2098.5</v>
@@ -9411,37 +9411,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M99">
-        <v>8172.669961492786</v>
+        <v>8256.924290992711</v>
       </c>
       <c r="N99">
-        <v>-4777.369961492786</v>
+        <v>-4861.624290992711</v>
       </c>
       <c r="O99">
-        <v>-1003.247691913485</v>
+        <v>-1020.941101108469</v>
       </c>
       <c r="P99">
-        <v>-3774.122269579301</v>
+        <v>-3840.683189884242</v>
       </c>
       <c r="Q99">
-        <v>-1660.422269579301</v>
+        <v>-1726.983189884242</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.851975707458511</v>
+        <v>1.255063561187767</v>
       </c>
       <c r="T99">
-        <v>13.5932805971924</v>
+        <v>20.38992089578859</v>
       </c>
       <c r="U99">
         <v>0.2126732333250682</v>
       </c>
       <c r="V99">
-        <v>0.08724358176208107</v>
+        <v>0.08635334113185576</v>
       </c>
       <c r="W99">
-        <v>0.1941188587048665</v>
+        <v>0.1943081890581339</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4154456274384813</v>
+        <v>0.4112063863421703</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2155232965007265</v>
+        <v>0.2171920288339772</v>
       </c>
       <c r="C100">
-        <v>-30343.56996352768</v>
+        <v>-30801.87916907071</v>
       </c>
       <c r="D100">
-        <v>6382.394036472321</v>
+        <v>6320.252830929297</v>
       </c>
       <c r="E100">
-        <v>12532.664</v>
+        <v>12928.83200000001</v>
       </c>
       <c r="F100">
-        <v>38824.464</v>
+        <v>39220.63200000001</v>
       </c>
       <c r="G100">
         <v>2098.5</v>
@@ -9493,37 +9493,37 @@
         <v>3395.299999999999</v>
       </c>
       <c r="M100">
-        <v>8256.924290992711</v>
+        <v>8341.178620492637</v>
       </c>
       <c r="N100">
-        <v>-4861.624290992711</v>
+        <v>-4945.878620492638</v>
       </c>
       <c r="O100">
-        <v>-1020.941101108469</v>
+        <v>-1038.634510303454</v>
       </c>
       <c r="P100">
-        <v>-3840.683189884242</v>
+        <v>-3907.244110189185</v>
       </c>
       <c r="Q100">
-        <v>-1726.983189884242</v>
+        <v>-1793.544110189185</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.255063561187767</v>
+        <v>2.464327122375533</v>
       </c>
       <c r="T100">
-        <v>20.38992089578859</v>
+        <v>40.77984179157718</v>
       </c>
       <c r="U100">
         <v>0.2126732333250682</v>
       </c>
       <c r="V100">
-        <v>0.08635334113185576</v>
+        <v>0.08548108516082689</v>
       </c>
       <c r="W100">
-        <v>0.1943081890581339</v>
+        <v>0.1944936945557797</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4112063863421703</v>
+        <v>0.4070527864801281</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2171920288339772</v>
-      </c>
-      <c r="C101">
-        <v>-30801.87916907071</v>
-      </c>
-      <c r="D101">
-        <v>6320.252830929297</v>
-      </c>
-      <c r="E101">
-        <v>12928.83200000001</v>
-      </c>
-      <c r="F101">
-        <v>39220.63200000001</v>
-      </c>
-      <c r="G101">
-        <v>2098.5</v>
-      </c>
-      <c r="H101">
-        <v>13325</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5508.999999999999</v>
-      </c>
-      <c r="K101">
-        <v>2113.7</v>
-      </c>
-      <c r="L101">
-        <v>3395.299999999999</v>
-      </c>
-      <c r="M101">
-        <v>8341.178620492637</v>
-      </c>
-      <c r="N101">
-        <v>-4945.878620492638</v>
-      </c>
-      <c r="O101">
-        <v>-1038.634510303454</v>
-      </c>
-      <c r="P101">
-        <v>-3907.244110189185</v>
-      </c>
-      <c r="Q101">
-        <v>-1793.544110189185</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.464327122375533</v>
-      </c>
-      <c r="T101">
-        <v>40.77984179157718</v>
-      </c>
-      <c r="U101">
-        <v>0.2126732333250682</v>
-      </c>
-      <c r="V101">
-        <v>0.08548108516082689</v>
-      </c>
-      <c r="W101">
-        <v>0.1944936945557797</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4070527864801281</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
